--- a/AAII_Financials/Quarterly/HUYA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HUYA_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -794,25 +794,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>227500</v>
+        <v>229100</v>
       </c>
       <c r="E8" s="3">
-        <v>251500</v>
+        <v>253200</v>
       </c>
       <c r="F8" s="3">
-        <v>269100</v>
+        <v>271000</v>
       </c>
       <c r="G8" s="3">
-        <v>290300</v>
+        <v>292200</v>
       </c>
       <c r="H8" s="3">
-        <v>328400</v>
+        <v>330700</v>
       </c>
       <c r="I8" s="3">
-        <v>314200</v>
+        <v>316300</v>
       </c>
       <c r="J8" s="3">
-        <v>340300</v>
+        <v>342600</v>
       </c>
       <c r="K8" s="3">
         <v>387000</v>
@@ -886,25 +886,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>196000</v>
+        <v>197300</v>
       </c>
       <c r="E9" s="3">
-        <v>213800</v>
+        <v>215300</v>
       </c>
       <c r="F9" s="3">
-        <v>233700</v>
+        <v>235300</v>
       </c>
       <c r="G9" s="3">
-        <v>329500</v>
+        <v>331800</v>
       </c>
       <c r="H9" s="3">
-        <v>281200</v>
+        <v>283100</v>
       </c>
       <c r="I9" s="3">
-        <v>283900</v>
+        <v>285800</v>
       </c>
       <c r="J9" s="3">
-        <v>294200</v>
+        <v>296200</v>
       </c>
       <c r="K9" s="3">
         <v>386800</v>
@@ -978,25 +978,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>31500</v>
+        <v>31700</v>
       </c>
       <c r="E10" s="3">
-        <v>37700</v>
+        <v>38000</v>
       </c>
       <c r="F10" s="3">
-        <v>35400</v>
+        <v>35600</v>
       </c>
       <c r="G10" s="3">
-        <v>-39200</v>
+        <v>-39500</v>
       </c>
       <c r="H10" s="3">
-        <v>47300</v>
+        <v>47600</v>
       </c>
       <c r="I10" s="3">
-        <v>30300</v>
+        <v>30500</v>
       </c>
       <c r="J10" s="3">
-        <v>46100</v>
+        <v>46400</v>
       </c>
       <c r="K10" s="3">
         <v>100</v>
@@ -1104,25 +1104,25 @@
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>19600</v>
+        <v>19700</v>
       </c>
       <c r="E12" s="3">
-        <v>19900</v>
+        <v>20100</v>
       </c>
       <c r="F12" s="3">
-        <v>21000</v>
+        <v>21200</v>
       </c>
       <c r="G12" s="3">
-        <v>19900</v>
+        <v>20000</v>
       </c>
       <c r="H12" s="3">
-        <v>23700</v>
+        <v>23900</v>
       </c>
       <c r="I12" s="3">
-        <v>23300</v>
+        <v>23400</v>
       </c>
       <c r="J12" s="3">
-        <v>27100</v>
+        <v>27300</v>
       </c>
       <c r="K12" s="3">
         <v>28300</v>
@@ -1291,13 +1291,13 @@
         <v>11200</v>
       </c>
       <c r="E14" s="3">
-        <v>9000</v>
+        <v>9100</v>
       </c>
       <c r="F14" s="3">
         <v>0</v>
       </c>
       <c r="G14" s="3">
-        <v>7600</v>
+        <v>7700</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>16</v>
@@ -1503,25 +1503,25 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>242600</v>
+        <v>244300</v>
       </c>
       <c r="E17" s="3">
-        <v>264500</v>
+        <v>266300</v>
       </c>
       <c r="F17" s="3">
-        <v>276200</v>
+        <v>278000</v>
       </c>
       <c r="G17" s="3">
-        <v>377500</v>
+        <v>380100</v>
       </c>
       <c r="H17" s="3">
-        <v>326800</v>
+        <v>329100</v>
       </c>
       <c r="I17" s="3">
-        <v>325400</v>
+        <v>327600</v>
       </c>
       <c r="J17" s="3">
-        <v>348600</v>
+        <v>351000</v>
       </c>
       <c r="K17" s="3">
         <v>450000</v>
@@ -1595,25 +1595,25 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>-15100</v>
+        <v>-15200</v>
       </c>
       <c r="E18" s="3">
-        <v>-13000</v>
+        <v>-13100</v>
       </c>
       <c r="F18" s="3">
-        <v>-7000</v>
+        <v>-7100</v>
       </c>
       <c r="G18" s="3">
-        <v>-87300</v>
+        <v>-87800</v>
       </c>
       <c r="H18" s="3">
         <v>1600</v>
       </c>
       <c r="I18" s="3">
-        <v>-11200</v>
+        <v>-11300</v>
       </c>
       <c r="J18" s="3">
-        <v>-8300</v>
+        <v>-8400</v>
       </c>
       <c r="K18" s="3">
         <v>-63000</v>
@@ -1721,25 +1721,25 @@
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>17500</v>
+        <v>17600</v>
       </c>
       <c r="E20" s="3">
-        <v>16900</v>
+        <v>17100</v>
       </c>
       <c r="F20" s="3">
-        <v>13400</v>
+        <v>13500</v>
       </c>
       <c r="G20" s="3">
-        <v>14600</v>
+        <v>14700</v>
       </c>
       <c r="H20" s="3">
-        <v>9400</v>
+        <v>9500</v>
       </c>
       <c r="I20" s="3">
         <v>8700</v>
       </c>
       <c r="J20" s="3">
-        <v>9200</v>
+        <v>9300</v>
       </c>
       <c r="K20" s="3">
         <v>8500</v>
@@ -1997,7 +1997,7 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>2300</v>
+        <v>2400</v>
       </c>
       <c r="E23" s="3">
         <v>4000</v>
@@ -2006,10 +2006,10 @@
         <v>6400</v>
       </c>
       <c r="G23" s="3">
-        <v>-72700</v>
+        <v>-73200</v>
       </c>
       <c r="H23" s="3">
-        <v>11000</v>
+        <v>11100</v>
       </c>
       <c r="I23" s="3">
         <v>-2500</v>
@@ -2282,10 +2282,10 @@
         <v>6200</v>
       </c>
       <c r="G26" s="3">
-        <v>-72400</v>
+        <v>-72800</v>
       </c>
       <c r="H26" s="3">
-        <v>8300</v>
+        <v>8400</v>
       </c>
       <c r="I26" s="3">
         <v>-2700</v>
@@ -2374,10 +2374,10 @@
         <v>6200</v>
       </c>
       <c r="G27" s="3">
-        <v>-72400</v>
+        <v>-72900</v>
       </c>
       <c r="H27" s="3">
-        <v>8300</v>
+        <v>8400</v>
       </c>
       <c r="I27" s="3">
         <v>-2700</v>
@@ -2825,25 +2825,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-17500</v>
+        <v>-17600</v>
       </c>
       <c r="E32" s="3">
-        <v>-16900</v>
+        <v>-17100</v>
       </c>
       <c r="F32" s="3">
-        <v>-13400</v>
+        <v>-13500</v>
       </c>
       <c r="G32" s="3">
-        <v>-14600</v>
+        <v>-14700</v>
       </c>
       <c r="H32" s="3">
-        <v>-9400</v>
+        <v>-9500</v>
       </c>
       <c r="I32" s="3">
         <v>-8700</v>
       </c>
       <c r="J32" s="3">
-        <v>-9200</v>
+        <v>-9300</v>
       </c>
       <c r="K32" s="3">
         <v>-8500</v>
@@ -2926,10 +2926,10 @@
         <v>6200</v>
       </c>
       <c r="G33" s="3">
-        <v>-72400</v>
+        <v>-72900</v>
       </c>
       <c r="H33" s="3">
-        <v>8300</v>
+        <v>8400</v>
       </c>
       <c r="I33" s="3">
         <v>-2700</v>
@@ -3110,10 +3110,10 @@
         <v>6200</v>
       </c>
       <c r="G35" s="3">
-        <v>-72400</v>
+        <v>-72900</v>
       </c>
       <c r="H35" s="3">
-        <v>8300</v>
+        <v>8400</v>
       </c>
       <c r="I35" s="3">
         <v>-2700</v>
@@ -3358,25 +3358,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>114000</v>
+        <v>114800</v>
       </c>
       <c r="E41" s="3">
-        <v>95600</v>
+        <v>96200</v>
       </c>
       <c r="F41" s="3">
-        <v>268000</v>
+        <v>269900</v>
       </c>
       <c r="G41" s="3">
-        <v>90500</v>
+        <v>91100</v>
       </c>
       <c r="H41" s="3">
-        <v>149500</v>
+        <v>150500</v>
       </c>
       <c r="I41" s="3">
-        <v>285600</v>
+        <v>287500</v>
       </c>
       <c r="J41" s="3">
-        <v>204400</v>
+        <v>205800</v>
       </c>
       <c r="K41" s="3">
         <v>1397500</v>
@@ -3450,25 +3450,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>1057300</v>
+        <v>1064500</v>
       </c>
       <c r="E42" s="3">
-        <v>1150300</v>
+        <v>1158100</v>
       </c>
       <c r="F42" s="3">
-        <v>1081100</v>
+        <v>1088400</v>
       </c>
       <c r="G42" s="3">
-        <v>1245700</v>
+        <v>1254200</v>
       </c>
       <c r="H42" s="3">
-        <v>1321500</v>
+        <v>1330500</v>
       </c>
       <c r="I42" s="3">
-        <v>1194200</v>
+        <v>1202300</v>
       </c>
       <c r="J42" s="3">
-        <v>1241800</v>
+        <v>1250300</v>
       </c>
       <c r="K42" s="3">
         <v>112500</v>
@@ -3542,25 +3542,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>24000</v>
+        <v>24100</v>
       </c>
       <c r="E43" s="3">
-        <v>17100</v>
+        <v>17200</v>
       </c>
       <c r="F43" s="3">
-        <v>20500</v>
+        <v>20600</v>
       </c>
       <c r="G43" s="3">
-        <v>18700</v>
+        <v>18900</v>
       </c>
       <c r="H43" s="3">
-        <v>21600</v>
+        <v>21700</v>
       </c>
       <c r="I43" s="3">
-        <v>30200</v>
+        <v>30400</v>
       </c>
       <c r="J43" s="3">
-        <v>30300</v>
+        <v>30500</v>
       </c>
       <c r="K43" s="3">
         <v>32600</v>
@@ -3726,25 +3726,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>94300</v>
+        <v>95000</v>
       </c>
       <c r="E45" s="3">
-        <v>84800</v>
+        <v>85400</v>
       </c>
       <c r="F45" s="3">
-        <v>81000</v>
+        <v>81500</v>
       </c>
       <c r="G45" s="3">
-        <v>88500</v>
+        <v>89200</v>
       </c>
       <c r="H45" s="3">
-        <v>140400</v>
+        <v>141300</v>
       </c>
       <c r="I45" s="3">
-        <v>110400</v>
+        <v>111200</v>
       </c>
       <c r="J45" s="3">
-        <v>128300</v>
+        <v>129200</v>
       </c>
       <c r="K45" s="3">
         <v>99300</v>
@@ -3818,25 +3818,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>1289600</v>
+        <v>1298400</v>
       </c>
       <c r="E46" s="3">
-        <v>1347800</v>
+        <v>1356900</v>
       </c>
       <c r="F46" s="3">
-        <v>1450500</v>
+        <v>1460400</v>
       </c>
       <c r="G46" s="3">
-        <v>1443400</v>
+        <v>1453200</v>
       </c>
       <c r="H46" s="3">
-        <v>1633000</v>
+        <v>1644100</v>
       </c>
       <c r="I46" s="3">
-        <v>1620400</v>
+        <v>1631500</v>
       </c>
       <c r="J46" s="3">
-        <v>1604800</v>
+        <v>1615700</v>
       </c>
       <c r="K46" s="3">
         <v>1641800</v>
@@ -3910,25 +3910,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>410600</v>
+        <v>413400</v>
       </c>
       <c r="E47" s="3">
-        <v>381200</v>
+        <v>383800</v>
       </c>
       <c r="F47" s="3">
-        <v>216000</v>
+        <v>217400</v>
       </c>
       <c r="G47" s="3">
-        <v>273200</v>
+        <v>275100</v>
       </c>
       <c r="H47" s="3">
-        <v>176300</v>
+        <v>177500</v>
       </c>
       <c r="I47" s="3">
-        <v>124200</v>
+        <v>125000</v>
       </c>
       <c r="J47" s="3">
-        <v>119400</v>
+        <v>120300</v>
       </c>
       <c r="K47" s="3">
         <v>83900</v>
@@ -4002,25 +4002,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>80600</v>
+        <v>81200</v>
       </c>
       <c r="E48" s="3">
-        <v>79300</v>
+        <v>79800</v>
       </c>
       <c r="F48" s="3">
-        <v>76900</v>
+        <v>77400</v>
       </c>
       <c r="G48" s="3">
-        <v>75400</v>
+        <v>75900</v>
       </c>
       <c r="H48" s="3">
-        <v>71600</v>
+        <v>72100</v>
       </c>
       <c r="I48" s="3">
-        <v>70300</v>
+        <v>70800</v>
       </c>
       <c r="J48" s="3">
-        <v>64100</v>
+        <v>64600</v>
       </c>
       <c r="K48" s="3">
         <v>65400</v>
@@ -4100,19 +4100,19 @@
         <v>6500</v>
       </c>
       <c r="F49" s="3">
-        <v>7200</v>
+        <v>7300</v>
       </c>
       <c r="G49" s="3">
         <v>8000</v>
       </c>
       <c r="H49" s="3">
-        <v>8700</v>
+        <v>8800</v>
       </c>
       <c r="I49" s="3">
         <v>10000</v>
       </c>
       <c r="J49" s="3">
-        <v>10900</v>
+        <v>11000</v>
       </c>
       <c r="K49" s="3">
         <v>11600</v>
@@ -4370,25 +4370,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>17000</v>
+        <v>17100</v>
       </c>
       <c r="E52" s="3">
-        <v>14600</v>
+        <v>14700</v>
       </c>
       <c r="F52" s="3">
-        <v>13000</v>
+        <v>13100</v>
       </c>
       <c r="G52" s="3">
-        <v>15300</v>
+        <v>15400</v>
       </c>
       <c r="H52" s="3">
-        <v>19000</v>
+        <v>19200</v>
       </c>
       <c r="I52" s="3">
-        <v>25800</v>
+        <v>25900</v>
       </c>
       <c r="J52" s="3">
-        <v>29400</v>
+        <v>29600</v>
       </c>
       <c r="K52" s="3">
         <v>23600</v>
@@ -4554,25 +4554,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1803300</v>
+        <v>1815600</v>
       </c>
       <c r="E54" s="3">
-        <v>1829300</v>
+        <v>1841800</v>
       </c>
       <c r="F54" s="3">
-        <v>1763700</v>
+        <v>1775700</v>
       </c>
       <c r="G54" s="3">
-        <v>1815300</v>
+        <v>1827700</v>
       </c>
       <c r="H54" s="3">
-        <v>1908700</v>
+        <v>1921600</v>
       </c>
       <c r="I54" s="3">
-        <v>1850600</v>
+        <v>1863200</v>
       </c>
       <c r="J54" s="3">
-        <v>1828600</v>
+        <v>1841100</v>
       </c>
       <c r="K54" s="3">
         <v>1826300</v>
@@ -4720,7 +4720,7 @@
         <v>7700</v>
       </c>
       <c r="F57" s="3">
-        <v>4000</v>
+        <v>4100</v>
       </c>
       <c r="G57" s="3">
         <v>3100</v>
@@ -4729,7 +4729,7 @@
         <v>2900</v>
       </c>
       <c r="I57" s="3">
-        <v>5100</v>
+        <v>5200</v>
       </c>
       <c r="J57" s="3">
         <v>1700</v>
@@ -4898,25 +4898,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>247400</v>
+        <v>249100</v>
       </c>
       <c r="E59" s="3">
-        <v>255200</v>
+        <v>256900</v>
       </c>
       <c r="F59" s="3">
-        <v>249900</v>
+        <v>251700</v>
       </c>
       <c r="G59" s="3">
-        <v>300800</v>
+        <v>302900</v>
       </c>
       <c r="H59" s="3">
-        <v>304600</v>
+        <v>306600</v>
       </c>
       <c r="I59" s="3">
-        <v>308700</v>
+        <v>310800</v>
       </c>
       <c r="J59" s="3">
-        <v>336700</v>
+        <v>339000</v>
       </c>
       <c r="K59" s="3">
         <v>353200</v>
@@ -4990,25 +4990,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>250100</v>
+        <v>251800</v>
       </c>
       <c r="E60" s="3">
-        <v>262800</v>
+        <v>264600</v>
       </c>
       <c r="F60" s="3">
-        <v>254000</v>
+        <v>255700</v>
       </c>
       <c r="G60" s="3">
-        <v>303900</v>
+        <v>306000</v>
       </c>
       <c r="H60" s="3">
-        <v>307400</v>
+        <v>309500</v>
       </c>
       <c r="I60" s="3">
-        <v>313800</v>
+        <v>316000</v>
       </c>
       <c r="J60" s="3">
-        <v>338400</v>
+        <v>340700</v>
       </c>
       <c r="K60" s="3">
         <v>354900</v>
@@ -5180,19 +5180,19 @@
         <v>12000</v>
       </c>
       <c r="F62" s="3">
-        <v>13400</v>
+        <v>13500</v>
       </c>
       <c r="G62" s="3">
-        <v>14200</v>
+        <v>14300</v>
       </c>
       <c r="H62" s="3">
-        <v>16900</v>
+        <v>17000</v>
       </c>
       <c r="I62" s="3">
-        <v>19800</v>
+        <v>19900</v>
       </c>
       <c r="J62" s="3">
-        <v>23500</v>
+        <v>23700</v>
       </c>
       <c r="K62" s="3">
         <v>23200</v>
@@ -5542,25 +5542,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>261100</v>
+        <v>262900</v>
       </c>
       <c r="E66" s="3">
-        <v>274800</v>
+        <v>276600</v>
       </c>
       <c r="F66" s="3">
-        <v>267400</v>
+        <v>269200</v>
       </c>
       <c r="G66" s="3">
-        <v>318100</v>
+        <v>320300</v>
       </c>
       <c r="H66" s="3">
-        <v>324300</v>
+        <v>326500</v>
       </c>
       <c r="I66" s="3">
-        <v>333600</v>
+        <v>335900</v>
       </c>
       <c r="J66" s="3">
-        <v>361900</v>
+        <v>364300</v>
       </c>
       <c r="K66" s="3">
         <v>378200</v>
@@ -6036,25 +6036,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-218800</v>
+        <v>-220200</v>
       </c>
       <c r="E72" s="3">
-        <v>-220400</v>
+        <v>-221900</v>
       </c>
       <c r="F72" s="3">
-        <v>-223600</v>
+        <v>-225100</v>
       </c>
       <c r="G72" s="3">
-        <v>-229800</v>
+        <v>-231400</v>
       </c>
       <c r="H72" s="3">
-        <v>-157400</v>
+        <v>-158500</v>
       </c>
       <c r="I72" s="3">
-        <v>-165800</v>
+        <v>-166900</v>
       </c>
       <c r="J72" s="3">
-        <v>-163100</v>
+        <v>-164200</v>
       </c>
       <c r="K72" s="3">
         <v>-162300</v>
@@ -6404,25 +6404,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>1542200</v>
+        <v>1552700</v>
       </c>
       <c r="E76" s="3">
-        <v>1554600</v>
+        <v>1565200</v>
       </c>
       <c r="F76" s="3">
-        <v>1496300</v>
+        <v>1506500</v>
       </c>
       <c r="G76" s="3">
-        <v>1497300</v>
+        <v>1507400</v>
       </c>
       <c r="H76" s="3">
-        <v>1584300</v>
+        <v>1595100</v>
       </c>
       <c r="I76" s="3">
-        <v>1517000</v>
+        <v>1527300</v>
       </c>
       <c r="J76" s="3">
-        <v>1466700</v>
+        <v>1476700</v>
       </c>
       <c r="K76" s="3">
         <v>1448100</v>
@@ -6694,10 +6694,10 @@
         <v>6200</v>
       </c>
       <c r="G81" s="3">
-        <v>-72400</v>
+        <v>-72900</v>
       </c>
       <c r="H81" s="3">
-        <v>8300</v>
+        <v>8400</v>
       </c>
       <c r="I81" s="3">
         <v>-2700</v>

--- a/AAII_Financials/Quarterly/HUYA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HUYA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="92">
   <si>
     <t>HUYA</t>
   </si>
@@ -656,416 +656,441 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>229100</v>
+        <v>207800</v>
       </c>
       <c r="E8" s="3">
-        <v>253200</v>
+        <v>217700</v>
       </c>
       <c r="F8" s="3">
-        <v>271000</v>
+        <v>227700</v>
       </c>
       <c r="G8" s="3">
-        <v>292200</v>
+        <v>251600</v>
       </c>
       <c r="H8" s="3">
-        <v>330700</v>
+        <v>271100</v>
       </c>
       <c r="I8" s="3">
+        <v>296500</v>
+      </c>
+      <c r="J8" s="3">
+        <v>328600</v>
+      </c>
+      <c r="K8" s="3">
         <v>316300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>342600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>387000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>423000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>425500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>374100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>416200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>414800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>397500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>380500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>379900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>353400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>307200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>249300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>218600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>178700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>149000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>121000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>110000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>86600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>68500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>58000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>49300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>28600</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>197300</v>
+        <v>177300</v>
       </c>
       <c r="E9" s="3">
-        <v>215300</v>
+        <v>209800</v>
       </c>
       <c r="F9" s="3">
-        <v>235300</v>
+        <v>196100</v>
       </c>
       <c r="G9" s="3">
-        <v>331800</v>
+        <v>213900</v>
       </c>
       <c r="H9" s="3">
-        <v>283100</v>
+        <v>234000</v>
       </c>
       <c r="I9" s="3">
+        <v>329900</v>
+      </c>
+      <c r="J9" s="3">
+        <v>281300</v>
+      </c>
+      <c r="K9" s="3">
         <v>285800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>296200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>386800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>351300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>342000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>300300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>333100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>323300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>312700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>305600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>308100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>290000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>255900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>207500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>183900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>151600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>125100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>102200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>93900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>75700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>59900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>55700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>56300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>40700</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>31700</v>
+        <v>30500</v>
       </c>
       <c r="E10" s="3">
-        <v>38000</v>
+        <v>7900</v>
       </c>
       <c r="F10" s="3">
-        <v>35600</v>
+        <v>31500</v>
       </c>
       <c r="G10" s="3">
-        <v>-39500</v>
+        <v>37700</v>
       </c>
       <c r="H10" s="3">
-        <v>47600</v>
+        <v>37200</v>
       </c>
       <c r="I10" s="3">
+        <v>-33400</v>
+      </c>
+      <c r="J10" s="3">
+        <v>47300</v>
+      </c>
+      <c r="K10" s="3">
         <v>30500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>46400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>71600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>83500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>73800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>83200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>91400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>84700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>74900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>71800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>63400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>51300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>41800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>34700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>27100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>23900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>18800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>16000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>10900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>8500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>2300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>-7000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>-12000</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1098,100 +1123,108 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>19700</v>
+        <v>18700</v>
       </c>
       <c r="E12" s="3">
-        <v>20100</v>
+        <v>19300</v>
       </c>
       <c r="F12" s="3">
+        <v>19600</v>
+      </c>
+      <c r="G12" s="3">
+        <v>19900</v>
+      </c>
+      <c r="H12" s="3">
         <v>21200</v>
       </c>
-      <c r="G12" s="3">
-        <v>20000</v>
-      </c>
-      <c r="H12" s="3">
-        <v>23900</v>
-      </c>
       <c r="I12" s="3">
+        <v>20400</v>
+      </c>
+      <c r="J12" s="3">
+        <v>23700</v>
+      </c>
+      <c r="K12" s="3">
         <v>23400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>27300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>28300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>29300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>29900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>28600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>30000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>26900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>26500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>24600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>27500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>21100</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>16100</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>13800</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>11500</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>10400</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>8600</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>7400</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AC12" s="3">
         <v>6500</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AD12" s="3">
         <v>7300</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AE12" s="3">
         <v>5200</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AF12" s="3">
         <v>6200</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AG12" s="3">
         <v>7700</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AH12" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1282,28 +1315,34 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>11000</v>
+      </c>
+      <c r="F14" s="3">
         <v>11200</v>
       </c>
-      <c r="E14" s="3">
-        <v>9100</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
       <c r="G14" s="3">
-        <v>7700</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>16</v>
+        <v>9000</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
+        <v>12400</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>16</v>
@@ -1314,11 +1353,11 @@
       <c r="L14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
@@ -1374,8 +1413,14 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1466,8 +1511,14 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,192 +1548,206 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>244300</v>
+        <v>213100</v>
       </c>
       <c r="E17" s="3">
-        <v>266300</v>
+        <v>275100</v>
       </c>
       <c r="F17" s="3">
-        <v>278000</v>
+        <v>242800</v>
       </c>
       <c r="G17" s="3">
-        <v>380100</v>
+        <v>264600</v>
       </c>
       <c r="H17" s="3">
-        <v>329100</v>
+        <v>279000</v>
       </c>
       <c r="I17" s="3">
+        <v>392700</v>
+      </c>
+      <c r="J17" s="3">
+        <v>327000</v>
+      </c>
+      <c r="K17" s="3">
         <v>327600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>351000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>450000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>411200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>399300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>350800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>390200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>381900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>370700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>359500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>364300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>343400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>296800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>244900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>215900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>179100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>151500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>117000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>110200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>91700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>71000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>64100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>69400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>53400</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>-15200</v>
+        <v>-5300</v>
       </c>
       <c r="E18" s="3">
-        <v>-13100</v>
+        <v>-57400</v>
       </c>
       <c r="F18" s="3">
-        <v>-7100</v>
+        <v>-15100</v>
       </c>
       <c r="G18" s="3">
-        <v>-87800</v>
+        <v>-13000</v>
       </c>
       <c r="H18" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-96200</v>
+      </c>
+      <c r="J18" s="3">
         <v>1600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-11300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-8400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-63000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>11800</v>
-      </c>
-      <c r="M18" s="3">
-        <v>26100</v>
-      </c>
-      <c r="N18" s="3">
-        <v>23300</v>
       </c>
       <c r="O18" s="3">
         <v>26100</v>
       </c>
       <c r="P18" s="3">
+        <v>23300</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>26100</v>
+      </c>
+      <c r="R18" s="3">
         <v>32800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>26700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>21000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>15700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>10000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>10300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>4300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>2700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>4000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-5100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>-2500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>-6100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>-20100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>-24800</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1715,100 +1780,108 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>17600</v>
+        <v>15800</v>
       </c>
       <c r="E20" s="3">
-        <v>17100</v>
+        <v>18300</v>
       </c>
       <c r="F20" s="3">
-        <v>13500</v>
+        <v>17500</v>
       </c>
       <c r="G20" s="3">
+        <v>17000</v>
+      </c>
+      <c r="H20" s="3">
+        <v>13400</v>
+      </c>
+      <c r="I20" s="3">
+        <v>14600</v>
+      </c>
+      <c r="J20" s="3">
+        <v>9500</v>
+      </c>
+      <c r="K20" s="3">
+        <v>8700</v>
+      </c>
+      <c r="L20" s="3">
+        <v>9300</v>
+      </c>
+      <c r="M20" s="3">
+        <v>8500</v>
+      </c>
+      <c r="N20" s="3">
         <v>14700</v>
       </c>
-      <c r="H20" s="3">
-        <v>9500</v>
-      </c>
-      <c r="I20" s="3">
-        <v>8700</v>
-      </c>
-      <c r="J20" s="3">
-        <v>9300</v>
-      </c>
-      <c r="K20" s="3">
-        <v>8500</v>
-      </c>
-      <c r="L20" s="3">
-        <v>14700</v>
-      </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>8900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>9000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>10300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>11900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>11300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>12100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>13600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>13600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>11600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>8300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>7700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>7100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>-320100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>-200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>1000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>100</v>
       </c>
-      <c r="AF20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
@@ -1899,8 +1972,14 @@
       <c r="AF21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1991,100 +2070,112 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>2400</v>
+        <v>10500</v>
       </c>
       <c r="E23" s="3">
+        <v>-39100</v>
+      </c>
+      <c r="F23" s="3">
+        <v>2300</v>
+      </c>
+      <c r="G23" s="3">
         <v>4000</v>
       </c>
-      <c r="F23" s="3">
-        <v>6400</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-73200</v>
-      </c>
       <c r="H23" s="3">
-        <v>11100</v>
+        <v>5500</v>
       </c>
       <c r="I23" s="3">
+        <v>-81600</v>
+      </c>
+      <c r="J23" s="3">
+        <v>11000</v>
+      </c>
+      <c r="K23" s="3">
         <v>-2500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-54500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>26500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>35000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>32300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>36300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>44700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>38000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>33100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>29300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>23600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>21900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>12600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>10300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>6700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-322600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>3900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-4300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-2200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>-6100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>-20000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>-24800</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2092,77 +2183,77 @@
         <v>700</v>
       </c>
       <c r="E24" s="3">
+        <v>200</v>
+      </c>
+      <c r="F24" s="3">
+        <v>700</v>
+      </c>
+      <c r="G24" s="3">
         <v>800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
+        <v>-800</v>
+      </c>
+      <c r="J24" s="3">
+        <v>2700</v>
+      </c>
+      <c r="K24" s="3">
         <v>200</v>
       </c>
-      <c r="G24" s="3">
-        <v>-300</v>
-      </c>
-      <c r="H24" s="3">
-        <v>2700</v>
-      </c>
-      <c r="I24" s="3">
-        <v>200</v>
-      </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>1300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>-11400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>5800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>8400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>5700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>5200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>7500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>7600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>5900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>4200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>4300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>3300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>2900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>-4600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>-900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>-600</v>
       </c>
-      <c r="AA24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB24" s="3">
-        <v>0</v>
-      </c>
       <c r="AC24" s="3">
         <v>0</v>
       </c>
@@ -2175,8 +2266,14 @@
       <c r="AF24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2364,210 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-39300</v>
+      </c>
+      <c r="F26" s="3">
         <v>1700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>3200</v>
       </c>
-      <c r="F26" s="3">
-        <v>6200</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-72800</v>
-      </c>
       <c r="H26" s="3">
-        <v>8400</v>
+        <v>5500</v>
       </c>
       <c r="I26" s="3">
+        <v>-80800</v>
+      </c>
+      <c r="J26" s="3">
+        <v>8300</v>
+      </c>
+      <c r="K26" s="3">
         <v>-2700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-43100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>20700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>26700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>26700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>31200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>37300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>30500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>27200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>25000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>19200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>18600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>9700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>15000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>7900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-321700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>4500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-4300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-2200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>-6100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>-20000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>-24800</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-39300</v>
+      </c>
+      <c r="F27" s="3">
         <v>1700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>3200</v>
       </c>
-      <c r="F27" s="3">
-        <v>6200</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-72900</v>
-      </c>
       <c r="H27" s="3">
-        <v>8400</v>
+        <v>5500</v>
       </c>
       <c r="I27" s="3">
+        <v>-80900</v>
+      </c>
+      <c r="J27" s="3">
+        <v>8300</v>
+      </c>
+      <c r="K27" s="3">
         <v>-2700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-43100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>74500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>26700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>26600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>35200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>37300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>30500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>27000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>24600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>19200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>18600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>9700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>14500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>7900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-310800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-71200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-5800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-2200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>-6100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>-20000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>-24800</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2658,14 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2635,8 +2756,14 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2854,14 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,192 +2952,210 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-17600</v>
+        <v>-15800</v>
       </c>
       <c r="E32" s="3">
-        <v>-17100</v>
+        <v>-18300</v>
       </c>
       <c r="F32" s="3">
-        <v>-13500</v>
+        <v>-17500</v>
       </c>
       <c r="G32" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="H32" s="3">
+        <v>-13400</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-14600</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="K32" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="L32" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="M32" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="N32" s="3">
         <v>-14700</v>
       </c>
-      <c r="H32" s="3">
-        <v>-9500</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-8700</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-9300</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-8500</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-14700</v>
-      </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-8900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-9000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-10300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-11900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-11300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-12100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-13600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-13600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-11600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-8300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-7700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-7100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>320100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>-100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>-100</v>
       </c>
-      <c r="AF32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-39300</v>
+      </c>
+      <c r="F33" s="3">
         <v>1700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>3200</v>
       </c>
-      <c r="F33" s="3">
-        <v>6200</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-72900</v>
-      </c>
       <c r="H33" s="3">
-        <v>8400</v>
+        <v>5500</v>
       </c>
       <c r="I33" s="3">
+        <v>-80900</v>
+      </c>
+      <c r="J33" s="3">
+        <v>8300</v>
+      </c>
+      <c r="K33" s="3">
         <v>-2700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-43100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>74500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>26700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>26600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>35200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>37300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>30500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>27000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>24600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>19200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>18600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>9700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>14500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>7900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-310800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-71200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-5800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-2200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>-6100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>-20000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>-24800</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3246,215 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-39300</v>
+      </c>
+      <c r="F35" s="3">
         <v>1700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>3200</v>
       </c>
-      <c r="F35" s="3">
-        <v>6200</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-72900</v>
-      </c>
       <c r="H35" s="3">
-        <v>8400</v>
+        <v>5500</v>
       </c>
       <c r="I35" s="3">
+        <v>-80900</v>
+      </c>
+      <c r="J35" s="3">
+        <v>8300</v>
+      </c>
+      <c r="K35" s="3">
         <v>-2700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-43100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>74500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>26700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>26600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>35200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>37300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>30500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>27000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>24600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>19200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>18600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>9700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>14500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>7900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-310800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-71200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-5800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-2200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>-6100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>-20000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>-24800</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3487,10 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,86 +3523,88 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>114800</v>
+        <v>74900</v>
       </c>
       <c r="E41" s="3">
-        <v>96200</v>
+        <v>70700</v>
       </c>
       <c r="F41" s="3">
-        <v>269900</v>
+        <v>114100</v>
       </c>
       <c r="G41" s="3">
-        <v>91100</v>
+        <v>95600</v>
       </c>
       <c r="H41" s="3">
-        <v>150500</v>
+        <v>268200</v>
       </c>
       <c r="I41" s="3">
+        <v>95900</v>
+      </c>
+      <c r="J41" s="3">
+        <v>149600</v>
+      </c>
+      <c r="K41" s="3">
         <v>287500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>205800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1397500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>1437100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>1383600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>1370200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>1290200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>1341400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>1230000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>1243000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>1209800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>1322900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>1254600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>869400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>826800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>805000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>770000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>584200</v>
       </c>
-      <c r="AA41" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AB41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AC41" s="3" t="s">
         <v>16</v>
       </c>
@@ -3444,83 +3617,89 @@
       <c r="AF41" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG41" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH41" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>1064500</v>
+        <v>916700</v>
       </c>
       <c r="E42" s="3">
-        <v>1158100</v>
+        <v>946600</v>
       </c>
       <c r="F42" s="3">
-        <v>1088400</v>
+        <v>1057900</v>
       </c>
       <c r="G42" s="3">
-        <v>1254200</v>
+        <v>1151000</v>
       </c>
       <c r="H42" s="3">
-        <v>1330500</v>
+        <v>1081700</v>
       </c>
       <c r="I42" s="3">
+        <v>1246400</v>
+      </c>
+      <c r="J42" s="3">
+        <v>1322300</v>
+      </c>
+      <c r="K42" s="3">
         <v>1202300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>1250300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>112500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>143500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>158700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>159500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>168000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>249800</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>353400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>384600</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>341800</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>165000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>137700</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>97600</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>43600</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>17000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>21300</v>
       </c>
-      <c r="Z42" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AA42" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AB42" s="3" t="s">
         <v>16</v>
       </c>
@@ -3536,86 +3715,92 @@
       <c r="AF42" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH42" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>24100</v>
+        <v>32200</v>
       </c>
       <c r="E43" s="3">
-        <v>17200</v>
+        <v>29400</v>
       </c>
       <c r="F43" s="3">
-        <v>20600</v>
+        <v>24000</v>
       </c>
       <c r="G43" s="3">
+        <v>17100</v>
+      </c>
+      <c r="H43" s="3">
+        <v>20500</v>
+      </c>
+      <c r="I43" s="3">
+        <v>19900</v>
+      </c>
+      <c r="J43" s="3">
+        <v>21600</v>
+      </c>
+      <c r="K43" s="3">
+        <v>30400</v>
+      </c>
+      <c r="L43" s="3">
+        <v>30500</v>
+      </c>
+      <c r="M43" s="3">
+        <v>32600</v>
+      </c>
+      <c r="N43" s="3">
+        <v>40700</v>
+      </c>
+      <c r="O43" s="3">
+        <v>41000</v>
+      </c>
+      <c r="P43" s="3">
+        <v>33800</v>
+      </c>
+      <c r="Q43" s="3">
         <v>18900</v>
       </c>
-      <c r="H43" s="3">
-        <v>21700</v>
-      </c>
-      <c r="I43" s="3">
-        <v>30400</v>
-      </c>
-      <c r="J43" s="3">
-        <v>30500</v>
-      </c>
-      <c r="K43" s="3">
-        <v>32600</v>
-      </c>
-      <c r="L43" s="3">
-        <v>40700</v>
-      </c>
-      <c r="M43" s="3">
-        <v>41000</v>
-      </c>
-      <c r="N43" s="3">
-        <v>33800</v>
-      </c>
-      <c r="O43" s="3">
-        <v>18900</v>
-      </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>19000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>17100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>17600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>17500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>25700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>14600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>33500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>41100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>18500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>19900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>19800</v>
       </c>
-      <c r="AA43" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AB43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AC43" s="3" t="s">
         <v>16</v>
       </c>
@@ -3628,8 +3813,14 @@
       <c r="AF43" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH43" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3720,86 +3911,92 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>95000</v>
+        <v>91800</v>
       </c>
       <c r="E45" s="3">
-        <v>85400</v>
+        <v>79400</v>
       </c>
       <c r="F45" s="3">
-        <v>81500</v>
+        <v>94400</v>
       </c>
       <c r="G45" s="3">
-        <v>89200</v>
+        <v>84900</v>
       </c>
       <c r="H45" s="3">
-        <v>141300</v>
+        <v>81000</v>
       </c>
       <c r="I45" s="3">
+        <v>88600</v>
+      </c>
+      <c r="J45" s="3">
+        <v>140500</v>
+      </c>
+      <c r="K45" s="3">
         <v>111200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>129200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>99300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>133300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>107700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>94800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>91900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>71800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>61100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>63100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>61900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>68100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>46800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>35500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>46400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>32700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>24700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>12200</v>
       </c>
-      <c r="AA45" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AB45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AC45" s="3" t="s">
         <v>16</v>
       </c>
@@ -3812,86 +4009,92 @@
       <c r="AF45" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH45" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>1298400</v>
+        <v>1115600</v>
       </c>
       <c r="E46" s="3">
-        <v>1356900</v>
+        <v>1126100</v>
       </c>
       <c r="F46" s="3">
-        <v>1460400</v>
+        <v>1290400</v>
       </c>
       <c r="G46" s="3">
-        <v>1453200</v>
+        <v>1348600</v>
       </c>
       <c r="H46" s="3">
-        <v>1644100</v>
+        <v>1451400</v>
       </c>
       <c r="I46" s="3">
+        <v>1450800</v>
+      </c>
+      <c r="J46" s="3">
+        <v>1633900</v>
+      </c>
+      <c r="K46" s="3">
         <v>1631500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>1615700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>1641800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>1754600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>1690900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>1658300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>1568900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>1682100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>1661600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>1708300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>1630900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>1581700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>1453600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>1035900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>957800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>873300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>835800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>616200</v>
       </c>
-      <c r="AA46" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AB46" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AC46" s="3" t="s">
         <v>16</v>
       </c>
@@ -3904,86 +4107,92 @@
       <c r="AF46" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH46" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>413400</v>
+        <v>413800</v>
       </c>
       <c r="E47" s="3">
-        <v>383800</v>
+        <v>456600</v>
       </c>
       <c r="F47" s="3">
-        <v>217400</v>
+        <v>410800</v>
       </c>
       <c r="G47" s="3">
-        <v>275100</v>
+        <v>381400</v>
       </c>
       <c r="H47" s="3">
-        <v>177500</v>
+        <v>216100</v>
       </c>
       <c r="I47" s="3">
+        <v>273400</v>
+      </c>
+      <c r="J47" s="3">
+        <v>176400</v>
+      </c>
+      <c r="K47" s="3">
         <v>125000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>120300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>83900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>82800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>72500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>73200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>65000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>66400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>63400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>63500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>58400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>57400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>56200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>50200</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>31900</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>29800</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>30400</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>100</v>
       </c>
-      <c r="AA47" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AB47" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AC47" s="3" t="s">
         <v>16</v>
       </c>
@@ -3996,86 +4205,92 @@
       <c r="AF47" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH47" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>81200</v>
+        <v>103200</v>
       </c>
       <c r="E48" s="3">
-        <v>79800</v>
+        <v>97500</v>
       </c>
       <c r="F48" s="3">
-        <v>77400</v>
+        <v>80700</v>
       </c>
       <c r="G48" s="3">
-        <v>75900</v>
+        <v>79300</v>
       </c>
       <c r="H48" s="3">
-        <v>72100</v>
+        <v>77000</v>
       </c>
       <c r="I48" s="3">
+        <v>75400</v>
+      </c>
+      <c r="J48" s="3">
+        <v>71700</v>
+      </c>
+      <c r="K48" s="3">
         <v>70800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>64600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>65400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>69300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>26100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>23300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>25300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>30000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>30900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>29100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>30700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>33500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>33600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>28900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>12700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>11700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>10000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>5500</v>
       </c>
-      <c r="AA48" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AB48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AC48" s="3" t="s">
         <v>16</v>
       </c>
@@ -4088,61 +4303,67 @@
       <c r="AF48" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH48" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>84200</v>
+      </c>
+      <c r="E49" s="3">
+        <v>85500</v>
+      </c>
+      <c r="F49" s="3">
         <v>5500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>6500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
+        <v>7200</v>
+      </c>
+      <c r="I49" s="3">
+        <v>90700</v>
+      </c>
+      <c r="J49" s="3">
+        <v>8700</v>
+      </c>
+      <c r="K49" s="3">
+        <v>10000</v>
+      </c>
+      <c r="L49" s="3">
+        <v>11000</v>
+      </c>
+      <c r="M49" s="3">
+        <v>11600</v>
+      </c>
+      <c r="N49" s="3">
+        <v>12900</v>
+      </c>
+      <c r="O49" s="3">
+        <v>13600</v>
+      </c>
+      <c r="P49" s="3">
         <v>7300</v>
       </c>
-      <c r="G49" s="3">
-        <v>8000</v>
-      </c>
-      <c r="H49" s="3">
-        <v>8800</v>
-      </c>
-      <c r="I49" s="3">
-        <v>10000</v>
-      </c>
-      <c r="J49" s="3">
-        <v>11000</v>
-      </c>
-      <c r="K49" s="3">
-        <v>11600</v>
-      </c>
-      <c r="L49" s="3">
-        <v>12900</v>
-      </c>
-      <c r="M49" s="3">
-        <v>13600</v>
-      </c>
-      <c r="N49" s="3">
-        <v>7300</v>
-      </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>8700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>10700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>9700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>7000</v>
-      </c>
-      <c r="S49" s="3">
-        <v>6900</v>
-      </c>
-      <c r="T49" s="3">
-        <v>7400</v>
       </c>
       <c r="U49" s="3">
         <v>6900</v>
@@ -4151,23 +4372,23 @@
         <v>7400</v>
       </c>
       <c r="W49" s="3">
+        <v>6900</v>
+      </c>
+      <c r="X49" s="3">
+        <v>7400</v>
+      </c>
+      <c r="Y49" s="3">
         <v>7500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>7000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>5200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>800</v>
       </c>
-      <c r="AA49" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AB49" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AC49" s="3" t="s">
         <v>16</v>
       </c>
@@ -4180,8 +4401,14 @@
       <c r="AF49" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH49" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4499,14 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,86 +4597,92 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>17100</v>
+        <v>19900</v>
       </c>
       <c r="E52" s="3">
-        <v>14700</v>
+        <v>19900</v>
       </c>
       <c r="F52" s="3">
-        <v>13100</v>
+        <v>17000</v>
       </c>
       <c r="G52" s="3">
-        <v>15400</v>
+        <v>14600</v>
       </c>
       <c r="H52" s="3">
-        <v>19200</v>
+        <v>13000</v>
       </c>
       <c r="I52" s="3">
+        <v>15300</v>
+      </c>
+      <c r="J52" s="3">
+        <v>19100</v>
+      </c>
+      <c r="K52" s="3">
         <v>25900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>29600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>23600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>25200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>64800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>63900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>59500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>21700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>28900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>27700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>23200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>25400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>23300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>20600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>22000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>10500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>2200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>5400</v>
       </c>
-      <c r="AA52" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AB52" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AC52" s="3" t="s">
         <v>16</v>
       </c>
@@ -4456,8 +4695,14 @@
       <c r="AF52" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH52" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,86 +4793,92 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1815600</v>
+        <v>1736700</v>
       </c>
       <c r="E54" s="3">
-        <v>1841800</v>
+        <v>1785600</v>
       </c>
       <c r="F54" s="3">
-        <v>1775700</v>
+        <v>1804400</v>
       </c>
       <c r="G54" s="3">
-        <v>1827700</v>
+        <v>1830400</v>
       </c>
       <c r="H54" s="3">
-        <v>1921600</v>
+        <v>1764700</v>
       </c>
       <c r="I54" s="3">
+        <v>1905600</v>
+      </c>
+      <c r="J54" s="3">
+        <v>1909800</v>
+      </c>
+      <c r="K54" s="3">
         <v>1863200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>1841100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>1826300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>1944700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>1868000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>1826100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>1727600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>1810900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>1794500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>1835600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>1750200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>1705400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>1573700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>1143100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>1032000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>932300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>883600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>627900</v>
       </c>
-      <c r="AA54" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AB54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AC54" s="3" t="s">
         <v>16</v>
       </c>
@@ -4640,8 +4891,14 @@
       <c r="AF54" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG54" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH54" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4931,10 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,85 +4967,87 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E57" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F57" s="3">
         <v>2700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>7700</v>
       </c>
-      <c r="F57" s="3">
-        <v>4100</v>
-      </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
+        <v>4000</v>
+      </c>
+      <c r="I57" s="3">
         <v>3100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>2900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>5200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>1700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>1700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>2700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>8100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>1100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>1400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>2900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>5100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>1700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>2800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>3000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>1300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>2600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>1000</v>
       </c>
-      <c r="Z57" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA57" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AB57" s="3" t="s">
-        <v>16</v>
+      <c r="AB57" s="3">
+        <v>0</v>
       </c>
       <c r="AC57" s="3" t="s">
         <v>16</v>
@@ -4800,8 +5061,14 @@
       <c r="AF57" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH57" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4892,86 +5159,92 @@
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>249100</v>
+        <v>399700</v>
       </c>
       <c r="E59" s="3">
-        <v>256900</v>
+        <v>296600</v>
       </c>
       <c r="F59" s="3">
-        <v>251700</v>
+        <v>247500</v>
       </c>
       <c r="G59" s="3">
-        <v>302900</v>
+        <v>255300</v>
       </c>
       <c r="H59" s="3">
-        <v>306600</v>
+        <v>250100</v>
       </c>
       <c r="I59" s="3">
+        <v>308500</v>
+      </c>
+      <c r="J59" s="3">
+        <v>304700</v>
+      </c>
+      <c r="K59" s="3">
         <v>310800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>339000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>353200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>370200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>355100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>339900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>330600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>340500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>362100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>368100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>376200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>337600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>298300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>242600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>199100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>151400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>128700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>244600</v>
       </c>
-      <c r="AA59" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AB59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AC59" s="3" t="s">
         <v>16</v>
       </c>
@@ -4984,86 +5257,92 @@
       <c r="AF59" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH59" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>251800</v>
+        <v>404600</v>
       </c>
       <c r="E60" s="3">
-        <v>264600</v>
+        <v>298600</v>
       </c>
       <c r="F60" s="3">
-        <v>255700</v>
+        <v>250200</v>
       </c>
       <c r="G60" s="3">
-        <v>306000</v>
+        <v>263000</v>
       </c>
       <c r="H60" s="3">
-        <v>309500</v>
+        <v>254100</v>
       </c>
       <c r="I60" s="3">
+        <v>311700</v>
+      </c>
+      <c r="J60" s="3">
+        <v>307600</v>
+      </c>
+      <c r="K60" s="3">
         <v>316000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>340700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>354900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>372900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>363200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>341000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>332000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>343400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>367200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>368500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>376700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>339300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>301100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>245600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>200500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>154000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>129600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>244600</v>
       </c>
-      <c r="AA60" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AB60" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AC60" s="3" t="s">
         <v>16</v>
       </c>
@@ -5076,8 +5355,14 @@
       <c r="AF60" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH60" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5168,86 +5453,92 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>17200</v>
+      </c>
+      <c r="E62" s="3">
+        <v>19100</v>
+      </c>
+      <c r="F62" s="3">
         <v>11100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>12000</v>
       </c>
-      <c r="F62" s="3">
-        <v>13500</v>
-      </c>
-      <c r="G62" s="3">
-        <v>14300</v>
-      </c>
       <c r="H62" s="3">
-        <v>17000</v>
+        <v>13400</v>
       </c>
       <c r="I62" s="3">
+        <v>17700</v>
+      </c>
+      <c r="J62" s="3">
+        <v>16900</v>
+      </c>
+      <c r="K62" s="3">
         <v>19900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>23700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>23200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>28600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>34800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>35700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>34700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>35000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>37800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>38500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>36200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>35300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>33300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>27800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>11700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>9600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>10700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>7000</v>
       </c>
-      <c r="AA62" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AB62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AC62" s="3" t="s">
         <v>16</v>
       </c>
@@ -5260,8 +5551,14 @@
       <c r="AF62" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH62" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5649,14 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5747,14 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,86 +5845,92 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>262900</v>
+        <v>421800</v>
       </c>
       <c r="E66" s="3">
-        <v>276600</v>
+        <v>317700</v>
       </c>
       <c r="F66" s="3">
-        <v>269200</v>
+        <v>261300</v>
       </c>
       <c r="G66" s="3">
-        <v>320300</v>
+        <v>274900</v>
       </c>
       <c r="H66" s="3">
-        <v>326500</v>
+        <v>267500</v>
       </c>
       <c r="I66" s="3">
+        <v>329300</v>
+      </c>
+      <c r="J66" s="3">
+        <v>324500</v>
+      </c>
+      <c r="K66" s="3">
         <v>335900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>364300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>378200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>401500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>398000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>376600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>366600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>378400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>405000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>407000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>412900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>374500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>334300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>273300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>212200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>163700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>140300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>251600</v>
       </c>
-      <c r="AA66" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AB66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AC66" s="3" t="s">
         <v>16</v>
       </c>
@@ -5628,8 +5943,14 @@
       <c r="AF66" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG66" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH66" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5983,10 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +6077,14 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6175,14 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5918,14 +6253,14 @@
         <v>0</v>
       </c>
       <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB70" s="3">
         <v>434700</v>
       </c>
-      <c r="AA70" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB70" s="3">
-        <v>0</v>
-      </c>
       <c r="AC70" s="3">
         <v>0</v>
       </c>
@@ -5938,8 +6273,14 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,86 +6371,92 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-220200</v>
+        <v>-256800</v>
       </c>
       <c r="E72" s="3">
-        <v>-221900</v>
+        <v>-266600</v>
       </c>
       <c r="F72" s="3">
-        <v>-225100</v>
+        <v>-218900</v>
       </c>
       <c r="G72" s="3">
-        <v>-231400</v>
+        <v>-220600</v>
       </c>
       <c r="H72" s="3">
-        <v>-158500</v>
+        <v>-223800</v>
       </c>
       <c r="I72" s="3">
+        <v>-238400</v>
+      </c>
+      <c r="J72" s="3">
+        <v>-157500</v>
+      </c>
+      <c r="K72" s="3">
         <v>-166900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-164200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-162300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-123000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-199500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-226300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-245200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-296800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-224900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-276600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-295900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-324700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-336800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-355400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-347000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-348400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-365300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-59100</v>
       </c>
-      <c r="AA72" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AB72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AC72" s="3" t="s">
         <v>16</v>
       </c>
@@ -6122,8 +6469,14 @@
       <c r="AF72" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH72" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6567,14 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6665,14 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,86 +6763,92 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>1552700</v>
+        <v>1315000</v>
       </c>
       <c r="E76" s="3">
-        <v>1565200</v>
+        <v>1467900</v>
       </c>
       <c r="F76" s="3">
-        <v>1506500</v>
+        <v>1543100</v>
       </c>
       <c r="G76" s="3">
-        <v>1507400</v>
+        <v>1555500</v>
       </c>
       <c r="H76" s="3">
-        <v>1595100</v>
+        <v>1497200</v>
       </c>
       <c r="I76" s="3">
+        <v>1576300</v>
+      </c>
+      <c r="J76" s="3">
+        <v>1585200</v>
+      </c>
+      <c r="K76" s="3">
         <v>1527300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>1476700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>1448100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>1543200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>1470100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>1449400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>1360900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>1432500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>1389500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>1428600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>1337300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>1330900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>1239400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>869700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>819800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>768600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>743300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>-58300</v>
       </c>
-      <c r="AA76" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AB76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AC76" s="3" t="s">
         <v>16</v>
       </c>
@@ -6490,8 +6861,14 @@
       <c r="AF76" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG76" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH76" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6959,215 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-39300</v>
+      </c>
+      <c r="F81" s="3">
         <v>1700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>3200</v>
       </c>
-      <c r="F81" s="3">
-        <v>6200</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-72900</v>
-      </c>
       <c r="H81" s="3">
-        <v>8400</v>
+        <v>5500</v>
       </c>
       <c r="I81" s="3">
+        <v>-80900</v>
+      </c>
+      <c r="J81" s="3">
+        <v>8300</v>
+      </c>
+      <c r="K81" s="3">
         <v>-2700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-43100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>74500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>26700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>26600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>35200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>37300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>30500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>27000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>24600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>19200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>18600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>9700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>14500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>7900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-310800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-71200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-5800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-2200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>-6100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>-20000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>-24800</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,8 +7200,10 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6897,8 +7294,14 @@
       <c r="AF83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7392,14 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7490,14 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7588,14 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7686,14 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,8 +7784,14 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -7449,8 +7882,14 @@
       <c r="AF89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,8 +7922,10 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7575,8 +8016,14 @@
       <c r="AF91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +8114,14 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,8 +8212,14 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7851,8 +8310,14 @@
       <c r="AF94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8350,10 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7977,8 +8444,14 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8542,14 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8640,14 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,8 +8738,14 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8345,8 +8836,14 @@
       <c r="AF100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8437,8 +8934,14 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -8527,6 +9030,12 @@
         <v>0</v>
       </c>
       <c r="AF102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/HUYA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HUYA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="92">
   <si>
     <t>HUYA</t>
   </si>
@@ -656,441 +656,454 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>207800</v>
+        <v>217300</v>
       </c>
       <c r="E8" s="3">
-        <v>217700</v>
+        <v>212000</v>
       </c>
       <c r="F8" s="3">
-        <v>227700</v>
+        <v>222200</v>
       </c>
       <c r="G8" s="3">
-        <v>251600</v>
+        <v>232300</v>
       </c>
       <c r="H8" s="3">
-        <v>271100</v>
+        <v>259100</v>
       </c>
       <c r="I8" s="3">
-        <v>296500</v>
+        <v>276700</v>
       </c>
       <c r="J8" s="3">
+        <v>302600</v>
+      </c>
+      <c r="K8" s="3">
         <v>328600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>316300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>342600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>387000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>423000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>425500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>374100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>416200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>414800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>397500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>380500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>379900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>353400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>307200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>249300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>218600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>178700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>149000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>121000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>110000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>86600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>68500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>58000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>49300</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>28600</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>177300</v>
+        <v>187000</v>
       </c>
       <c r="E9" s="3">
-        <v>209800</v>
+        <v>180900</v>
       </c>
       <c r="F9" s="3">
-        <v>196100</v>
+        <v>214100</v>
       </c>
       <c r="G9" s="3">
-        <v>213900</v>
+        <v>200100</v>
       </c>
       <c r="H9" s="3">
-        <v>234000</v>
+        <v>218500</v>
       </c>
       <c r="I9" s="3">
-        <v>329900</v>
+        <v>238700</v>
       </c>
       <c r="J9" s="3">
+        <v>336600</v>
+      </c>
+      <c r="K9" s="3">
         <v>281300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>285800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>296200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>386800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>351300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>342000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>300300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>333100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>323300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>312700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>305600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>308100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>290000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>255900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>207500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>183900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>151600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>125100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>102200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>93900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>75700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>59900</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>55700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>56300</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>40700</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>30300</v>
+      </c>
+      <c r="E10" s="3">
+        <v>31100</v>
+      </c>
+      <c r="F10" s="3">
+        <v>8100</v>
+      </c>
+      <c r="G10" s="3">
+        <v>32200</v>
+      </c>
+      <c r="H10" s="3">
+        <v>40600</v>
+      </c>
+      <c r="I10" s="3">
+        <v>37900</v>
+      </c>
+      <c r="J10" s="3">
+        <v>-34000</v>
+      </c>
+      <c r="K10" s="3">
+        <v>47300</v>
+      </c>
+      <c r="L10" s="3">
         <v>30500</v>
       </c>
-      <c r="E10" s="3">
-        <v>7900</v>
-      </c>
-      <c r="F10" s="3">
-        <v>31500</v>
-      </c>
-      <c r="G10" s="3">
-        <v>37700</v>
-      </c>
-      <c r="H10" s="3">
-        <v>37200</v>
-      </c>
-      <c r="I10" s="3">
-        <v>-33400</v>
-      </c>
-      <c r="J10" s="3">
-        <v>47300</v>
-      </c>
-      <c r="K10" s="3">
-        <v>30500</v>
-      </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>46400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>71600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>83500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>73800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>83200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>91400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>84700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>74900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>71800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>63400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>51300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>41800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>34700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>27100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>23900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>18800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>16000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>10900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>8500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>2300</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>-7000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>-12000</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1125,106 +1138,110 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>18700</v>
+        <v>18100</v>
       </c>
       <c r="E12" s="3">
-        <v>19300</v>
+        <v>19000</v>
       </c>
       <c r="F12" s="3">
-        <v>19600</v>
+        <v>19700</v>
       </c>
       <c r="G12" s="3">
-        <v>19900</v>
+        <v>20000</v>
       </c>
       <c r="H12" s="3">
-        <v>21200</v>
+        <v>20500</v>
       </c>
       <c r="I12" s="3">
-        <v>20400</v>
+        <v>21600</v>
       </c>
       <c r="J12" s="3">
+        <v>20900</v>
+      </c>
+      <c r="K12" s="3">
         <v>23700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>23400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>27300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>28300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>29300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>29900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>28600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>30000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>26900</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>26500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>24600</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>27500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>21100</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>16100</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>13800</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>11500</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>10400</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>8600</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>7400</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>6500</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>7300</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>5200</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>6200</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>7700</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1321,31 +1338,34 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>6400</v>
       </c>
       <c r="E14" s="3">
-        <v>11000</v>
+        <v>0</v>
       </c>
       <c r="F14" s="3">
-        <v>11200</v>
+        <v>11300</v>
       </c>
       <c r="G14" s="3">
-        <v>9000</v>
+        <v>11400</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="I14" s="3">
-        <v>12400</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>16</v>
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
+        <v>12700</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>16</v>
@@ -1359,8 +1379,8 @@
       <c r="N14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1419,8 +1439,11 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1517,8 +1540,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,204 +1576,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>213100</v>
+        <v>227400</v>
       </c>
       <c r="E17" s="3">
-        <v>275100</v>
+        <v>217500</v>
       </c>
       <c r="F17" s="3">
-        <v>242800</v>
+        <v>280700</v>
       </c>
       <c r="G17" s="3">
-        <v>264600</v>
+        <v>247700</v>
       </c>
       <c r="H17" s="3">
-        <v>279000</v>
+        <v>264100</v>
       </c>
       <c r="I17" s="3">
-        <v>392700</v>
+        <v>284700</v>
       </c>
       <c r="J17" s="3">
+        <v>400700</v>
+      </c>
+      <c r="K17" s="3">
         <v>327000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>327600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>351000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>450000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>411200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>399300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>350800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>390200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>381900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>370700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>359500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>364300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>343400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>296800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>244900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>215900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>179100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>151500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>117000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>110200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>91700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>71000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>64100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>69400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>53400</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>-5300</v>
+        <v>-10000</v>
       </c>
       <c r="E18" s="3">
-        <v>-57400</v>
+        <v>-5400</v>
       </c>
       <c r="F18" s="3">
-        <v>-15100</v>
+        <v>-58500</v>
       </c>
       <c r="G18" s="3">
-        <v>-13000</v>
+        <v>-15400</v>
       </c>
       <c r="H18" s="3">
-        <v>-7800</v>
+        <v>-5000</v>
       </c>
       <c r="I18" s="3">
-        <v>-96200</v>
+        <v>-8000</v>
       </c>
       <c r="J18" s="3">
+        <v>-98200</v>
+      </c>
+      <c r="K18" s="3">
         <v>1600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-11300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-8400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-63000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>11800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>26100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>23300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>26100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>32800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>26700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>21000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>15700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>10000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>10300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>4300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>2700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-2500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>4000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-5100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-2500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-6100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-20100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-24800</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1782,106 +1815,110 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>15800</v>
+        <v>14500</v>
       </c>
       <c r="E20" s="3">
-        <v>18300</v>
+        <v>16200</v>
       </c>
       <c r="F20" s="3">
-        <v>17500</v>
+        <v>18600</v>
       </c>
       <c r="G20" s="3">
-        <v>17000</v>
+        <v>17800</v>
       </c>
       <c r="H20" s="3">
-        <v>13400</v>
+        <v>8500</v>
       </c>
       <c r="I20" s="3">
-        <v>14600</v>
+        <v>13600</v>
       </c>
       <c r="J20" s="3">
+        <v>14900</v>
+      </c>
+      <c r="K20" s="3">
         <v>9500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>8700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>9300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>8500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>14700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>8900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>9000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>10300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>11900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>11300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>12100</v>
-      </c>
-      <c r="U20" s="3">
-        <v>13600</v>
       </c>
       <c r="V20" s="3">
         <v>13600</v>
       </c>
       <c r="W20" s="3">
+        <v>13600</v>
+      </c>
+      <c r="X20" s="3">
         <v>11600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>8300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>7700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>7100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-320100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>1000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>300</v>
-      </c>
-      <c r="AF20" s="3">
-        <v>100</v>
       </c>
       <c r="AG20" s="3">
         <v>100</v>
       </c>
       <c r="AH20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
@@ -1978,8 +2015,11 @@
       <c r="AH21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2076,187 +2116,193 @@
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>10500</v>
+        <v>4500</v>
       </c>
       <c r="E23" s="3">
-        <v>-39100</v>
+        <v>10700</v>
       </c>
       <c r="F23" s="3">
-        <v>2300</v>
+        <v>-39900</v>
       </c>
       <c r="G23" s="3">
-        <v>4000</v>
+        <v>2400</v>
       </c>
       <c r="H23" s="3">
-        <v>5500</v>
+        <v>3500</v>
       </c>
       <c r="I23" s="3">
-        <v>-81600</v>
+        <v>5600</v>
       </c>
       <c r="J23" s="3">
+        <v>-83300</v>
+      </c>
+      <c r="K23" s="3">
         <v>11000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-2500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-54500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>26500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>35000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>32300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>36300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>44700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>38000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>33100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>29300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>23600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>21900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>12600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>10300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>6700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-322600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>3900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-4300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-2200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-6100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-20000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-24800</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>300</v>
+      </c>
+      <c r="E24" s="3">
         <v>700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>700</v>
       </c>
-      <c r="G24" s="3">
-        <v>800</v>
-      </c>
       <c r="H24" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
         <v>-800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-11400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>5800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>8400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>5700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>5200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>7500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>7600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>5900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>4200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>4300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>3300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>2900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-4600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-600</v>
       </c>
-      <c r="AC24" s="3">
-        <v>0</v>
-      </c>
       <c r="AD24" s="3">
         <v>0</v>
       </c>
@@ -2272,8 +2318,11 @@
       <c r="AH24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,204 +2419,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>9800</v>
+        <v>4200</v>
       </c>
       <c r="E26" s="3">
-        <v>-39300</v>
+        <v>10000</v>
       </c>
       <c r="F26" s="3">
+        <v>-40100</v>
+      </c>
+      <c r="G26" s="3">
         <v>1700</v>
       </c>
-      <c r="G26" s="3">
-        <v>3200</v>
-      </c>
       <c r="H26" s="3">
-        <v>5500</v>
+        <v>2900</v>
       </c>
       <c r="I26" s="3">
-        <v>-80800</v>
+        <v>5600</v>
       </c>
       <c r="J26" s="3">
+        <v>-82500</v>
+      </c>
+      <c r="K26" s="3">
         <v>8300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-2700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-43100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>20700</v>
-      </c>
-      <c r="O26" s="3">
-        <v>26700</v>
       </c>
       <c r="P26" s="3">
         <v>26700</v>
       </c>
       <c r="Q26" s="3">
+        <v>26700</v>
+      </c>
+      <c r="R26" s="3">
         <v>31200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>37300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>30500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>27200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>25000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>19200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>18600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>9700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>15000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>7900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-321700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>4500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-4300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-2200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-6100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-20000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-24800</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>9800</v>
+        <v>4200</v>
       </c>
       <c r="E27" s="3">
-        <v>-39300</v>
+        <v>10000</v>
       </c>
       <c r="F27" s="3">
+        <v>-40100</v>
+      </c>
+      <c r="G27" s="3">
         <v>1700</v>
       </c>
-      <c r="G27" s="3">
-        <v>3200</v>
-      </c>
       <c r="H27" s="3">
-        <v>5500</v>
+        <v>2900</v>
       </c>
       <c r="I27" s="3">
-        <v>-80900</v>
+        <v>5600</v>
       </c>
       <c r="J27" s="3">
+        <v>-82500</v>
+      </c>
+      <c r="K27" s="3">
         <v>8300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-2700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-43100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>74500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>26700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>26600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>35200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>37300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>30500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>27000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>24600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>19200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>18600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>9700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>14500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>7900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-310800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-71200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-5800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-2200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-6100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-20000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-24800</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2762,8 +2823,11 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,204 +3025,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-15800</v>
+        <v>-14500</v>
       </c>
       <c r="E32" s="3">
-        <v>-18300</v>
+        <v>-16200</v>
       </c>
       <c r="F32" s="3">
-        <v>-17500</v>
+        <v>-18600</v>
       </c>
       <c r="G32" s="3">
-        <v>-17000</v>
+        <v>-17800</v>
       </c>
       <c r="H32" s="3">
-        <v>-13400</v>
+        <v>-8500</v>
       </c>
       <c r="I32" s="3">
-        <v>-14600</v>
+        <v>-13600</v>
       </c>
       <c r="J32" s="3">
+        <v>-14900</v>
+      </c>
+      <c r="K32" s="3">
         <v>-9500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-8700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-9300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-8500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-14700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-8900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-9000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-10300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-11900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-11300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-12100</v>
-      </c>
-      <c r="U32" s="3">
-        <v>-13600</v>
       </c>
       <c r="V32" s="3">
         <v>-13600</v>
       </c>
       <c r="W32" s="3">
+        <v>-13600</v>
+      </c>
+      <c r="X32" s="3">
         <v>-11600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-8300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-7700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-7100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>320100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-300</v>
-      </c>
-      <c r="AF32" s="3">
-        <v>-100</v>
       </c>
       <c r="AG32" s="3">
         <v>-100</v>
       </c>
       <c r="AH32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+        <v>-100</v>
+      </c>
+      <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>9800</v>
+        <v>4200</v>
       </c>
       <c r="E33" s="3">
-        <v>-39300</v>
+        <v>10000</v>
       </c>
       <c r="F33" s="3">
+        <v>-40100</v>
+      </c>
+      <c r="G33" s="3">
         <v>1700</v>
       </c>
-      <c r="G33" s="3">
-        <v>3200</v>
-      </c>
       <c r="H33" s="3">
-        <v>5500</v>
+        <v>2900</v>
       </c>
       <c r="I33" s="3">
-        <v>-80900</v>
+        <v>5600</v>
       </c>
       <c r="J33" s="3">
+        <v>-82500</v>
+      </c>
+      <c r="K33" s="3">
         <v>8300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-2700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-43100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>74500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>26700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>26600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>35200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>37300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>30500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>27000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>24600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>19200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>18600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>9700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>14500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>7900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-310800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-71200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-5800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-2200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-6100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-20000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-24800</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,209 +3328,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>9800</v>
+        <v>4200</v>
       </c>
       <c r="E35" s="3">
-        <v>-39300</v>
+        <v>10000</v>
       </c>
       <c r="F35" s="3">
+        <v>-40100</v>
+      </c>
+      <c r="G35" s="3">
         <v>1700</v>
       </c>
-      <c r="G35" s="3">
-        <v>3200</v>
-      </c>
       <c r="H35" s="3">
-        <v>5500</v>
+        <v>2900</v>
       </c>
       <c r="I35" s="3">
-        <v>-80900</v>
+        <v>5600</v>
       </c>
       <c r="J35" s="3">
+        <v>-82500</v>
+      </c>
+      <c r="K35" s="3">
         <v>8300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-2700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-43100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>74500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>26700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>26600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>35200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>37300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>30500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>27000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>24600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>19200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>18600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>9700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>14500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>7900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-310800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-71200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-5800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-2200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-6100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-20000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-24800</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,89 +3611,90 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>74900</v>
+        <v>141800</v>
       </c>
       <c r="E41" s="3">
-        <v>70700</v>
+        <v>76400</v>
       </c>
       <c r="F41" s="3">
-        <v>114100</v>
+        <v>72200</v>
       </c>
       <c r="G41" s="3">
-        <v>95600</v>
+        <v>116400</v>
       </c>
       <c r="H41" s="3">
-        <v>268200</v>
+        <v>97600</v>
       </c>
       <c r="I41" s="3">
-        <v>95900</v>
+        <v>273700</v>
       </c>
       <c r="J41" s="3">
+        <v>97900</v>
+      </c>
+      <c r="K41" s="3">
         <v>149600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>287500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>205800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1397500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1437100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1383600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1370200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1290200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1341400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1230000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1243000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1209800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1322900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1254600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>869400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>826800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>805000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>770000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>584200</v>
       </c>
-      <c r="AC41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD41" s="3" t="s">
         <v>16</v>
       </c>
@@ -3623,86 +3710,89 @@
       <c r="AH41" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI41" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>916700</v>
+        <v>786400</v>
       </c>
       <c r="E42" s="3">
-        <v>946600</v>
+        <v>935400</v>
       </c>
       <c r="F42" s="3">
-        <v>1057900</v>
+        <v>965900</v>
       </c>
       <c r="G42" s="3">
-        <v>1151000</v>
+        <v>1079500</v>
       </c>
       <c r="H42" s="3">
-        <v>1081700</v>
+        <v>1174400</v>
       </c>
       <c r="I42" s="3">
-        <v>1246400</v>
+        <v>1103800</v>
       </c>
       <c r="J42" s="3">
+        <v>1271800</v>
+      </c>
+      <c r="K42" s="3">
         <v>1322300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1202300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1250300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>112500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>143500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>158700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>159500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>168000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>249800</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>353400</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>384600</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>341800</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>165000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>137700</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>97600</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>43600</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>17000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>21300</v>
       </c>
-      <c r="AB42" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AC42" s="3" t="s">
         <v>16</v>
       </c>
@@ -3721,89 +3811,92 @@
       <c r="AH42" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>32200</v>
+        <v>52400</v>
       </c>
       <c r="E43" s="3">
-        <v>29400</v>
+        <v>32900</v>
       </c>
       <c r="F43" s="3">
-        <v>24000</v>
+        <v>30000</v>
       </c>
       <c r="G43" s="3">
+        <v>24500</v>
+      </c>
+      <c r="H43" s="3">
+        <v>17400</v>
+      </c>
+      <c r="I43" s="3">
+        <v>20900</v>
+      </c>
+      <c r="J43" s="3">
+        <v>20300</v>
+      </c>
+      <c r="K43" s="3">
+        <v>21600</v>
+      </c>
+      <c r="L43" s="3">
+        <v>30400</v>
+      </c>
+      <c r="M43" s="3">
+        <v>30500</v>
+      </c>
+      <c r="N43" s="3">
+        <v>32600</v>
+      </c>
+      <c r="O43" s="3">
+        <v>40700</v>
+      </c>
+      <c r="P43" s="3">
+        <v>41000</v>
+      </c>
+      <c r="Q43" s="3">
+        <v>33800</v>
+      </c>
+      <c r="R43" s="3">
+        <v>18900</v>
+      </c>
+      <c r="S43" s="3">
+        <v>19000</v>
+      </c>
+      <c r="T43" s="3">
         <v>17100</v>
       </c>
-      <c r="H43" s="3">
-        <v>20500</v>
-      </c>
-      <c r="I43" s="3">
+      <c r="U43" s="3">
+        <v>17600</v>
+      </c>
+      <c r="V43" s="3">
+        <v>17500</v>
+      </c>
+      <c r="W43" s="3">
+        <v>25700</v>
+      </c>
+      <c r="X43" s="3">
+        <v>14600</v>
+      </c>
+      <c r="Y43" s="3">
+        <v>33500</v>
+      </c>
+      <c r="Z43" s="3">
+        <v>41100</v>
+      </c>
+      <c r="AA43" s="3">
+        <v>18500</v>
+      </c>
+      <c r="AB43" s="3">
         <v>19900</v>
       </c>
-      <c r="J43" s="3">
-        <v>21600</v>
-      </c>
-      <c r="K43" s="3">
-        <v>30400</v>
-      </c>
-      <c r="L43" s="3">
-        <v>30500</v>
-      </c>
-      <c r="M43" s="3">
-        <v>32600</v>
-      </c>
-      <c r="N43" s="3">
-        <v>40700</v>
-      </c>
-      <c r="O43" s="3">
-        <v>41000</v>
-      </c>
-      <c r="P43" s="3">
-        <v>33800</v>
-      </c>
-      <c r="Q43" s="3">
-        <v>18900</v>
-      </c>
-      <c r="R43" s="3">
-        <v>19000</v>
-      </c>
-      <c r="S43" s="3">
-        <v>17100</v>
-      </c>
-      <c r="T43" s="3">
-        <v>17600</v>
-      </c>
-      <c r="U43" s="3">
-        <v>17500</v>
-      </c>
-      <c r="V43" s="3">
-        <v>25700</v>
-      </c>
-      <c r="W43" s="3">
-        <v>14600</v>
-      </c>
-      <c r="X43" s="3">
-        <v>33500</v>
-      </c>
-      <c r="Y43" s="3">
-        <v>41100</v>
-      </c>
-      <c r="Z43" s="3">
-        <v>18500</v>
-      </c>
-      <c r="AA43" s="3">
-        <v>19900</v>
-      </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>19800</v>
       </c>
-      <c r="AC43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD43" s="3" t="s">
         <v>16</v>
       </c>
@@ -3819,8 +3912,11 @@
       <c r="AH43" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3917,89 +4013,92 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>91800</v>
+        <v>90400</v>
       </c>
       <c r="E45" s="3">
-        <v>79400</v>
+        <v>93700</v>
       </c>
       <c r="F45" s="3">
-        <v>94400</v>
+        <v>81000</v>
       </c>
       <c r="G45" s="3">
-        <v>84900</v>
+        <v>96300</v>
       </c>
       <c r="H45" s="3">
-        <v>81000</v>
+        <v>86600</v>
       </c>
       <c r="I45" s="3">
-        <v>88600</v>
+        <v>82700</v>
       </c>
       <c r="J45" s="3">
+        <v>90400</v>
+      </c>
+      <c r="K45" s="3">
         <v>140500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>111200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>129200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>99300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>133300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>107700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>94800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>91900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>71800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>61100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>63100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>61900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>68100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>46800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>35500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>46400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>32700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>24700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>12200</v>
       </c>
-      <c r="AC45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD45" s="3" t="s">
         <v>16</v>
       </c>
@@ -4015,89 +4114,92 @@
       <c r="AH45" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>1115600</v>
+        <v>1071000</v>
       </c>
       <c r="E46" s="3">
-        <v>1126100</v>
+        <v>1138400</v>
       </c>
       <c r="F46" s="3">
-        <v>1290400</v>
+        <v>1149100</v>
       </c>
       <c r="G46" s="3">
-        <v>1348600</v>
+        <v>1316700</v>
       </c>
       <c r="H46" s="3">
-        <v>1451400</v>
+        <v>1376100</v>
       </c>
       <c r="I46" s="3">
-        <v>1450800</v>
+        <v>1481000</v>
       </c>
       <c r="J46" s="3">
+        <v>1480400</v>
+      </c>
+      <c r="K46" s="3">
         <v>1633900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1631500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1615700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1641800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1754600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1690900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1658300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1568900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1682100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1661600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1708300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1630900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1581700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1453600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1035900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>957800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>873300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>835800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>616200</v>
       </c>
-      <c r="AC46" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD46" s="3" t="s">
         <v>16</v>
       </c>
@@ -4113,89 +4215,92 @@
       <c r="AH46" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI46" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>413800</v>
+        <v>317700</v>
       </c>
       <c r="E47" s="3">
-        <v>456600</v>
+        <v>422200</v>
       </c>
       <c r="F47" s="3">
-        <v>410800</v>
+        <v>466000</v>
       </c>
       <c r="G47" s="3">
-        <v>381400</v>
+        <v>419200</v>
       </c>
       <c r="H47" s="3">
-        <v>216100</v>
+        <v>389200</v>
       </c>
       <c r="I47" s="3">
-        <v>273400</v>
+        <v>220500</v>
       </c>
       <c r="J47" s="3">
+        <v>279000</v>
+      </c>
+      <c r="K47" s="3">
         <v>176400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>125000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>120300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>83900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>82800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>72500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>73200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>65000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>66400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>63400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>63500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>58400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>57400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>56200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>50200</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>31900</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>29800</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>30400</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>100</v>
       </c>
-      <c r="AC47" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD47" s="3" t="s">
         <v>16</v>
       </c>
@@ -4211,89 +4316,92 @@
       <c r="AH47" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>103200</v>
+        <v>108600</v>
       </c>
       <c r="E48" s="3">
-        <v>97500</v>
+        <v>105300</v>
       </c>
       <c r="F48" s="3">
-        <v>80700</v>
+        <v>99500</v>
       </c>
       <c r="G48" s="3">
-        <v>79300</v>
+        <v>82300</v>
       </c>
       <c r="H48" s="3">
+        <v>81000</v>
+      </c>
+      <c r="I48" s="3">
+        <v>78500</v>
+      </c>
+      <c r="J48" s="3">
         <v>77000</v>
       </c>
-      <c r="I48" s="3">
-        <v>75400</v>
-      </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>71700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>70800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>64600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>65400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>69300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>26100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>23300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>25300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>30000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>30900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>29100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>30700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>33500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>33600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>28900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>12700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>11700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>10000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>5500</v>
       </c>
-      <c r="AC48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD48" s="3" t="s">
         <v>16</v>
       </c>
@@ -4309,89 +4417,92 @@
       <c r="AH48" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI48" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>84200</v>
+        <v>85000</v>
       </c>
       <c r="E49" s="3">
-        <v>85500</v>
+        <v>86000</v>
       </c>
       <c r="F49" s="3">
-        <v>5500</v>
+        <v>87200</v>
       </c>
       <c r="G49" s="3">
-        <v>6500</v>
+        <v>5600</v>
       </c>
       <c r="H49" s="3">
-        <v>7200</v>
+        <v>6600</v>
       </c>
       <c r="I49" s="3">
-        <v>90700</v>
+        <v>7400</v>
       </c>
       <c r="J49" s="3">
+        <v>92500</v>
+      </c>
+      <c r="K49" s="3">
         <v>8700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>10000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>11000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>11600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>12900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>13600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>7300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>8700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>10700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>9700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>7000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>6900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>7400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>6900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>7400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>7500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>7000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>5200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>800</v>
       </c>
-      <c r="AC49" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD49" s="3" t="s">
         <v>16</v>
       </c>
@@ -4407,8 +4518,11 @@
       <c r="AH49" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,89 +4720,92 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>19900</v>
+        <v>17100</v>
       </c>
       <c r="E52" s="3">
-        <v>19900</v>
+        <v>20300</v>
       </c>
       <c r="F52" s="3">
-        <v>17000</v>
+        <v>20300</v>
       </c>
       <c r="G52" s="3">
-        <v>14600</v>
+        <v>17300</v>
       </c>
       <c r="H52" s="3">
-        <v>13000</v>
+        <v>14900</v>
       </c>
       <c r="I52" s="3">
-        <v>15300</v>
+        <v>13300</v>
       </c>
       <c r="J52" s="3">
+        <v>15600</v>
+      </c>
+      <c r="K52" s="3">
         <v>19100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>25900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>29600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>23600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>25200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>64800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>63900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>59500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>21700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>28900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>27700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>23200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>25400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>23300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>20600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>22000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>10500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>2200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>5400</v>
       </c>
-      <c r="AC52" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD52" s="3" t="s">
         <v>16</v>
       </c>
@@ -4701,8 +4821,11 @@
       <c r="AH52" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI52" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,89 +4922,92 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1736700</v>
+        <v>1599300</v>
       </c>
       <c r="E54" s="3">
-        <v>1785600</v>
+        <v>1772200</v>
       </c>
       <c r="F54" s="3">
-        <v>1804400</v>
+        <v>1822100</v>
       </c>
       <c r="G54" s="3">
-        <v>1830400</v>
+        <v>1841200</v>
       </c>
       <c r="H54" s="3">
-        <v>1764700</v>
+        <v>1867800</v>
       </c>
       <c r="I54" s="3">
-        <v>1905600</v>
+        <v>1800700</v>
       </c>
       <c r="J54" s="3">
+        <v>1944500</v>
+      </c>
+      <c r="K54" s="3">
         <v>1909800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1863200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1841100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1826300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1944700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1868000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1826100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1727600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1810900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1794500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1835600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1750200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1705400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1573700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1143100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1032000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>932300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>883600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>627900</v>
       </c>
-      <c r="AC54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD54" s="3" t="s">
         <v>16</v>
       </c>
@@ -4897,8 +5023,11 @@
       <c r="AH54" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI54" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,88 +5099,89 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>4900</v>
+        <v>2600</v>
       </c>
       <c r="E57" s="3">
+        <v>5000</v>
+      </c>
+      <c r="F57" s="3">
         <v>2100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2700</v>
       </c>
-      <c r="G57" s="3">
-        <v>7700</v>
-      </c>
       <c r="H57" s="3">
-        <v>4000</v>
+        <v>7800</v>
       </c>
       <c r="I57" s="3">
-        <v>3100</v>
+        <v>4100</v>
       </c>
       <c r="J57" s="3">
+        <v>3200</v>
+      </c>
+      <c r="K57" s="3">
         <v>2900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5200</v>
-      </c>
-      <c r="L57" s="3">
-        <v>1700</v>
       </c>
       <c r="M57" s="3">
         <v>1700</v>
       </c>
       <c r="N57" s="3">
+        <v>1700</v>
+      </c>
+      <c r="O57" s="3">
         <v>2700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>8100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>5100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>3000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1000</v>
       </c>
-      <c r="AB57" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC57" s="3" t="s">
-        <v>16</v>
+      <c r="AC57" s="3">
+        <v>0</v>
       </c>
       <c r="AD57" s="3" t="s">
         <v>16</v>
@@ -5067,8 +5198,11 @@
       <c r="AH57" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI57" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5165,89 +5299,92 @@
       <c r="AH58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>399700</v>
+        <v>248300</v>
       </c>
       <c r="E59" s="3">
-        <v>296600</v>
+        <v>407800</v>
       </c>
       <c r="F59" s="3">
-        <v>247500</v>
+        <v>302600</v>
       </c>
       <c r="G59" s="3">
-        <v>255300</v>
+        <v>252600</v>
       </c>
       <c r="H59" s="3">
-        <v>250100</v>
+        <v>260500</v>
       </c>
       <c r="I59" s="3">
-        <v>308500</v>
+        <v>255200</v>
       </c>
       <c r="J59" s="3">
+        <v>314800</v>
+      </c>
+      <c r="K59" s="3">
         <v>304700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>310800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>339000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>353200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>370200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>355100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>339900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>330600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>340500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>362100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>368100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>376200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>337600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>298300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>242600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>199100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>151400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>128700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>244600</v>
       </c>
-      <c r="AC59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD59" s="3" t="s">
         <v>16</v>
       </c>
@@ -5263,89 +5400,92 @@
       <c r="AH59" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI59" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>404600</v>
+        <v>250900</v>
       </c>
       <c r="E60" s="3">
-        <v>298600</v>
+        <v>412800</v>
       </c>
       <c r="F60" s="3">
-        <v>250200</v>
+        <v>304700</v>
       </c>
       <c r="G60" s="3">
-        <v>263000</v>
+        <v>255300</v>
       </c>
       <c r="H60" s="3">
-        <v>254100</v>
+        <v>268300</v>
       </c>
       <c r="I60" s="3">
-        <v>311700</v>
+        <v>259300</v>
       </c>
       <c r="J60" s="3">
+        <v>318000</v>
+      </c>
+      <c r="K60" s="3">
         <v>307600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>316000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>340700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>354900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>372900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>363200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>341000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>332000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>343400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>367200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>368500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>376700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>339300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>301100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>245600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>200500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>154000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>129600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>244600</v>
       </c>
-      <c r="AC60" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD60" s="3" t="s">
         <v>16</v>
       </c>
@@ -5361,8 +5501,11 @@
       <c r="AH60" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI60" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5459,89 +5602,92 @@
       <c r="AH61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>17200</v>
+        <v>14100</v>
       </c>
       <c r="E62" s="3">
-        <v>19100</v>
+        <v>17600</v>
       </c>
       <c r="F62" s="3">
-        <v>11100</v>
+        <v>19500</v>
       </c>
       <c r="G62" s="3">
-        <v>12000</v>
+        <v>11300</v>
       </c>
       <c r="H62" s="3">
-        <v>13400</v>
+        <v>12200</v>
       </c>
       <c r="I62" s="3">
-        <v>17700</v>
+        <v>13600</v>
       </c>
       <c r="J62" s="3">
+        <v>18000</v>
+      </c>
+      <c r="K62" s="3">
         <v>16900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>19900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>23700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>23200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>28600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>34800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>35700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>34700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>35000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>37800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>38500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>36200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>35300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>33300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>27800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>11700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>9600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>10700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>7000</v>
       </c>
-      <c r="AC62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD62" s="3" t="s">
         <v>16</v>
       </c>
@@ -5557,8 +5703,11 @@
       <c r="AH62" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI62" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,89 +6006,92 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>421800</v>
+        <v>265000</v>
       </c>
       <c r="E66" s="3">
-        <v>317700</v>
+        <v>430400</v>
       </c>
       <c r="F66" s="3">
-        <v>261300</v>
+        <v>324200</v>
       </c>
       <c r="G66" s="3">
-        <v>274900</v>
+        <v>266600</v>
       </c>
       <c r="H66" s="3">
-        <v>267500</v>
+        <v>280500</v>
       </c>
       <c r="I66" s="3">
-        <v>329300</v>
+        <v>273000</v>
       </c>
       <c r="J66" s="3">
+        <v>336000</v>
+      </c>
+      <c r="K66" s="3">
         <v>324500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>335900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>364300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>378200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>401500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>398000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>376600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>366600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>378400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>405000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>407000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>412900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>374500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>334300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>273300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>212200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>163700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>140300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>251600</v>
       </c>
-      <c r="AC66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD66" s="3" t="s">
         <v>16</v>
       </c>
@@ -5949,8 +6107,11 @@
       <c r="AH66" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI66" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6259,11 +6427,11 @@
         <v>0</v>
       </c>
       <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC70" s="3">
         <v>434700</v>
       </c>
-      <c r="AC70" s="3">
-        <v>0</v>
-      </c>
       <c r="AD70" s="3">
         <v>0</v>
       </c>
@@ -6279,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,89 +6548,92 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-256800</v>
+        <v>-257900</v>
       </c>
       <c r="E72" s="3">
-        <v>-266600</v>
+        <v>-262100</v>
       </c>
       <c r="F72" s="3">
-        <v>-218900</v>
+        <v>-272100</v>
       </c>
       <c r="G72" s="3">
-        <v>-220600</v>
+        <v>-223300</v>
       </c>
       <c r="H72" s="3">
-        <v>-223800</v>
+        <v>-225100</v>
       </c>
       <c r="I72" s="3">
-        <v>-238400</v>
+        <v>-228300</v>
       </c>
       <c r="J72" s="3">
+        <v>-243200</v>
+      </c>
+      <c r="K72" s="3">
         <v>-157500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-166900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-164200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-162300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-123000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-199500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-226300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-245200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-296800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-224900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-276600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-295900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-324700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-336800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-355400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-347000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-348400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-365300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-59100</v>
       </c>
-      <c r="AC72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD72" s="3" t="s">
         <v>16</v>
       </c>
@@ -6475,8 +6649,11 @@
       <c r="AH72" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI72" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,89 +6952,92 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>1315000</v>
+        <v>1334400</v>
       </c>
       <c r="E76" s="3">
-        <v>1467900</v>
+        <v>1341800</v>
       </c>
       <c r="F76" s="3">
-        <v>1543100</v>
+        <v>1497900</v>
       </c>
       <c r="G76" s="3">
-        <v>1555500</v>
+        <v>1574600</v>
       </c>
       <c r="H76" s="3">
-        <v>1497200</v>
+        <v>1587200</v>
       </c>
       <c r="I76" s="3">
-        <v>1576300</v>
+        <v>1527700</v>
       </c>
       <c r="J76" s="3">
+        <v>1608500</v>
+      </c>
+      <c r="K76" s="3">
         <v>1585200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1527300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1476700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1448100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1543200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1470100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1449400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1360900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1432500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1389500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1428600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1337300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1330900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1239400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>869700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>819800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>768600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>743300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>-58300</v>
       </c>
-      <c r="AC76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD76" s="3" t="s">
         <v>16</v>
       </c>
@@ -6867,8 +7053,11 @@
       <c r="AH76" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI76" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,209 +7154,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>9800</v>
+        <v>4200</v>
       </c>
       <c r="E81" s="3">
-        <v>-39300</v>
+        <v>10000</v>
       </c>
       <c r="F81" s="3">
+        <v>-40100</v>
+      </c>
+      <c r="G81" s="3">
         <v>1700</v>
       </c>
-      <c r="G81" s="3">
-        <v>3200</v>
-      </c>
       <c r="H81" s="3">
-        <v>5500</v>
+        <v>2900</v>
       </c>
       <c r="I81" s="3">
-        <v>-80900</v>
+        <v>5600</v>
       </c>
       <c r="J81" s="3">
+        <v>-82500</v>
+      </c>
+      <c r="K81" s="3">
         <v>8300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-2700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-43100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>74500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>26700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>26600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>35200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>37300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>30500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>27000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>24600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>19200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>18600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>9700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>14500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>7900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-310800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-71200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-5800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-2200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-6100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-20000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-24800</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,8 +7400,9 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7300,8 +7499,11 @@
       <c r="AH83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,8 +8004,11 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -7888,8 +8105,11 @@
       <c r="AH89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,8 +8144,9 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8022,8 +8243,11 @@
       <c r="AH91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,8 +8445,11 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8316,8 +8546,11 @@
       <c r="AH94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,8 +8585,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8450,8 +8684,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,8 +8987,11 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8842,8 +9088,11 @@
       <c r="AH100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8940,8 +9189,11 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -9036,6 +9288,9 @@
         <v>0</v>
       </c>
       <c r="AH102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/HUYA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HUYA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="92">
   <si>
     <t>HUYA</t>
   </si>
@@ -656,454 +656,467 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>217300</v>
+        <v>219200</v>
       </c>
       <c r="E8" s="3">
-        <v>212000</v>
+        <v>212100</v>
       </c>
       <c r="F8" s="3">
+        <v>208300</v>
+      </c>
+      <c r="G8" s="3">
         <v>222200</v>
       </c>
-      <c r="G8" s="3">
-        <v>232300</v>
-      </c>
       <c r="H8" s="3">
-        <v>259100</v>
+        <v>228100</v>
       </c>
       <c r="I8" s="3">
-        <v>276700</v>
+        <v>251200</v>
       </c>
       <c r="J8" s="3">
+        <v>285700</v>
+      </c>
+      <c r="K8" s="3">
         <v>302600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>328600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>316300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>342600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>387000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>423000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>425500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>374100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>416200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>414800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>397500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>380500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>379900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>353400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>307200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>249300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>218600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>178700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>149000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>121000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>110000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>86600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>68500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>58000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>49300</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>28600</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>187000</v>
+        <v>190200</v>
       </c>
       <c r="E9" s="3">
-        <v>180900</v>
+        <v>182600</v>
       </c>
       <c r="F9" s="3">
+        <v>177800</v>
+      </c>
+      <c r="G9" s="3">
         <v>214100</v>
       </c>
-      <c r="G9" s="3">
-        <v>200100</v>
-      </c>
       <c r="H9" s="3">
-        <v>218500</v>
+        <v>194800</v>
       </c>
       <c r="I9" s="3">
-        <v>238700</v>
+        <v>213500</v>
       </c>
       <c r="J9" s="3">
+        <v>246500</v>
+      </c>
+      <c r="K9" s="3">
         <v>336600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>281300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>285800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>296200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>386800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>351300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>342000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>300300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>333100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>323300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>312700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>305600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>308100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>290000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>255900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>207500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>183900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>151600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>125100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>102200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>93900</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>75700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>59900</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>55700</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>56300</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>40700</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>30300</v>
+        <v>29000</v>
       </c>
       <c r="E10" s="3">
-        <v>31100</v>
+        <v>29600</v>
       </c>
       <c r="F10" s="3">
+        <v>30500</v>
+      </c>
+      <c r="G10" s="3">
         <v>8100</v>
       </c>
-      <c r="G10" s="3">
-        <v>32200</v>
-      </c>
       <c r="H10" s="3">
-        <v>40600</v>
+        <v>33300</v>
       </c>
       <c r="I10" s="3">
-        <v>37900</v>
+        <v>37600</v>
       </c>
       <c r="J10" s="3">
+        <v>39200</v>
+      </c>
+      <c r="K10" s="3">
         <v>-34000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>47300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>30500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>46400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>71600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>83500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>73800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>83200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>91400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>84700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>74900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>71800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>63400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>51300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>41800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>34700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>27100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>23900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>18800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>16000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>10900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>8500</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>2300</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>-7000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>-12000</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1139,109 +1152,113 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>18100</v>
+        <v>17900</v>
       </c>
       <c r="E12" s="3">
-        <v>19000</v>
+        <v>17700</v>
       </c>
       <c r="F12" s="3">
-        <v>19700</v>
+        <v>18700</v>
       </c>
       <c r="G12" s="3">
-        <v>20000</v>
+        <v>15000</v>
       </c>
       <c r="H12" s="3">
-        <v>20500</v>
+        <v>19600</v>
       </c>
       <c r="I12" s="3">
-        <v>21600</v>
+        <v>19900</v>
       </c>
       <c r="J12" s="3">
+        <v>22300</v>
+      </c>
+      <c r="K12" s="3">
         <v>20900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>23700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>23400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>27300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>28300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>29300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>29900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>28600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>30000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>26900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>26500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>24600</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>27500</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>21100</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>16100</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>13800</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>11500</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>10400</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>8600</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>7400</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>6500</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>7300</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>5200</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>6200</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>7700</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1341,35 +1358,38 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>6400</v>
+        <v>5200</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>11300</v>
+        <v>6200</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="G14" s="3">
-        <v>11400</v>
+        <v>16100</v>
       </c>
       <c r="H14" s="3">
-        <v>300</v>
+        <v>11100</v>
       </c>
       <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
+        <v>9000</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K14" s="3">
         <v>12700</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>16</v>
       </c>
@@ -1382,8 +1402,8 @@
       <c r="O14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1442,31 +1462,34 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>3700</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1543,8 +1566,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,210 +1603,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>227400</v>
+        <v>223800</v>
       </c>
       <c r="E17" s="3">
-        <v>217500</v>
+        <v>215700</v>
       </c>
       <c r="F17" s="3">
-        <v>280700</v>
+        <v>213600</v>
       </c>
       <c r="G17" s="3">
-        <v>247700</v>
+        <v>264700</v>
       </c>
       <c r="H17" s="3">
-        <v>264100</v>
+        <v>232400</v>
       </c>
       <c r="I17" s="3">
-        <v>284700</v>
+        <v>255100</v>
       </c>
       <c r="J17" s="3">
+        <v>294000</v>
+      </c>
+      <c r="K17" s="3">
         <v>400700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>327000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>327600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>351000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>450000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>411200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>399300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>350800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>390200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>381900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>370700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>359500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>364300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>343400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>296800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>244900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>215900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>179100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>151500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>117000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>110200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>91700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>71000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>64100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>69400</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>53400</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>-10000</v>
+        <v>-4600</v>
       </c>
       <c r="E18" s="3">
-        <v>-5400</v>
+        <v>-3600</v>
       </c>
       <c r="F18" s="3">
-        <v>-58500</v>
+        <v>-5300</v>
       </c>
       <c r="G18" s="3">
-        <v>-15400</v>
+        <v>-42500</v>
       </c>
       <c r="H18" s="3">
-        <v>-5000</v>
+        <v>-4300</v>
       </c>
       <c r="I18" s="3">
-        <v>-8000</v>
+        <v>-4000</v>
       </c>
       <c r="J18" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="K18" s="3">
         <v>-98200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-11300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-8400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-63000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>11800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>26100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>23300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>26100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>32800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>26700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>21000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>15700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>10000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>10300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>4300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>2700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-2500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>4000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-5100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-2500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-6100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-20100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-24800</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1816,132 +1849,136 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>14500</v>
+        <v>200</v>
       </c>
       <c r="E20" s="3">
-        <v>16200</v>
+        <v>-100</v>
       </c>
       <c r="F20" s="3">
-        <v>18600</v>
+        <v>300</v>
       </c>
       <c r="G20" s="3">
-        <v>17800</v>
+        <v>-400</v>
       </c>
       <c r="H20" s="3">
+        <v>200</v>
+      </c>
+      <c r="I20" s="3">
+        <v>400</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K20" s="3">
+        <v>14900</v>
+      </c>
+      <c r="L20" s="3">
+        <v>9500</v>
+      </c>
+      <c r="M20" s="3">
+        <v>8700</v>
+      </c>
+      <c r="N20" s="3">
+        <v>9300</v>
+      </c>
+      <c r="O20" s="3">
         <v>8500</v>
       </c>
-      <c r="I20" s="3">
-        <v>13600</v>
-      </c>
-      <c r="J20" s="3">
-        <v>14900</v>
-      </c>
-      <c r="K20" s="3">
-        <v>9500</v>
-      </c>
-      <c r="L20" s="3">
-        <v>8700</v>
-      </c>
-      <c r="M20" s="3">
-        <v>9300</v>
-      </c>
-      <c r="N20" s="3">
-        <v>8500</v>
-      </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>14700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>8900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>9000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>10300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>11900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>11300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>12100</v>
-      </c>
-      <c r="V20" s="3">
-        <v>13600</v>
       </c>
       <c r="W20" s="3">
         <v>13600</v>
       </c>
       <c r="X20" s="3">
+        <v>13600</v>
+      </c>
+      <c r="Y20" s="3">
         <v>11600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>8300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>7700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>7100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-320100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>1000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>700</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>300</v>
-      </c>
-      <c r="AG20" s="3">
-        <v>100</v>
       </c>
       <c r="AH20" s="3">
         <v>100</v>
       </c>
       <c r="AI20" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ20" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>16</v>
+      <c r="D21" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-38600</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-4500</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>16</v>
@@ -2018,31 +2055,34 @@
       <c r="AI21" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AJ21" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -2119,193 +2159,199 @@
       <c r="AI22" s="3">
         <v>0</v>
       </c>
+      <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>4500</v>
+        <v>3800</v>
       </c>
       <c r="E23" s="3">
-        <v>10700</v>
+        <v>4400</v>
       </c>
       <c r="F23" s="3">
+        <v>10500</v>
+      </c>
+      <c r="G23" s="3">
         <v>-39900</v>
       </c>
-      <c r="G23" s="3">
-        <v>2400</v>
-      </c>
       <c r="H23" s="3">
-        <v>3500</v>
+        <v>2000</v>
       </c>
       <c r="I23" s="3">
-        <v>5600</v>
+        <v>4000</v>
       </c>
       <c r="J23" s="3">
+        <v>5800</v>
+      </c>
+      <c r="K23" s="3">
         <v>-83300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>11000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-2500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-54500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>26500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>35000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>32300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>36300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>44700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>38000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>33100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>29300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>23600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>21900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>12600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>10300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>6700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-322600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>3900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-4300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-2200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-6100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-20000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-24800</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>400</v>
+      </c>
+      <c r="E24" s="3">
         <v>300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>200</v>
       </c>
-      <c r="G24" s="3">
-        <v>700</v>
-      </c>
       <c r="H24" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="I24" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
         <v>-800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-11400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>5800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>8400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>5700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>5200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>7500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>7600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>5900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>4200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>4300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>3300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>2900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-4600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-1200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-600</v>
       </c>
-      <c r="AD24" s="3">
-        <v>0</v>
-      </c>
       <c r="AE24" s="3">
         <v>0</v>
       </c>
@@ -2321,8 +2367,11 @@
       <c r="AI24" s="3">
         <v>0</v>
       </c>
+      <c r="AJ24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2422,210 +2471,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>4200</v>
+        <v>3400</v>
       </c>
       <c r="E26" s="3">
-        <v>10000</v>
+        <v>4100</v>
       </c>
       <c r="F26" s="3">
+        <v>9800</v>
+      </c>
+      <c r="G26" s="3">
         <v>-40100</v>
       </c>
-      <c r="G26" s="3">
-        <v>1700</v>
-      </c>
       <c r="H26" s="3">
-        <v>2900</v>
+        <v>1400</v>
       </c>
       <c r="I26" s="3">
-        <v>5600</v>
+        <v>3200</v>
       </c>
       <c r="J26" s="3">
+        <v>5800</v>
+      </c>
+      <c r="K26" s="3">
         <v>-82500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>8300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-2700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-43100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>20700</v>
-      </c>
-      <c r="P26" s="3">
-        <v>26700</v>
       </c>
       <c r="Q26" s="3">
         <v>26700</v>
       </c>
       <c r="R26" s="3">
+        <v>26700</v>
+      </c>
+      <c r="S26" s="3">
         <v>31200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>37300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>30500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>27200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>25000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>19200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>18600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>9700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>15000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>7900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-321700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>4500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-4300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-2200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-6100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-20000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-24800</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>4200</v>
+        <v>3400</v>
       </c>
       <c r="E27" s="3">
-        <v>10000</v>
+        <v>4100</v>
       </c>
       <c r="F27" s="3">
+        <v>9800</v>
+      </c>
+      <c r="G27" s="3">
         <v>-40100</v>
       </c>
-      <c r="G27" s="3">
-        <v>1700</v>
-      </c>
       <c r="H27" s="3">
-        <v>2900</v>
+        <v>1400</v>
       </c>
       <c r="I27" s="3">
-        <v>5600</v>
+        <v>3200</v>
       </c>
       <c r="J27" s="3">
+        <v>5800</v>
+      </c>
+      <c r="K27" s="3">
         <v>-82500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>8300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-2700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-43100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>74500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>26700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>26600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>35200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>37300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>30500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>27000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>24600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>19200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>18600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>9700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>14500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>7900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-310800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-71200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-5800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-2200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-6100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-20000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-24800</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2725,8 +2783,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2826,8 +2887,11 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +2991,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,210 +3095,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-14500</v>
+        <v>-200</v>
       </c>
       <c r="E32" s="3">
-        <v>-16200</v>
+        <v>100</v>
       </c>
       <c r="F32" s="3">
-        <v>-18600</v>
+        <v>-300</v>
       </c>
       <c r="G32" s="3">
-        <v>-17800</v>
+        <v>400</v>
       </c>
       <c r="H32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="J32" s="3">
+        <v>100</v>
+      </c>
+      <c r="K32" s="3">
+        <v>-14900</v>
+      </c>
+      <c r="L32" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="M32" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="N32" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="O32" s="3">
         <v>-8500</v>
       </c>
-      <c r="I32" s="3">
-        <v>-13600</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-14900</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-9500</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-8700</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-9300</v>
-      </c>
-      <c r="N32" s="3">
-        <v>-8500</v>
-      </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-14700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-8900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-9000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-10300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-11900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-11300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-12100</v>
-      </c>
-      <c r="V32" s="3">
-        <v>-13600</v>
       </c>
       <c r="W32" s="3">
         <v>-13600</v>
       </c>
       <c r="X32" s="3">
+        <v>-13600</v>
+      </c>
+      <c r="Y32" s="3">
         <v>-11600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-8300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-7700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-7100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>320100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-700</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-300</v>
-      </c>
-      <c r="AG32" s="3">
-        <v>-100</v>
       </c>
       <c r="AH32" s="3">
         <v>-100</v>
       </c>
       <c r="AI32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AJ32" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>4200</v>
+        <v>3400</v>
       </c>
       <c r="E33" s="3">
-        <v>10000</v>
+        <v>4100</v>
       </c>
       <c r="F33" s="3">
+        <v>9800</v>
+      </c>
+      <c r="G33" s="3">
         <v>-40100</v>
       </c>
-      <c r="G33" s="3">
-        <v>1700</v>
-      </c>
       <c r="H33" s="3">
-        <v>2900</v>
+        <v>1400</v>
       </c>
       <c r="I33" s="3">
-        <v>5600</v>
+        <v>3200</v>
       </c>
       <c r="J33" s="3">
+        <v>5800</v>
+      </c>
+      <c r="K33" s="3">
         <v>-82500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>8300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-2700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-43100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>74500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>26700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>26600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>35200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>37300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>30500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>27000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>24600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>19200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>18600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>9700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>14500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>7900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-310800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-71200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-5800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-2200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-6100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-20000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-24800</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,215 +3407,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>4200</v>
+        <v>3400</v>
       </c>
       <c r="E35" s="3">
-        <v>10000</v>
+        <v>4100</v>
       </c>
       <c r="F35" s="3">
+        <v>9800</v>
+      </c>
+      <c r="G35" s="3">
         <v>-40100</v>
       </c>
-      <c r="G35" s="3">
-        <v>1700</v>
-      </c>
       <c r="H35" s="3">
-        <v>2900</v>
+        <v>1400</v>
       </c>
       <c r="I35" s="3">
-        <v>5600</v>
+        <v>3200</v>
       </c>
       <c r="J35" s="3">
+        <v>5800</v>
+      </c>
+      <c r="K35" s="3">
         <v>-82500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>8300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-2700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-43100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>74500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>26700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>26600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>35200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>37300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>30500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>27000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>24600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>19200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>18600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>9700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>14500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>7900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-310800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-71200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-5800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-2200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-6100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-20000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-24800</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3660,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,92 +3698,93 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>141800</v>
+        <v>156200</v>
       </c>
       <c r="E41" s="3">
-        <v>76400</v>
+        <v>138400</v>
       </c>
       <c r="F41" s="3">
+        <v>75100</v>
+      </c>
+      <c r="G41" s="3">
         <v>72200</v>
       </c>
-      <c r="G41" s="3">
-        <v>116400</v>
-      </c>
       <c r="H41" s="3">
-        <v>97600</v>
+        <v>113100</v>
       </c>
       <c r="I41" s="3">
-        <v>273700</v>
+        <v>95400</v>
       </c>
       <c r="J41" s="3">
+        <v>282600</v>
+      </c>
+      <c r="K41" s="3">
         <v>97900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>149600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>287500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>205800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1397500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1437100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1383600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1370200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1290200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1341400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1230000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1243000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1209800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1322900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1254600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>869400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>826800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>805000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>770000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>584200</v>
       </c>
-      <c r="AD41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AE41" s="3" t="s">
         <v>16</v>
       </c>
@@ -3713,89 +3800,92 @@
       <c r="AI41" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AJ41" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>786400</v>
+        <v>780200</v>
       </c>
       <c r="E42" s="3">
-        <v>935400</v>
+        <v>767600</v>
       </c>
       <c r="F42" s="3">
-        <v>965900</v>
+        <v>918900</v>
       </c>
       <c r="G42" s="3">
-        <v>1079500</v>
+        <v>966200</v>
       </c>
       <c r="H42" s="3">
-        <v>1174400</v>
+        <v>1049400</v>
       </c>
       <c r="I42" s="3">
-        <v>1103800</v>
+        <v>1148700</v>
       </c>
       <c r="J42" s="3">
+        <v>1139800</v>
+      </c>
+      <c r="K42" s="3">
         <v>1271800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1322300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1202300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1250300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>112500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>143500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>158700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>159500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>168000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>249800</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>353400</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>384600</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>341800</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>165000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>137700</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>97600</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>43600</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>17000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>21300</v>
       </c>
-      <c r="AC42" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD42" s="3" t="s">
         <v>16</v>
       </c>
@@ -3814,92 +3904,95 @@
       <c r="AI42" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AJ42" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>52400</v>
+        <v>60900</v>
       </c>
       <c r="E43" s="3">
-        <v>32900</v>
+        <v>9700</v>
       </c>
       <c r="F43" s="3">
-        <v>30000</v>
+        <v>32300</v>
       </c>
       <c r="G43" s="3">
-        <v>24500</v>
+        <v>58000</v>
       </c>
       <c r="H43" s="3">
-        <v>17400</v>
+        <v>23800</v>
       </c>
       <c r="I43" s="3">
-        <v>20900</v>
+        <v>17100</v>
       </c>
       <c r="J43" s="3">
+        <v>21600</v>
+      </c>
+      <c r="K43" s="3">
         <v>20300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>21600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>30400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>30500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>32600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>40700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>41000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>33800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>18900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>19000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>17100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>17600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>17500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>25700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>14600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>33500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>41100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>18500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>19900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>19800</v>
       </c>
-      <c r="AD43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AE43" s="3" t="s">
         <v>16</v>
       </c>
@@ -3915,31 +4008,34 @@
       <c r="AI43" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AJ43" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -4016,92 +4112,95 @@
       <c r="AI44" s="3">
         <v>0</v>
       </c>
+      <c r="AJ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>98300</v>
+      </c>
+      <c r="E45" s="3">
+        <v>127500</v>
+      </c>
+      <c r="F45" s="3">
+        <v>89300</v>
+      </c>
+      <c r="G45" s="3">
+        <v>50500</v>
+      </c>
+      <c r="H45" s="3">
+        <v>91000</v>
+      </c>
+      <c r="I45" s="3">
+        <v>81800</v>
+      </c>
+      <c r="J45" s="3">
+        <v>83000</v>
+      </c>
+      <c r="K45" s="3">
         <v>90400</v>
       </c>
-      <c r="E45" s="3">
-        <v>93700</v>
-      </c>
-      <c r="F45" s="3">
-        <v>81000</v>
-      </c>
-      <c r="G45" s="3">
-        <v>96300</v>
-      </c>
-      <c r="H45" s="3">
-        <v>86600</v>
-      </c>
-      <c r="I45" s="3">
-        <v>82700</v>
-      </c>
-      <c r="J45" s="3">
-        <v>90400</v>
-      </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>140500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>111200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>129200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>99300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>133300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>107700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>94800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>91900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>71800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>61100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>63100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>61900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>68100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>46800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>35500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>46400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>32700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>24700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>12200</v>
       </c>
-      <c r="AD45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AE45" s="3" t="s">
         <v>16</v>
       </c>
@@ -4117,92 +4216,95 @@
       <c r="AI45" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AJ45" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>1071000</v>
+        <v>1098100</v>
       </c>
       <c r="E46" s="3">
-        <v>1138400</v>
+        <v>1045400</v>
       </c>
       <c r="F46" s="3">
-        <v>1149100</v>
+        <v>1118300</v>
       </c>
       <c r="G46" s="3">
-        <v>1316700</v>
+        <v>1149400</v>
       </c>
       <c r="H46" s="3">
-        <v>1376100</v>
+        <v>1280000</v>
       </c>
       <c r="I46" s="3">
-        <v>1481000</v>
+        <v>1345900</v>
       </c>
       <c r="J46" s="3">
+        <v>1529300</v>
+      </c>
+      <c r="K46" s="3">
         <v>1480400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1633900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1631500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1615700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1641800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1754600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1690900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1658300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1568900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1682100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1661600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1708300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1630900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1581700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1453600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1035900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>957800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>873300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>835800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>616200</v>
       </c>
-      <c r="AD46" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AE46" s="3" t="s">
         <v>16</v>
       </c>
@@ -4218,92 +4320,95 @@
       <c r="AI46" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AJ46" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>317700</v>
+        <v>301700</v>
       </c>
       <c r="E47" s="3">
-        <v>422200</v>
+        <v>310100</v>
       </c>
       <c r="F47" s="3">
-        <v>466000</v>
+        <v>414800</v>
       </c>
       <c r="G47" s="3">
-        <v>419200</v>
+        <v>466100</v>
       </c>
       <c r="H47" s="3">
-        <v>389200</v>
+        <v>407500</v>
       </c>
       <c r="I47" s="3">
-        <v>220500</v>
+        <v>380700</v>
       </c>
       <c r="J47" s="3">
+        <v>227700</v>
+      </c>
+      <c r="K47" s="3">
         <v>279000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>176400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>125000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>120300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>83900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>82800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>72500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>73200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>65000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>66400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>63400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>63500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>58400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>57400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>56200</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>50200</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>31900</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>29800</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>30400</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>100</v>
       </c>
-      <c r="AD47" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AE47" s="3" t="s">
         <v>16</v>
       </c>
@@ -4319,92 +4424,95 @@
       <c r="AI47" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AJ47" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>108600</v>
+        <v>113400</v>
       </c>
       <c r="E48" s="3">
-        <v>105300</v>
+        <v>106000</v>
       </c>
       <c r="F48" s="3">
+        <v>103500</v>
+      </c>
+      <c r="G48" s="3">
         <v>99500</v>
       </c>
-      <c r="G48" s="3">
-        <v>82300</v>
-      </c>
       <c r="H48" s="3">
-        <v>81000</v>
+        <v>80000</v>
       </c>
       <c r="I48" s="3">
-        <v>78500</v>
+        <v>79200</v>
       </c>
       <c r="J48" s="3">
+        <v>81100</v>
+      </c>
+      <c r="K48" s="3">
         <v>77000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>71700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>70800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>64600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>65400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>69300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>26100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>23300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>25300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>30000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>30900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>29100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>30700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>33500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>33600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>28900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>12700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>11700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>10000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>5500</v>
       </c>
-      <c r="AD48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AE48" s="3" t="s">
         <v>16</v>
       </c>
@@ -4420,92 +4528,95 @@
       <c r="AI48" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AJ48" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>85000</v>
+        <v>83600</v>
       </c>
       <c r="E49" s="3">
-        <v>86000</v>
+        <v>83000</v>
       </c>
       <c r="F49" s="3">
-        <v>87200</v>
+        <v>84400</v>
       </c>
       <c r="G49" s="3">
-        <v>5600</v>
+        <v>87300</v>
       </c>
       <c r="H49" s="3">
-        <v>6600</v>
+        <v>5500</v>
       </c>
       <c r="I49" s="3">
+        <v>6500</v>
+      </c>
+      <c r="J49" s="3">
+        <v>7600</v>
+      </c>
+      <c r="K49" s="3">
+        <v>92500</v>
+      </c>
+      <c r="L49" s="3">
+        <v>8700</v>
+      </c>
+      <c r="M49" s="3">
+        <v>10000</v>
+      </c>
+      <c r="N49" s="3">
+        <v>11000</v>
+      </c>
+      <c r="O49" s="3">
+        <v>11600</v>
+      </c>
+      <c r="P49" s="3">
+        <v>12900</v>
+      </c>
+      <c r="Q49" s="3">
+        <v>13600</v>
+      </c>
+      <c r="R49" s="3">
+        <v>7300</v>
+      </c>
+      <c r="S49" s="3">
+        <v>8700</v>
+      </c>
+      <c r="T49" s="3">
+        <v>10700</v>
+      </c>
+      <c r="U49" s="3">
+        <v>9700</v>
+      </c>
+      <c r="V49" s="3">
+        <v>7000</v>
+      </c>
+      <c r="W49" s="3">
+        <v>6900</v>
+      </c>
+      <c r="X49" s="3">
         <v>7400</v>
       </c>
-      <c r="J49" s="3">
-        <v>92500</v>
-      </c>
-      <c r="K49" s="3">
-        <v>8700</v>
-      </c>
-      <c r="L49" s="3">
-        <v>10000</v>
-      </c>
-      <c r="M49" s="3">
-        <v>11000</v>
-      </c>
-      <c r="N49" s="3">
-        <v>11600</v>
-      </c>
-      <c r="O49" s="3">
-        <v>12900</v>
-      </c>
-      <c r="P49" s="3">
-        <v>13600</v>
-      </c>
-      <c r="Q49" s="3">
-        <v>7300</v>
-      </c>
-      <c r="R49" s="3">
-        <v>8700</v>
-      </c>
-      <c r="S49" s="3">
-        <v>10700</v>
-      </c>
-      <c r="T49" s="3">
-        <v>9700</v>
-      </c>
-      <c r="U49" s="3">
+      <c r="Y49" s="3">
+        <v>6900</v>
+      </c>
+      <c r="Z49" s="3">
+        <v>7400</v>
+      </c>
+      <c r="AA49" s="3">
+        <v>7500</v>
+      </c>
+      <c r="AB49" s="3">
         <v>7000</v>
       </c>
-      <c r="V49" s="3">
-        <v>6900</v>
-      </c>
-      <c r="W49" s="3">
-        <v>7400</v>
-      </c>
-      <c r="X49" s="3">
-        <v>6900</v>
-      </c>
-      <c r="Y49" s="3">
-        <v>7400</v>
-      </c>
-      <c r="Z49" s="3">
-        <v>7500</v>
-      </c>
-      <c r="AA49" s="3">
-        <v>7000</v>
-      </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>5200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>800</v>
       </c>
-      <c r="AD49" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AE49" s="3" t="s">
         <v>16</v>
       </c>
@@ -4521,8 +4632,11 @@
       <c r="AI49" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AJ49" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4736,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,92 +4840,95 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>17100</v>
+        <v>17600</v>
       </c>
       <c r="E52" s="3">
+        <v>16700</v>
+      </c>
+      <c r="F52" s="3">
+        <v>20000</v>
+      </c>
+      <c r="G52" s="3">
         <v>20300</v>
       </c>
-      <c r="F52" s="3">
-        <v>20300</v>
-      </c>
-      <c r="G52" s="3">
-        <v>17300</v>
-      </c>
       <c r="H52" s="3">
-        <v>14900</v>
+        <v>16800</v>
       </c>
       <c r="I52" s="3">
-        <v>13300</v>
+        <v>14600</v>
       </c>
       <c r="J52" s="3">
+        <v>13700</v>
+      </c>
+      <c r="K52" s="3">
         <v>15600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>19100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>25900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>29600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>23600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>25200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>64800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>63900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>59500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>21700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>28900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>27700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>23200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>25400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>23300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>20600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>22000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>10500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>2200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>5400</v>
       </c>
-      <c r="AD52" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AE52" s="3" t="s">
         <v>16</v>
       </c>
@@ -4824,8 +4944,11 @@
       <c r="AI52" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AJ52" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,92 +5048,95 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1599300</v>
+        <v>1614400</v>
       </c>
       <c r="E54" s="3">
-        <v>1772200</v>
+        <v>1561100</v>
       </c>
       <c r="F54" s="3">
-        <v>1822100</v>
+        <v>1741000</v>
       </c>
       <c r="G54" s="3">
-        <v>1841200</v>
+        <v>1822700</v>
       </c>
       <c r="H54" s="3">
-        <v>1867800</v>
+        <v>1789900</v>
       </c>
       <c r="I54" s="3">
-        <v>1800700</v>
+        <v>1826800</v>
       </c>
       <c r="J54" s="3">
+        <v>1859400</v>
+      </c>
+      <c r="K54" s="3">
         <v>1944500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1909800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1863200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1841100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1826300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1944700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1868000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1826100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1727600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1810900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1794500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1835600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1750200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1705400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1573700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1143100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1032000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>932300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>883600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>627900</v>
       </c>
-      <c r="AD54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AE54" s="3" t="s">
         <v>16</v>
       </c>
@@ -5026,8 +5152,11 @@
       <c r="AI54" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AJ54" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5192,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,91 +5230,92 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2600</v>
+        <v>9700</v>
       </c>
       <c r="E57" s="3">
-        <v>5000</v>
+        <v>2500</v>
       </c>
       <c r="F57" s="3">
+        <v>4900</v>
+      </c>
+      <c r="G57" s="3">
         <v>2100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2700</v>
       </c>
-      <c r="H57" s="3">
-        <v>7800</v>
-      </c>
       <c r="I57" s="3">
-        <v>4100</v>
+        <v>7600</v>
       </c>
       <c r="J57" s="3">
+        <v>4300</v>
+      </c>
+      <c r="K57" s="3">
         <v>3200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5200</v>
-      </c>
-      <c r="M57" s="3">
-        <v>1700</v>
       </c>
       <c r="N57" s="3">
         <v>1700</v>
       </c>
       <c r="O57" s="3">
+        <v>1700</v>
+      </c>
+      <c r="P57" s="3">
         <v>2700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>8100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>5100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>3000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1000</v>
       </c>
-      <c r="AC57" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD57" s="3" t="s">
-        <v>16</v>
+      <c r="AD57" s="3">
+        <v>0</v>
       </c>
       <c r="AE57" s="3" t="s">
         <v>16</v>
@@ -5201,31 +5332,34 @@
       <c r="AI57" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AJ57" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>4200</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>3300</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -5302,92 +5436,95 @@
       <c r="AI58" s="3">
         <v>0</v>
       </c>
+      <c r="AJ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>248300</v>
+        <v>315800</v>
       </c>
       <c r="E59" s="3">
-        <v>407800</v>
+        <v>65600</v>
       </c>
       <c r="F59" s="3">
-        <v>302600</v>
+        <v>220700</v>
       </c>
       <c r="G59" s="3">
-        <v>252600</v>
+        <v>106600</v>
       </c>
       <c r="H59" s="3">
-        <v>260500</v>
+        <v>72200</v>
       </c>
       <c r="I59" s="3">
-        <v>255200</v>
+        <v>72900</v>
       </c>
       <c r="J59" s="3">
+        <v>74000</v>
+      </c>
+      <c r="K59" s="3">
         <v>314800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>304700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>310800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>339000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>353200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>370200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>355100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>339900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>330600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>340500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>362100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>368100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>376200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>337600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>298300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>242600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>199100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>151400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>128700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>244600</v>
       </c>
-      <c r="AD59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AE59" s="3" t="s">
         <v>16</v>
       </c>
@@ -5403,92 +5540,95 @@
       <c r="AI59" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AJ59" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>250900</v>
+        <v>514300</v>
       </c>
       <c r="E60" s="3">
-        <v>412800</v>
+        <v>244900</v>
       </c>
       <c r="F60" s="3">
-        <v>304700</v>
+        <v>405600</v>
       </c>
       <c r="G60" s="3">
-        <v>255300</v>
+        <v>304800</v>
       </c>
       <c r="H60" s="3">
-        <v>268300</v>
+        <v>248200</v>
       </c>
       <c r="I60" s="3">
-        <v>259300</v>
+        <v>262400</v>
       </c>
       <c r="J60" s="3">
+        <v>267800</v>
+      </c>
+      <c r="K60" s="3">
         <v>318000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>307600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>316000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>340700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>354900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>372900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>363200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>341000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>332000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>343400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>367200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>368500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>376700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>339300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>301100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>245600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>200500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>154000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>129600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>244600</v>
       </c>
-      <c r="AD60" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AE60" s="3" t="s">
         <v>16</v>
       </c>
@@ -5504,31 +5644,34 @@
       <c r="AI60" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AJ60" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>4600</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>5700</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>6800</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -5605,92 +5748,95 @@
       <c r="AI61" s="3">
         <v>0</v>
       </c>
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>14100</v>
-      </c>
-      <c r="E62" s="3">
-        <v>17600</v>
-      </c>
-      <c r="F62" s="3">
-        <v>19500</v>
-      </c>
-      <c r="G62" s="3">
-        <v>11300</v>
-      </c>
-      <c r="H62" s="3">
-        <v>12200</v>
-      </c>
-      <c r="I62" s="3">
-        <v>13600</v>
-      </c>
-      <c r="J62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K62" s="3">
         <v>18000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>16900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>19900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>23700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>23200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>28600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>34800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>35700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>34700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>35000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>37800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>38500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>36200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>35300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>33300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>27800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>11700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>9600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>10700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>7000</v>
       </c>
-      <c r="AD62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AE62" s="3" t="s">
         <v>16</v>
       </c>
@@ -5706,8 +5852,11 @@
       <c r="AI62" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AJ62" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +5956,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5908,8 +6060,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,92 +6164,95 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>265000</v>
+        <v>527400</v>
       </c>
       <c r="E66" s="3">
-        <v>430400</v>
+        <v>258600</v>
       </c>
       <c r="F66" s="3">
-        <v>324200</v>
+        <v>422800</v>
       </c>
       <c r="G66" s="3">
-        <v>266600</v>
+        <v>324300</v>
       </c>
       <c r="H66" s="3">
-        <v>280500</v>
+        <v>259200</v>
       </c>
       <c r="I66" s="3">
-        <v>273000</v>
+        <v>274400</v>
       </c>
       <c r="J66" s="3">
+        <v>281900</v>
+      </c>
+      <c r="K66" s="3">
         <v>336000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>324500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>335900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>364300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>378200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>401500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>398000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>376600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>366600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>378400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>405000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>407000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>412900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>374500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>334300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>273300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>212200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>163700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>140300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>251600</v>
       </c>
-      <c r="AD66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AE66" s="3" t="s">
         <v>16</v>
       </c>
@@ -6110,8 +6268,11 @@
       <c r="AI66" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AJ66" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6308,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6410,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,8 +6514,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6430,11 +6598,11 @@
         <v>0</v>
       </c>
       <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD70" s="3">
         <v>434700</v>
       </c>
-      <c r="AD70" s="3">
-        <v>0</v>
-      </c>
       <c r="AE70" s="3">
         <v>0</v>
       </c>
@@ -6450,8 +6618,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,92 +6722,95 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-257900</v>
+        <v>-257400</v>
       </c>
       <c r="E72" s="3">
-        <v>-262100</v>
+        <v>-251700</v>
       </c>
       <c r="F72" s="3">
-        <v>-272100</v>
+        <v>-257400</v>
       </c>
       <c r="G72" s="3">
-        <v>-223300</v>
+        <v>-272200</v>
       </c>
       <c r="H72" s="3">
-        <v>-225100</v>
+        <v>-217100</v>
       </c>
       <c r="I72" s="3">
-        <v>-228300</v>
+        <v>-220100</v>
       </c>
       <c r="J72" s="3">
+        <v>-235800</v>
+      </c>
+      <c r="K72" s="3">
         <v>-243200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-157500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-166900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-164200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-162300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-123000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-199500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-226300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-245200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-296800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-224900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-276600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-295900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-324700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-336800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-355400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-347000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-348400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-365300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-59100</v>
       </c>
-      <c r="AD72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AE72" s="3" t="s">
         <v>16</v>
       </c>
@@ -6652,8 +6826,11 @@
       <c r="AI72" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AJ72" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +6930,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7034,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,92 +7138,95 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>1334400</v>
+        <v>1087100</v>
       </c>
       <c r="E76" s="3">
-        <v>1341800</v>
+        <v>1302500</v>
       </c>
       <c r="F76" s="3">
-        <v>1497900</v>
+        <v>1318100</v>
       </c>
       <c r="G76" s="3">
-        <v>1574600</v>
+        <v>1498300</v>
       </c>
       <c r="H76" s="3">
-        <v>1587200</v>
+        <v>1530700</v>
       </c>
       <c r="I76" s="3">
-        <v>1527700</v>
+        <v>1552400</v>
       </c>
       <c r="J76" s="3">
+        <v>1577600</v>
+      </c>
+      <c r="K76" s="3">
         <v>1608500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1585200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1527300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1476700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1448100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1543200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1470100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1449400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1360900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1432500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1389500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1428600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1337300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1330900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1239400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>869700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>819800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>768600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>743300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>-58300</v>
       </c>
-      <c r="AD76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AE76" s="3" t="s">
         <v>16</v>
       </c>
@@ -7056,8 +7242,11 @@
       <c r="AI76" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AJ76" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,215 +7346,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>4200</v>
+        <v>3400</v>
       </c>
       <c r="E81" s="3">
-        <v>10000</v>
+        <v>4100</v>
       </c>
       <c r="F81" s="3">
+        <v>9800</v>
+      </c>
+      <c r="G81" s="3">
         <v>-40100</v>
       </c>
-      <c r="G81" s="3">
-        <v>1700</v>
-      </c>
       <c r="H81" s="3">
-        <v>2900</v>
+        <v>1400</v>
       </c>
       <c r="I81" s="3">
-        <v>5600</v>
+        <v>3200</v>
       </c>
       <c r="J81" s="3">
+        <v>5800</v>
+      </c>
+      <c r="K81" s="3">
         <v>-82500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>8300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-2700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-43100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>74500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>26700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>26600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>35200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>37300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>30500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>27000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>24600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>19200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>18600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>9700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>14500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>7900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-310800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-71200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-5800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-2200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-6100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-20000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-24800</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,31 +7599,32 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>0</v>
-      </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
+      <c r="D83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -7502,8 +7701,11 @@
       <c r="AI83" s="3">
         <v>0</v>
       </c>
+      <c r="AJ83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +7805,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +7909,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8013,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8117,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,31 +8221,34 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
-        <v>0</v>
-      </c>
-      <c r="E89" s="3">
-        <v>0</v>
-      </c>
-      <c r="F89" s="3">
-        <v>0</v>
-      </c>
-      <c r="G89" s="3">
-        <v>0</v>
-      </c>
-      <c r="H89" s="3">
-        <v>0</v>
-      </c>
-      <c r="I89" s="3">
-        <v>0</v>
-      </c>
-      <c r="J89" s="3">
-        <v>0</v>
+      <c r="D89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K89" s="3">
         <v>0</v>
@@ -8108,8 +8325,11 @@
       <c r="AI89" s="3">
         <v>0</v>
       </c>
+      <c r="AJ89" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,31 +8365,32 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -8246,8 +8467,11 @@
       <c r="AI91" s="3">
         <v>0</v>
       </c>
+      <c r="AJ91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8571,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,31 +8675,34 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
-      </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
+      <c r="D94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K94" s="3">
         <v>0</v>
@@ -8549,8 +8779,11 @@
       <c r="AI94" s="3">
         <v>0</v>
       </c>
+      <c r="AJ94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,31 +8819,32 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8687,8 +8921,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9025,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9129,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,31 +9233,34 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>0</v>
-      </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
+      <c r="D100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K100" s="3">
         <v>0</v>
@@ -9091,31 +9337,34 @@
       <c r="AI100" s="3">
         <v>0</v>
       </c>
+      <c r="AJ100" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -9192,31 +9441,34 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3">
-        <v>0</v>
-      </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
-      <c r="J102" s="3">
-        <v>0</v>
+      <c r="D102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J102" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K102" s="3">
         <v>0</v>
@@ -9291,6 +9543,9 @@
         <v>0</v>
       </c>
       <c r="AI102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/HUYA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HUYA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="92">
   <si>
     <t>HUYA</t>
   </si>
@@ -656,467 +656,479 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>204900</v>
+      </c>
+      <c r="E8" s="3">
         <v>219200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>212100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>208300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>222200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>228100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>251200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>285700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>302600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>328600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>316300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>342600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>387000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>423000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>425500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>374100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>416200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>414800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>397500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>380500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>379900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>353400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>307200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>249300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>218600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>178700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>149000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>121000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>110000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>86600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>68500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>58000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>49300</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>28600</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>181600</v>
+      </c>
+      <c r="E9" s="3">
         <v>190200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>182600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>177800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>214100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>194800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>213500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>246500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>336600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>281300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>285800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>296200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>386800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>351300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>342000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>300300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>333100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>323300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>312700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>305600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>308100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>290000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>255900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>207500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>183900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>151600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>125100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>102200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>93900</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>75700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>59900</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>55700</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>56300</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>40700</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>23400</v>
+      </c>
+      <c r="E10" s="3">
         <v>29000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>29600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>30500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>8100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>33300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>37600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>39200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-34000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>47300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>30500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>46400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>71600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>83500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>73800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>83200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>91400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>84700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>74900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>71800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>63400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>51300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>41800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>34700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>27100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>23900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>18800</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>16000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>10900</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>8500</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>2300</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>-7000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>-12000</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1153,112 +1165,116 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>16900</v>
+      </c>
+      <c r="E12" s="3">
         <v>17900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>17700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>18700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>15000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>19600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>19900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>22300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>20900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>23700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>23400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>27300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>28300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>29300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>29900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>28600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>30000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>26900</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>26500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>24600</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>27500</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>21100</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>16100</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>13800</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>11500</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>10400</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>8600</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>7400</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>6500</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>7300</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>5200</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>6200</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>7700</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1361,38 +1377,41 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>20700</v>
+      </c>
+      <c r="E14" s="3">
         <v>5200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>6200</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H14" s="3">
         <v>16100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>11100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>9000</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L14" s="3">
         <v>12700</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>16</v>
       </c>
@@ -1405,8 +1424,8 @@
       <c r="P14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1465,35 +1484,38 @@
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E15" s="3">
         <v>3600</v>
-      </c>
-      <c r="E15" s="3">
-        <v>3500</v>
       </c>
       <c r="F15" s="3">
         <v>3500</v>
       </c>
       <c r="G15" s="3">
+        <v>3500</v>
+      </c>
+      <c r="H15" s="3">
         <v>3600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>3500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>2800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>3700</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1569,8 +1591,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1604,216 +1629,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>217600</v>
+      </c>
+      <c r="E17" s="3">
         <v>223800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>215700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>213600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>264700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>232400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>255100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>294000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>400700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>327000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>327600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>351000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>450000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>411200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>399300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>350800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>390200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>381900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>370700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>359500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>364300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>343400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>296800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>244900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>215900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>179100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>151500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>117000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>110200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>91700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>71000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>64100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>69400</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>53400</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-4600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-3600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-5300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-42500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-4300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-4000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-8300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-98200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-11300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-8400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-63000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>11800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>26100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>23300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>26100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>32800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>26700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>21000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>15700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>10000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>10300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>4300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>2700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-2500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>4000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-5100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-2500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-6100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-20100</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-24800</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1850,139 +1882,143 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>100</v>
+      </c>
+      <c r="E20" s="3">
         <v>200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>14900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>9500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>8700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>9300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>8500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>14700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>8900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>9000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>10300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>11900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>11300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>12100</v>
-      </c>
-      <c r="W20" s="3">
-        <v>13600</v>
       </c>
       <c r="X20" s="3">
         <v>13600</v>
       </c>
       <c r="Y20" s="3">
+        <v>13600</v>
+      </c>
+      <c r="Z20" s="3">
         <v>11600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>8300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>7700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>7100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-320100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>1000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>700</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>300</v>
-      </c>
-      <c r="AH20" s="3">
-        <v>100</v>
       </c>
       <c r="AI20" s="3">
         <v>100</v>
       </c>
       <c r="AJ20" s="3">
+        <v>100</v>
+      </c>
+      <c r="AK20" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="E21" s="3">
         <v>-1200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-2200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-38600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-1100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-1500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-4500</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>16</v>
       </c>
@@ -2058,8 +2094,11 @@
       <c r="AJ21" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AK21" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2084,8 +2123,8 @@
       <c r="J22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -2162,112 +2201,118 @@
       <c r="AJ22" s="3">
         <v>0</v>
       </c>
+      <c r="AK22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-23200</v>
+      </c>
+      <c r="E23" s="3">
         <v>3800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>4400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>10500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-39900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>4000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>5800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-83300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>11000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-2500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-54500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>26500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>35000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>32300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>36300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>44700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>38000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>33100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>29300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>23600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>21900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>12600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>10300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>6700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-322600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>3900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-4300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-2200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-6100</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-20000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-24800</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2275,86 +2320,86 @@
         <v>400</v>
       </c>
       <c r="E24" s="3">
+        <v>400</v>
+      </c>
+      <c r="F24" s="3">
         <v>300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>800</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
       <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
         <v>-800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-11400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>5800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>8400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>5700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>5200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>7500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>7600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>5900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>4200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>4300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>3300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>2900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-4600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-1200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-600</v>
       </c>
-      <c r="AE24" s="3">
-        <v>0</v>
-      </c>
       <c r="AF24" s="3">
         <v>0</v>
       </c>
@@ -2370,8 +2415,11 @@
       <c r="AJ24" s="3">
         <v>0</v>
       </c>
+      <c r="AK24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2474,216 +2522,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-23600</v>
+      </c>
+      <c r="E26" s="3">
         <v>3400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>4100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>9800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-40100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>3200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>5800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-82500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>8300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-2700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-43100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>20700</v>
-      </c>
-      <c r="Q26" s="3">
-        <v>26700</v>
       </c>
       <c r="R26" s="3">
         <v>26700</v>
       </c>
       <c r="S26" s="3">
+        <v>26700</v>
+      </c>
+      <c r="T26" s="3">
         <v>31200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>37300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>30500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>27200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>25000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>19200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>18600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>9700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>15000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>7900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-321700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>4500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-4300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-2200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-6100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-20000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-24800</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-23600</v>
+      </c>
+      <c r="E27" s="3">
         <v>3400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>4100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>9800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-40100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>3200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>5800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-82500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>8300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-2700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-43100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>74500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>26700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>26600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>35200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>37300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>30500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>27000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>24600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>19200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>18600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>9700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>14500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>7900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-310800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-71200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-5800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-2200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-6100</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-20000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-24800</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2786,8 +2843,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2890,8 +2950,11 @@
       <c r="AJ29" s="3">
         <v>0</v>
       </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2994,8 +3057,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3098,216 +3164,225 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-14900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-9500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-8700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-9300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-8500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-14700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-8900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-9000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-10300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-11900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-11300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-12100</v>
-      </c>
-      <c r="W32" s="3">
-        <v>-13600</v>
       </c>
       <c r="X32" s="3">
         <v>-13600</v>
       </c>
       <c r="Y32" s="3">
+        <v>-13600</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-11600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-8300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-7700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-7100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>320100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-700</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-300</v>
-      </c>
-      <c r="AH32" s="3">
-        <v>-100</v>
       </c>
       <c r="AI32" s="3">
         <v>-100</v>
       </c>
       <c r="AJ32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AK32" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-23600</v>
+      </c>
+      <c r="E33" s="3">
         <v>3400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>4100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>9800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-40100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>3200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>5800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-82500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>8300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-2700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-43100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>74500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>26700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>26600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>35200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>37300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>30500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>27000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>24600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>19200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>18600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>9700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>14500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>7900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-310800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-71200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-5800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-2200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-6100</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-20000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-24800</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3410,221 +3485,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-23600</v>
+      </c>
+      <c r="E35" s="3">
         <v>3400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>4100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>9800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-40100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>3200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>5800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-82500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>8300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-2700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-43100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>74500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>26700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>26600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>35200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>37300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>30500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>27000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>24600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>19200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>18600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>9700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>14500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>7900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-310800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-71200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-5800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-2200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-6100</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-20000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-24800</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3661,8 +3745,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3699,95 +3784,96 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>162900</v>
+      </c>
+      <c r="E41" s="3">
         <v>156200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>138400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>75100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>72200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>113100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>95400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>282600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>97900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>149600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>287500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>205800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1397500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1437100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1383600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1370200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1290200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1341400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1230000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1243000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1209800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1322900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1254600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>869400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>826800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>805000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>770000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>584200</v>
       </c>
-      <c r="AE41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AF41" s="3" t="s">
         <v>16</v>
       </c>
@@ -3803,92 +3889,95 @@
       <c r="AJ41" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AK41" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>558300</v>
+      </c>
+      <c r="E42" s="3">
         <v>780200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>767600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>918900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>966200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1049400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1148700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1139800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1271800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1322300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1202300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1250300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>112500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>143500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>158700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>159500</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>168000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>249800</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>353400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>384600</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>341800</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>165000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>137700</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>97600</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>43600</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>17000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>21300</v>
       </c>
-      <c r="AD42" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AE42" s="3" t="s">
         <v>16</v>
       </c>
@@ -3907,95 +3996,98 @@
       <c r="AJ42" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AK42" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>60900</v>
+        <v>10400</v>
       </c>
       <c r="E43" s="3">
+        <v>12800</v>
+      </c>
+      <c r="F43" s="3">
         <v>9700</v>
       </c>
-      <c r="F43" s="3">
-        <v>32300</v>
-      </c>
       <c r="G43" s="3">
+        <v>10300</v>
+      </c>
+      <c r="H43" s="3">
         <v>58000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>23800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>17100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>21600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>20300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>21600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>30400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>30500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>32600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>40700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>41000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>33800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>18900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>19000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>17100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>17600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>17500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>25700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>14600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>33500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>41100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>18500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>19900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>19800</v>
       </c>
-      <c r="AE43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AF43" s="3" t="s">
         <v>16</v>
       </c>
@@ -4011,8 +4103,11 @@
       <c r="AJ43" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AK43" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4037,8 +4132,8 @@
       <c r="J44" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -4115,95 +4210,98 @@
       <c r="AJ44" s="3">
         <v>0</v>
       </c>
+      <c r="AK44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>98300</v>
+        <v>71700</v>
       </c>
       <c r="E45" s="3">
+        <v>146300</v>
+      </c>
+      <c r="F45" s="3">
         <v>127500</v>
       </c>
-      <c r="F45" s="3">
-        <v>89300</v>
-      </c>
       <c r="G45" s="3">
+        <v>111300</v>
+      </c>
+      <c r="H45" s="3">
         <v>50500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>91000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>81800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>83000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>90400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>140500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>111200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>129200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>99300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>133300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>107700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>94800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>91900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>71800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>61100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>63100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>61900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>68100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>46800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>35500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>46400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>32700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>24700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>12200</v>
       </c>
-      <c r="AE45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AF45" s="3" t="s">
         <v>16</v>
       </c>
@@ -4219,95 +4317,98 @@
       <c r="AJ45" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AK45" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>834100</v>
+      </c>
+      <c r="E46" s="3">
         <v>1098100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1045400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1118300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1149400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1280000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1345900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1529300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1480400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1633900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1631500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1615700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1641800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1754600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1690900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1658300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1568900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1682100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1661600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1708300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1630900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1581700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1453600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1035900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>957800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>873300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>835800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>616200</v>
       </c>
-      <c r="AE46" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AF46" s="3" t="s">
         <v>16</v>
       </c>
@@ -4323,95 +4424,98 @@
       <c r="AJ46" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AK46" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>261800</v>
+      </c>
+      <c r="E47" s="3">
         <v>301700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>310100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>414800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>466100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>407500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>380700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>227700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>279000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>176400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>125000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>120300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>83900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>82800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>72500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>73200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>65000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>66400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>63400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>63500</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>58400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>57400</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>56200</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>50200</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>31900</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>29800</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>30400</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>100</v>
       </c>
-      <c r="AE47" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AF47" s="3" t="s">
         <v>16</v>
       </c>
@@ -4427,95 +4531,98 @@
       <c r="AJ47" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AK47" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>112800</v>
+      </c>
+      <c r="E48" s="3">
         <v>113400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>106000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>103500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>99500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>80000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>79200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>81100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>77000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>71700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>70800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>64600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>65400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>69300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>26100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>23300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>25300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>30000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>30900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>29100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>30700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>33500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>33600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>28900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>12700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>11700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>10000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>5500</v>
       </c>
-      <c r="AE48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AF48" s="3" t="s">
         <v>16</v>
       </c>
@@ -4531,95 +4638,98 @@
       <c r="AJ48" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AK48" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>84500</v>
+      </c>
+      <c r="E49" s="3">
         <v>83600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>83000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>84400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>87300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>5500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>6500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>7600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>92500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>8700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>10000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>11000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>11600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>12900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>13600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>7300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>8700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>10700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>9700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>7000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>6900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>7400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>6900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>7400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>7500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>7000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>5200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>800</v>
       </c>
-      <c r="AE49" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AF49" s="3" t="s">
         <v>16</v>
       </c>
@@ -4635,8 +4745,11 @@
       <c r="AJ49" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AK49" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4739,8 +4852,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4843,8 +4959,11 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4852,86 +4971,86 @@
         <v>17600</v>
       </c>
       <c r="E52" s="3">
+        <v>17600</v>
+      </c>
+      <c r="F52" s="3">
         <v>16700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>20000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>20300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>16800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>14600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>13700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>15600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>19100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>25900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>29600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>23600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>25200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>64800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>63900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>59500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>21700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>28900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>27700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>23200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>25400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>23300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>20600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>22000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>10500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>2200</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>5400</v>
       </c>
-      <c r="AE52" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AF52" s="3" t="s">
         <v>16</v>
       </c>
@@ -4947,8 +5066,11 @@
       <c r="AJ52" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AK52" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5051,95 +5173,98 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1310800</v>
+      </c>
+      <c r="E54" s="3">
         <v>1614400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1561100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1741000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1822700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1789900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1826800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1859400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1944500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1909800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1863200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1841100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1826300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1944700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1868000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1826100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1727600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1810900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1794500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1835600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1750200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1705400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1573700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1143100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1032000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>932300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>883600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>627900</v>
       </c>
-      <c r="AE54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AF54" s="3" t="s">
         <v>16</v>
       </c>
@@ -5155,8 +5280,11 @@
       <c r="AJ54" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AK54" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5193,8 +5321,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5231,94 +5360,95 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E57" s="3">
         <v>9700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>7600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5200</v>
-      </c>
-      <c r="N57" s="3">
-        <v>1700</v>
       </c>
       <c r="O57" s="3">
         <v>1700</v>
       </c>
       <c r="P57" s="3">
+        <v>1700</v>
+      </c>
+      <c r="Q57" s="3">
         <v>2700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>8100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>5100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>3000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1000</v>
       </c>
-      <c r="AD57" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE57" s="3" t="s">
-        <v>16</v>
+      <c r="AE57" s="3">
+        <v>0</v>
       </c>
       <c r="AF57" s="3" t="s">
         <v>16</v>
@@ -5335,16 +5465,19 @@
       <c r="AJ57" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AK57" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E58" s="3">
         <v>4200</v>
-      </c>
-      <c r="E58" s="3">
-        <v>4500</v>
       </c>
       <c r="F58" s="3">
         <v>4500</v>
@@ -5353,17 +5486,17 @@
         <v>4500</v>
       </c>
       <c r="H58" s="3">
+        <v>4500</v>
+      </c>
+      <c r="I58" s="3">
         <v>1400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3300</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -5439,95 +5572,98 @@
       <c r="AJ58" s="3">
         <v>0</v>
       </c>
+      <c r="AK58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>66000</v>
+      </c>
+      <c r="E59" s="3">
         <v>315800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>65600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>220700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>106600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>72200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>72900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>74000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>314800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>304700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>310800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>339000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>353200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>370200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>355100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>339900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>330600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>340500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>362100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>368100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>376200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>337600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>298300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>242600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>199100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>151400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>128700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>244600</v>
       </c>
-      <c r="AE59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AF59" s="3" t="s">
         <v>16</v>
       </c>
@@ -5543,95 +5679,98 @@
       <c r="AJ59" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AK59" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>265500</v>
+      </c>
+      <c r="E60" s="3">
         <v>514300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>244900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>405600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>304800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>248200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>262400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>267800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>318000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>307600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>316000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>340700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>354900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>372900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>363200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>341000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>332000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>343400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>367200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>368500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>376700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>339300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>301100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>245600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>200500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>154000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>129600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>244600</v>
       </c>
-      <c r="AE60" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AF60" s="3" t="s">
         <v>16</v>
       </c>
@@ -5647,35 +5786,38 @@
       <c r="AJ60" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AK60" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E61" s="3">
         <v>3500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>5700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>6800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1000</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -5751,8 +5893,11 @@
       <c r="AJ61" s="3">
         <v>0</v>
       </c>
+      <c r="AK61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5777,69 +5922,69 @@
       <c r="J62" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L62" s="3">
         <v>18000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>16900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>19900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>23700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>23200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>28600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>34800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>35700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>34700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>35000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>37800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>38500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>36200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>35300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>33300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>27800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>11700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>9600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>10700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>7000</v>
       </c>
-      <c r="AE62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AF62" s="3" t="s">
         <v>16</v>
       </c>
@@ -5855,8 +6000,11 @@
       <c r="AJ62" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AK62" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5959,8 +6107,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6063,8 +6214,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6167,95 +6321,98 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>276400</v>
+      </c>
+      <c r="E66" s="3">
         <v>527400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>258600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>422800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>324300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>259200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>274400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>281900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>336000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>324500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>335900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>364300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>378200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>401500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>398000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>376600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>366600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>378400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>405000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>407000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>412900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>374500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>334300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>273300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>212200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>163700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>140300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>251600</v>
       </c>
-      <c r="AE66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AF66" s="3" t="s">
         <v>16</v>
       </c>
@@ -6271,8 +6428,11 @@
       <c r="AJ66" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AK66" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6309,8 +6469,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6413,8 +6574,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6517,8 +6681,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6601,11 +6768,11 @@
         <v>0</v>
       </c>
       <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE70" s="3">
         <v>434700</v>
       </c>
-      <c r="AE70" s="3">
-        <v>0</v>
-      </c>
       <c r="AF70" s="3">
         <v>0</v>
       </c>
@@ -6621,8 +6788,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6725,95 +6895,98 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-271000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-257400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-251700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-257400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-272200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-217100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-220100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-235800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-243200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-157500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-166900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-164200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-162300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-123000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-199500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-226300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-245200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-296800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-224900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-276600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-295900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-324700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-336800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-355400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-347000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-348400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-365300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-59100</v>
       </c>
-      <c r="AE72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AF72" s="3" t="s">
         <v>16</v>
       </c>
@@ -6829,8 +7002,11 @@
       <c r="AJ72" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AK72" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6933,8 +7109,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7037,8 +7216,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7141,95 +7323,98 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1034500</v>
+      </c>
+      <c r="E76" s="3">
         <v>1087100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1302500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1318100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1498300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1530700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1552400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1577600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1608500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1585200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1527300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1476700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1448100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1543200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1470100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1449400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1360900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1432500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1389500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1428600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1337300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1330900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1239400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>869700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>819800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>768600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>743300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>-58300</v>
       </c>
-      <c r="AE76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AF76" s="3" t="s">
         <v>16</v>
       </c>
@@ -7245,8 +7430,11 @@
       <c r="AJ76" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AK76" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7349,221 +7537,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-23600</v>
+      </c>
+      <c r="E81" s="3">
         <v>3400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>4100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>9800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-40100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>3200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>5800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-82500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>8300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-2700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-43100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>74500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>26700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>26600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>35200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>37300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>30500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>27000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>24600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>19200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>18600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>9700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>14500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>7900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-310800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-71200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-5800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-2200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-6100</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-20000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-24800</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7600,8 +7797,9 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7626,8 +7824,8 @@
       <c r="J83" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
+      <c r="K83" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="L83" s="3">
         <v>0</v>
@@ -7704,8 +7902,11 @@
       <c r="AJ83" s="3">
         <v>0</v>
       </c>
+      <c r="AK83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7808,8 +8009,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7912,8 +8116,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8016,8 +8223,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8120,8 +8330,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8224,8 +8437,11 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -8250,8 +8466,8 @@
       <c r="J89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K89" s="3">
-        <v>0</v>
+      <c r="K89" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="L89" s="3">
         <v>0</v>
@@ -8328,8 +8544,11 @@
       <c r="AJ89" s="3">
         <v>0</v>
       </c>
+      <c r="AK89" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8366,8 +8585,9 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8392,8 +8612,8 @@
       <c r="J91" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
@@ -8470,8 +8690,11 @@
       <c r="AJ91" s="3">
         <v>0</v>
       </c>
+      <c r="AK91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8574,8 +8797,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8678,8 +8904,11 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8704,8 +8933,8 @@
       <c r="J94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
+      <c r="K94" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="L94" s="3">
         <v>0</v>
@@ -8782,8 +9011,11 @@
       <c r="AJ94" s="3">
         <v>0</v>
       </c>
+      <c r="AK94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8820,8 +9052,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8846,8 +9079,8 @@
       <c r="J96" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -8924,8 +9157,11 @@
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9028,8 +9264,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9132,8 +9371,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9236,8 +9478,11 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -9262,8 +9507,8 @@
       <c r="J100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
+      <c r="K100" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="L100" s="3">
         <v>0</v>
@@ -9340,8 +9585,11 @@
       <c r="AJ100" s="3">
         <v>0</v>
       </c>
+      <c r="AK100" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9366,8 +9614,8 @@
       <c r="J101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -9444,8 +9692,11 @@
       <c r="AJ101" s="3">
         <v>0</v>
       </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -9470,8 +9721,8 @@
       <c r="J102" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
+      <c r="K102" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="L102" s="3">
         <v>0</v>
@@ -9546,6 +9797,9 @@
         <v>0</v>
       </c>
       <c r="AJ102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/HUYA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HUYA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="92">
   <si>
     <t>HUYA</t>
   </si>
@@ -656,479 +656,492 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>207900</v>
+      </c>
+      <c r="E8" s="3">
         <v>204900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>219200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>212100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>208300</v>
       </c>
-      <c r="H8" s="3">
-        <v>222200</v>
-      </c>
       <c r="I8" s="3">
+        <v>215700</v>
+      </c>
+      <c r="J8" s="3">
         <v>228100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>251200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>285700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>302600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>328600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>316300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>342600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>387000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>423000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>425500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>374100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>416200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>414800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>397500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>380500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>379900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>353400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>307200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>249300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>218600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>178700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>149000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>121000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>110000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>86600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>68500</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>58000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>49300</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>28600</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>181900</v>
+      </c>
+      <c r="E9" s="3">
         <v>181600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>190200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>182600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>177800</v>
       </c>
-      <c r="H9" s="3">
-        <v>214100</v>
-      </c>
       <c r="I9" s="3">
+        <v>213600</v>
+      </c>
+      <c r="J9" s="3">
         <v>194800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>213500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>246500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>336600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>281300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>285800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>296200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>386800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>351300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>342000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>300300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>333100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>323300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>312700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>305600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>308100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>290000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>255900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>207500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>183900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>151600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>125100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>102200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>93900</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>75700</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>59900</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>55700</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>56300</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>40700</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>26000</v>
+      </c>
+      <c r="E10" s="3">
         <v>23400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>29000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>29600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>30500</v>
       </c>
-      <c r="H10" s="3">
-        <v>8100</v>
-      </c>
       <c r="I10" s="3">
+        <v>2100</v>
+      </c>
+      <c r="J10" s="3">
         <v>33300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>37600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>39200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-34000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>47300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>30500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>46400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>71600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>83500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>73800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>83200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>91400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>84700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>74900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>71800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>63400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>51300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>41800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>34700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>27100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>23900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>18800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>16000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>10900</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>8500</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>2300</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>-7000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>-12000</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1166,115 +1179,119 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>16900</v>
+        <v>17800</v>
       </c>
       <c r="E12" s="3">
+        <v>13400</v>
+      </c>
+      <c r="F12" s="3">
         <v>17900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>17700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>18700</v>
       </c>
-      <c r="H12" s="3">
-        <v>15000</v>
-      </c>
       <c r="I12" s="3">
+        <v>14500</v>
+      </c>
+      <c r="J12" s="3">
         <v>19600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>19900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>22300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>20900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>23700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>23400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>27300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>28300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>29300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>29900</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>28600</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>30000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>26900</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>26500</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>24600</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>27500</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>21100</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>16100</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>13800</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>11500</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>10400</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>8600</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>7400</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>6500</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>7300</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>5200</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>6200</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>7700</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1380,41 +1397,44 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
-        <v>20700</v>
+      <c r="D14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="E14" s="3">
+        <v>24200</v>
+      </c>
+      <c r="F14" s="3">
         <v>5200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>6200</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I14" s="3">
         <v>16100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>11100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>9000</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M14" s="3">
         <v>12700</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>16</v>
       </c>
@@ -1427,8 +1447,8 @@
       <c r="Q14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="R14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
@@ -1487,38 +1507,41 @@
       <c r="AK14" s="3">
         <v>0</v>
       </c>
+      <c r="AL14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>3500</v>
+        <v>2600</v>
       </c>
       <c r="E15" s="3">
+        <v>2600</v>
+      </c>
+      <c r="F15" s="3">
         <v>3600</v>
-      </c>
-      <c r="F15" s="3">
-        <v>3500</v>
       </c>
       <c r="G15" s="3">
         <v>3500</v>
       </c>
       <c r="H15" s="3">
+        <v>3500</v>
+      </c>
+      <c r="I15" s="3">
         <v>3600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>3500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>2800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>3700</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1594,8 +1617,11 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1630,222 +1656,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>217600</v>
+        <v>216100</v>
       </c>
       <c r="E17" s="3">
+        <v>214100</v>
+      </c>
+      <c r="F17" s="3">
         <v>223800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>215700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>213600</v>
       </c>
-      <c r="H17" s="3">
-        <v>264700</v>
-      </c>
       <c r="I17" s="3">
+        <v>256400</v>
+      </c>
+      <c r="J17" s="3">
         <v>232400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>255100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>294000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>400700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>327000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>327600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>351000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>450000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>411200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>399300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>350800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>390200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>381900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>370700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>359500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>364300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>343400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>296800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>244900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>215900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>179100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>151500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>117000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>110200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>91700</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>71000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>64100</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>69400</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>53400</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>-12700</v>
+        <v>-8200</v>
       </c>
       <c r="E18" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="F18" s="3">
         <v>-4600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-3600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-5300</v>
       </c>
-      <c r="H18" s="3">
-        <v>-42500</v>
-      </c>
       <c r="I18" s="3">
+        <v>-40700</v>
+      </c>
+      <c r="J18" s="3">
         <v>-4300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-4000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-8300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-98200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-11300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-8400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-63000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>11800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>26100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>23300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>26100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>32800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>26700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>21000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>15700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>10000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>10300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>4300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-2500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>4000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-5100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-2500</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-6100</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-20100</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>-24800</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1883,145 +1916,149 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>200</v>
+      </c>
+      <c r="E20" s="3">
         <v>100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>300</v>
       </c>
-      <c r="H20" s="3">
-        <v>-400</v>
-      </c>
       <c r="I20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="J20" s="3">
         <v>200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>14900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>9500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>8700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>9300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>8500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>14700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>8900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>9000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>10300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>11900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>11300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>12100</v>
-      </c>
-      <c r="X20" s="3">
-        <v>13600</v>
       </c>
       <c r="Y20" s="3">
         <v>13600</v>
       </c>
       <c r="Z20" s="3">
+        <v>13600</v>
+      </c>
+      <c r="AA20" s="3">
         <v>11600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>8300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>7700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>7100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-320100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>1000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>700</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>300</v>
-      </c>
-      <c r="AI20" s="3">
-        <v>100</v>
       </c>
       <c r="AJ20" s="3">
         <v>100</v>
       </c>
       <c r="AK20" s="3">
+        <v>100</v>
+      </c>
+      <c r="AL20" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>-9300</v>
+        <v>-5700</v>
       </c>
       <c r="E21" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="F21" s="3">
         <v>-1200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-2200</v>
       </c>
-      <c r="H21" s="3">
-        <v>-38600</v>
-      </c>
       <c r="I21" s="3">
+        <v>-36800</v>
+      </c>
+      <c r="J21" s="3">
         <v>-1100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-1500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-4500</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>16</v>
       </c>
@@ -2097,8 +2134,11 @@
       <c r="AK21" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AL21" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2126,8 +2166,8 @@
       <c r="K22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -2204,115 +2244,121 @@
       <c r="AK22" s="3">
         <v>0</v>
       </c>
+      <c r="AL22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-23200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>3800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>4400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>10500</v>
       </c>
-      <c r="H23" s="3">
-        <v>-39900</v>
-      </c>
       <c r="I23" s="3">
+        <v>-38100</v>
+      </c>
+      <c r="J23" s="3">
         <v>2000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>4000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>5800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-83300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>11000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-2500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-54500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>26500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>35000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>32300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>36300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>44700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>38000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>33100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>29300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>23600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>21900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>12600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>10300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>6700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-322600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>3900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-4300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-2200</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-6100</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-20000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-24800</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2323,86 +2369,86 @@
         <v>400</v>
       </c>
       <c r="F24" s="3">
+        <v>400</v>
+      </c>
+      <c r="G24" s="3">
         <v>300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
+        <v>600</v>
+      </c>
+      <c r="J24" s="3">
+        <v>500</v>
+      </c>
+      <c r="K24" s="3">
+        <v>800</v>
+      </c>
+      <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
+        <v>-800</v>
+      </c>
+      <c r="N24" s="3">
+        <v>2700</v>
+      </c>
+      <c r="O24" s="3">
         <v>200</v>
       </c>
-      <c r="I24" s="3">
-        <v>500</v>
-      </c>
-      <c r="J24" s="3">
-        <v>800</v>
-      </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
-      <c r="L24" s="3">
-        <v>-800</v>
-      </c>
-      <c r="M24" s="3">
-        <v>2700</v>
-      </c>
-      <c r="N24" s="3">
-        <v>200</v>
-      </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-11400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>5800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>8400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>5700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>5200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>7500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>7600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>5900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>4200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>4300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>3300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>2900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-4600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-1200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-600</v>
       </c>
-      <c r="AF24" s="3">
-        <v>0</v>
-      </c>
       <c r="AG24" s="3">
         <v>0</v>
       </c>
@@ -2418,8 +2464,11 @@
       <c r="AK24" s="3">
         <v>0</v>
       </c>
+      <c r="AL24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2525,222 +2574,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-23600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>3400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>4100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>9800</v>
       </c>
-      <c r="H26" s="3">
-        <v>-40100</v>
-      </c>
       <c r="I26" s="3">
+        <v>-38800</v>
+      </c>
+      <c r="J26" s="3">
         <v>1400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>3200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>5800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-82500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>8300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-2700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-43100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>20700</v>
-      </c>
-      <c r="R26" s="3">
-        <v>26700</v>
       </c>
       <c r="S26" s="3">
         <v>26700</v>
       </c>
       <c r="T26" s="3">
+        <v>26700</v>
+      </c>
+      <c r="U26" s="3">
         <v>31200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>37300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>30500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>27200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>25000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>19200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>18600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>9700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>15000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>7900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-321700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>4500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-4300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-2200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-6100</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-20000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-24800</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-23600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>3400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>4100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>9800</v>
       </c>
-      <c r="H27" s="3">
-        <v>-40100</v>
-      </c>
       <c r="I27" s="3">
+        <v>-38800</v>
+      </c>
+      <c r="J27" s="3">
         <v>1400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>3200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>5800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-82500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>8300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-2700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-43100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>74500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>26700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>26600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>35200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>37300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>30500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>27000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>24600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>19200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>18600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>9700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>14500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>7900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-310800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-71200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-5800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-2200</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-6100</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-20000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-24800</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2846,8 +2904,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2953,8 +3014,11 @@
       <c r="AK29" s="3">
         <v>0</v>
       </c>
+      <c r="AL29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3060,8 +3124,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3167,222 +3234,231 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-300</v>
       </c>
-      <c r="H32" s="3">
-        <v>400</v>
-      </c>
       <c r="I32" s="3">
+        <v>300</v>
+      </c>
+      <c r="J32" s="3">
         <v>-200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-14900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-9500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-8700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-9300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-8500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-14700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-8900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-9000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-10300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-11900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-11300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-12100</v>
-      </c>
-      <c r="X32" s="3">
-        <v>-13600</v>
       </c>
       <c r="Y32" s="3">
         <v>-13600</v>
       </c>
       <c r="Z32" s="3">
+        <v>-13600</v>
+      </c>
+      <c r="AA32" s="3">
         <v>-11600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-8300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-7700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-7100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>320100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-700</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-300</v>
-      </c>
-      <c r="AI32" s="3">
-        <v>-100</v>
       </c>
       <c r="AJ32" s="3">
         <v>-100</v>
       </c>
       <c r="AK32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AL32" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-23600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>4100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>9800</v>
       </c>
-      <c r="H33" s="3">
-        <v>-40100</v>
-      </c>
       <c r="I33" s="3">
+        <v>-38800</v>
+      </c>
+      <c r="J33" s="3">
         <v>1400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>3200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>5800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-82500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>8300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-2700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-43100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>74500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>26700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>26600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>35200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>37300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>30500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>27000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>24600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>19200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>18600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>9700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>14500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>7900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-310800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-71200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-5800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-2200</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-6100</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-20000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-24800</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3488,227 +3564,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-23600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>4100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>9800</v>
       </c>
-      <c r="H35" s="3">
-        <v>-40100</v>
-      </c>
       <c r="I35" s="3">
+        <v>-38800</v>
+      </c>
+      <c r="J35" s="3">
         <v>1400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>3200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>5800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-82500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>8300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-2700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-43100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>74500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>26700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>26600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>35200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>37300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>30500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>27000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>24600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>19200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>18600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>9700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>14500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>7900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-310800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-71200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-5800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-2200</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-6100</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-20000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-24800</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3746,8 +3831,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3785,98 +3871,99 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>40900</v>
+      </c>
+      <c r="E41" s="3">
         <v>162900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>156200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>138400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>75100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>72200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>113100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>95400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>282600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>97900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>149600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>287500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>205800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1397500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1437100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1383600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1370200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1290200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1341400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1230000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1243000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1209800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1322900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1254600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>869400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>826800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>805000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>770000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>584200</v>
       </c>
-      <c r="AF41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AG41" s="3" t="s">
         <v>16</v>
       </c>
@@ -3892,95 +3979,98 @@
       <c r="AK41" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AL41" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>684600</v>
+      </c>
+      <c r="E42" s="3">
         <v>558300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>780200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>767600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>918900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>966200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1049400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1148700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1139800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1271800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1322300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1202300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1250300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>112500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>143500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>158700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>159500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>168000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>249800</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>353400</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>384600</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>341800</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>165000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>137700</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>97600</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>43600</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>17000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>21300</v>
       </c>
-      <c r="AE42" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AF42" s="3" t="s">
         <v>16</v>
       </c>
@@ -3999,98 +4089,101 @@
       <c r="AK42" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AL42" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>10400</v>
+        <v>15400</v>
       </c>
       <c r="E43" s="3">
+        <v>60000</v>
+      </c>
+      <c r="F43" s="3">
         <v>12800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>9700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>10300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>58000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>23800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>17100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>21600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>20300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>21600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>30400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>30500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>32600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>40700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>41000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>33800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>18900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>19000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>17100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>17600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>17500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>25700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>14600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>33500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>41100</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>18500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>19900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>19800</v>
       </c>
-      <c r="AF43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AG43" s="3" t="s">
         <v>16</v>
       </c>
@@ -4106,8 +4199,11 @@
       <c r="AK43" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AL43" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4135,8 +4231,8 @@
       <c r="K44" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -4213,98 +4309,101 @@
       <c r="AK44" s="3">
         <v>0</v>
       </c>
+      <c r="AL44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>71700</v>
+        <v>113000</v>
       </c>
       <c r="E45" s="3">
+        <v>50600</v>
+      </c>
+      <c r="F45" s="3">
         <v>146300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>127500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>111300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>50500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>91000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>81800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>83000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>90400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>140500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>111200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>129200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>99300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>133300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>107700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>94800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>91900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>71800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>61100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>63100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>61900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>68100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>46800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>35500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>46400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>32700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>24700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>12200</v>
       </c>
-      <c r="AF45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AG45" s="3" t="s">
         <v>16</v>
       </c>
@@ -4320,98 +4419,101 @@
       <c r="AK45" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AL45" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>856300</v>
+      </c>
+      <c r="E46" s="3">
         <v>834100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1098100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1045400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1118300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1149400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1280000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1345900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1529300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1480400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1633900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1631500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1615700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1641800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1754600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1690900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1658300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1568900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1682100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1661600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1708300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1630900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1581700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1453600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1035900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>957800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>873300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>835800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>616200</v>
       </c>
-      <c r="AF46" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AG46" s="3" t="s">
         <v>16</v>
       </c>
@@ -4427,98 +4529,101 @@
       <c r="AK46" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AL46" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>64000</v>
+      </c>
+      <c r="E47" s="3">
         <v>261800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>301700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>310100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>414800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>466100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>407500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>380700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>227700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>279000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>176400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>125000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>120300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>83900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>82800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>72500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>73200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>65000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>66400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>63400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>63500</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>58400</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>57400</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>56200</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>50200</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>31900</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>29800</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>30400</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>100</v>
       </c>
-      <c r="AF47" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AG47" s="3" t="s">
         <v>16</v>
       </c>
@@ -4534,98 +4639,101 @@
       <c r="AK47" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AL47" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>114500</v>
+      </c>
+      <c r="E48" s="3">
         <v>112800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>113400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>106000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>103500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>99500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>80000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>79200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>81100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>77000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>71700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>70800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>64600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>65400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>69300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>26100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>23300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>25300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>30000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>30900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>29100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>30700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>33500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>33600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>28900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>12700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>11700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>10000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>5500</v>
       </c>
-      <c r="AF48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AG48" s="3" t="s">
         <v>16</v>
       </c>
@@ -4641,98 +4749,101 @@
       <c r="AK48" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AL48" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>83700</v>
+      </c>
+      <c r="E49" s="3">
         <v>84500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>83600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>83000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>84400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>87300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>5500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>6500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>7600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>92500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>8700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>10000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>11000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>11600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>12900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>13600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>7300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>8700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>10700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>9700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>7000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>6900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>7400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>6900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>7400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>7500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>7000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>5200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>800</v>
       </c>
-      <c r="AF49" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AG49" s="3" t="s">
         <v>16</v>
       </c>
@@ -4748,8 +4859,11 @@
       <c r="AK49" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AL49" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4855,8 +4969,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4962,98 +5079,101 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>17600</v>
+        <v>151700</v>
       </c>
       <c r="E52" s="3">
         <v>17600</v>
       </c>
       <c r="F52" s="3">
+        <v>17600</v>
+      </c>
+      <c r="G52" s="3">
         <v>16700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>20000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>20300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>16800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>14600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>13700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>15600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>19100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>25900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>29600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>23600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>25200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>64800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>63900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>59500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>21700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>28900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>27700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>23200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>25400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>23300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>20600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>22000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>10500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>2200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>5400</v>
       </c>
-      <c r="AF52" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AG52" s="3" t="s">
         <v>16</v>
       </c>
@@ -5069,8 +5189,11 @@
       <c r="AK52" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AL52" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5176,98 +5299,101 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1270000</v>
+      </c>
+      <c r="E54" s="3">
         <v>1310800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1614400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1561100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1741000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1822700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1789900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1826800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1859400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1944500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1909800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1863200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1841100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1826300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1944700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1868000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1826100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1727600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1810900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1794500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1835600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1750200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1705400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1573700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1143100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1032000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>932300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>883600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>627900</v>
       </c>
-      <c r="AF54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AG54" s="3" t="s">
         <v>16</v>
       </c>
@@ -5283,8 +5409,11 @@
       <c r="AK54" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AL54" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5322,8 +5451,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5361,97 +5491,98 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E57" s="3">
         <v>9100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>9700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>7600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5200</v>
-      </c>
-      <c r="O57" s="3">
-        <v>1700</v>
       </c>
       <c r="P57" s="3">
         <v>1700</v>
       </c>
       <c r="Q57" s="3">
+        <v>1700</v>
+      </c>
+      <c r="R57" s="3">
         <v>2700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>8100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>5100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>3000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1000</v>
       </c>
-      <c r="AE57" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF57" s="3" t="s">
-        <v>16</v>
+      <c r="AF57" s="3">
+        <v>0</v>
       </c>
       <c r="AG57" s="3" t="s">
         <v>16</v>
@@ -5468,19 +5599,22 @@
       <c r="AK57" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AL57" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E58" s="3">
         <v>3900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>4200</v>
-      </c>
-      <c r="F58" s="3">
-        <v>4500</v>
       </c>
       <c r="G58" s="3">
         <v>4500</v>
@@ -5489,17 +5623,17 @@
         <v>4500</v>
       </c>
       <c r="I58" s="3">
+        <v>4500</v>
+      </c>
+      <c r="J58" s="3">
         <v>1400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3300</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -5575,98 +5709,101 @@
       <c r="AK58" s="3">
         <v>0</v>
       </c>
+      <c r="AL58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>66000</v>
+        <v>392100</v>
       </c>
       <c r="E59" s="3">
+        <v>83700</v>
+      </c>
+      <c r="F59" s="3">
         <v>315800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>65600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>220700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>106600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>72200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>72900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>74000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>314800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>304700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>310800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>339000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>353200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>370200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>355100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>339900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>330600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>340500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>362100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>368100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>376200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>337600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>298300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>242600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>199100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>151400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>128700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>244600</v>
       </c>
-      <c r="AF59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AG59" s="3" t="s">
         <v>16</v>
       </c>
@@ -5682,98 +5819,101 @@
       <c r="AK59" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AL59" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>548900</v>
+      </c>
+      <c r="E60" s="3">
         <v>265500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>514300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>244900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>405600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>304800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>248200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>262400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>267800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>318000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>307600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>316000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>340700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>354900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>372900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>363200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>341000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>332000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>343400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>367200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>368500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>376700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>339300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>301100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>245600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>200500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>154000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>129600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>244600</v>
       </c>
-      <c r="AF60" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AG60" s="3" t="s">
         <v>16</v>
       </c>
@@ -5789,38 +5929,41 @@
       <c r="AK60" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AL60" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E61" s="3">
         <v>2700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>5700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>6800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1000</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -5896,8 +6039,11 @@
       <c r="AK61" s="3">
         <v>0</v>
       </c>
+      <c r="AL61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5925,69 +6071,69 @@
       <c r="K62" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M62" s="3">
         <v>18000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>16900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>19900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>23700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>23200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>28600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>34800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>35700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>34700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>35000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>37800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>38500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>36200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>35300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>33300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>27800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>11700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>9600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>10700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>7000</v>
       </c>
-      <c r="AF62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AG62" s="3" t="s">
         <v>16</v>
       </c>
@@ -6003,8 +6149,11 @@
       <c r="AK62" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AL62" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6110,8 +6259,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6217,8 +6369,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6324,98 +6479,101 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>558800</v>
+      </c>
+      <c r="E66" s="3">
         <v>276400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>527400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>258600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>422800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>324300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>259200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>274400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>281900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>336000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>324500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>335900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>364300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>378200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>401500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>398000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>376600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>366600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>378400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>405000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>407000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>412900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>374500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>334300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>273300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>212200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>163700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>140300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>251600</v>
       </c>
-      <c r="AF66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AG66" s="3" t="s">
         <v>16</v>
       </c>
@@ -6431,8 +6589,11 @@
       <c r="AK66" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AL66" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6470,8 +6631,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6577,8 +6739,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6684,8 +6849,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6771,11 +6939,11 @@
         <v>0</v>
       </c>
       <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF70" s="3">
         <v>434700</v>
       </c>
-      <c r="AF70" s="3">
-        <v>0</v>
-      </c>
       <c r="AG70" s="3">
         <v>0</v>
       </c>
@@ -6791,8 +6959,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6898,98 +7069,101 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-272400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-271000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-257400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-251700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-257400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-272200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-217100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-220100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-235800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-243200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-157500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-166900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-164200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-162300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-123000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-199500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-226300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-245200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-296800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-224900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-276600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-295900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-324700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-336800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-355400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-347000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-348400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-365300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-59100</v>
       </c>
-      <c r="AF72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AG72" s="3" t="s">
         <v>16</v>
       </c>
@@ -7005,8 +7179,11 @@
       <c r="AK72" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AL72" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7112,8 +7289,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7219,8 +7399,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7326,98 +7509,101 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>711200</v>
+      </c>
+      <c r="E76" s="3">
         <v>1034500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1087100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1302500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1318100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1498300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1530700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1552400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1577600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1608500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1585200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1527300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1476700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1448100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1543200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1470100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1449400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1360900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1432500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1389500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1428600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1337300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1330900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1239400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>869700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>819800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>768600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>743300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>-58300</v>
       </c>
-      <c r="AF76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AG76" s="3" t="s">
         <v>16</v>
       </c>
@@ -7433,8 +7619,11 @@
       <c r="AK76" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AL76" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7540,227 +7729,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-23600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>4100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>9800</v>
       </c>
-      <c r="H81" s="3">
-        <v>-40100</v>
-      </c>
       <c r="I81" s="3">
+        <v>-38800</v>
+      </c>
+      <c r="J81" s="3">
         <v>1400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>3200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>5800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-82500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>8300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-2700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-43100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>74500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>26700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>26600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>35200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>37300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>30500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>27000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>24600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>19200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>18600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>9700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>14500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>7900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-310800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-71200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-5800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-2200</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-6100</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-20000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-24800</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7798,8 +7996,9 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7827,8 +8026,8 @@
       <c r="K83" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
+      <c r="L83" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="M83" s="3">
         <v>0</v>
@@ -7905,8 +8104,11 @@
       <c r="AK83" s="3">
         <v>0</v>
       </c>
+      <c r="AL83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8012,8 +8214,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8119,8 +8324,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8226,8 +8434,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8333,8 +8544,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8440,8 +8654,11 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -8469,8 +8686,8 @@
       <c r="K89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L89" s="3">
-        <v>0</v>
+      <c r="L89" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="M89" s="3">
         <v>0</v>
@@ -8547,8 +8764,11 @@
       <c r="AK89" s="3">
         <v>0</v>
       </c>
+      <c r="AL89" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8586,8 +8806,9 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8615,8 +8836,8 @@
       <c r="K91" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="L91" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -8693,8 +8914,11 @@
       <c r="AK91" s="3">
         <v>0</v>
       </c>
+      <c r="AL91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8800,8 +9024,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8907,8 +9134,11 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8936,8 +9166,8 @@
       <c r="K94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
+      <c r="L94" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="M94" s="3">
         <v>0</v>
@@ -9014,8 +9244,11 @@
       <c r="AK94" s="3">
         <v>0</v>
       </c>
+      <c r="AL94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9053,8 +9286,9 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9082,8 +9316,8 @@
       <c r="K96" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -9160,8 +9394,11 @@
       <c r="AK96" s="3">
         <v>0</v>
       </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9267,8 +9504,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9374,8 +9614,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9481,8 +9724,11 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -9510,8 +9756,8 @@
       <c r="K100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
+      <c r="L100" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="M100" s="3">
         <v>0</v>
@@ -9588,8 +9834,11 @@
       <c r="AK100" s="3">
         <v>0</v>
       </c>
+      <c r="AL100" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9617,8 +9866,8 @@
       <c r="K101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -9695,8 +9944,11 @@
       <c r="AK101" s="3">
         <v>0</v>
       </c>
+      <c r="AL101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -9724,8 +9976,8 @@
       <c r="K102" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
+      <c r="L102" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="M102" s="3">
         <v>0</v>
@@ -9800,6 +10052,9 @@
         <v>0</v>
       </c>
       <c r="AK102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/HUYA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HUYA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="92">
   <si>
     <t>HUYA</t>
   </si>
@@ -656,492 +656,505 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="3">
         <v>207900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>204900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>219200</v>
       </c>
-      <c r="G8" s="3">
-        <v>212100</v>
-      </c>
-      <c r="H8" s="3">
+      <c r="H8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" s="3">
         <v>208300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>215700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>228100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>251200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>285700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>302600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>328600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>316300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>342600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>387000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>423000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>425500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>374100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>416200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>414800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>397500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>380500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>379900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>353400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>307200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>249300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>218600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>178700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>149000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>121000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>110000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>86600</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>68500</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>58000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>49300</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>28600</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="3">
         <v>181900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>181600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>190200</v>
       </c>
-      <c r="G9" s="3">
-        <v>182600</v>
-      </c>
-      <c r="H9" s="3">
+      <c r="H9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I9" s="3">
         <v>177800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>213600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>194800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>213500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>246500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>336600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>281300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>285800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>296200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>386800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>351300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>342000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>300300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>333100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>323300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>312700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>305600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>308100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>290000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>255900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>207500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>183900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>151600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>125100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>102200</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>93900</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>75700</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>59900</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>55700</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>56300</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>40700</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="3">
         <v>26000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>23400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>29000</v>
       </c>
-      <c r="G10" s="3">
-        <v>29600</v>
-      </c>
-      <c r="H10" s="3">
+      <c r="H10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I10" s="3">
         <v>30500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>33300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>37600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>39200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-34000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>47300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>30500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>46400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>71600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>83500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>73800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>83200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>91400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>84700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>74900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>71800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>63400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>51300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>41800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>34700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>27100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>23900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>18800</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>16000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>10900</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>8500</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>2300</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>-7000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>-12000</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1180,118 +1193,122 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" s="3">
         <v>17800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>13400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>17900</v>
       </c>
-      <c r="G12" s="3">
-        <v>17700</v>
-      </c>
-      <c r="H12" s="3">
+      <c r="H12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I12" s="3">
         <v>18700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>14500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>19600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>19900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>22300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>20900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>23700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>23400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>27300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>28300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>29300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>29900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>28600</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>30000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>26900</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>26500</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>24600</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>27500</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>21100</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>16100</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>13800</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>11500</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>10400</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>8600</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>7400</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>6500</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>7300</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>5200</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>6200</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>7700</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1400,44 +1417,47 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14" s="3">
         <v>24200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>5200</v>
       </c>
-      <c r="G14" s="3">
-        <v>6200</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J14" s="3">
         <v>16100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>11100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>9000</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N14" s="3">
         <v>12700</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>16</v>
       </c>
@@ -1450,8 +1470,8 @@
       <c r="R14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
@@ -1510,41 +1530,44 @@
       <c r="AL14" s="3">
         <v>0</v>
       </c>
+      <c r="AM14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>2600</v>
+        <v>0</v>
       </c>
       <c r="E15" s="3">
         <v>2600</v>
       </c>
       <c r="F15" s="3">
+        <v>2600</v>
+      </c>
+      <c r="G15" s="3">
         <v>3600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3">
         <v>3500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
+        <v>3600</v>
+      </c>
+      <c r="K15" s="3">
         <v>3500</v>
       </c>
-      <c r="I15" s="3">
-        <v>3600</v>
-      </c>
-      <c r="J15" s="3">
-        <v>3500</v>
-      </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>2800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>3700</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1620,8 +1643,11 @@
       <c r="AL15" s="3">
         <v>0</v>
       </c>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1657,228 +1683,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" s="3">
         <v>216100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>214100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>223800</v>
       </c>
-      <c r="G17" s="3">
-        <v>215700</v>
-      </c>
-      <c r="H17" s="3">
+      <c r="H17" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I17" s="3">
         <v>213600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>256400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>232400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>255100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>294000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>400700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>327000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>327600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>351000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>450000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>411200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>399300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>350800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>390200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>381900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>370700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>359500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>364300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>343400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>296800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>244900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>215900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>179100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>151500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>117000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>110200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>91700</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>71000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>64100</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>69400</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>53400</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18" s="3">
         <v>-8200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-9200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-4600</v>
       </c>
-      <c r="G18" s="3">
-        <v>-3600</v>
-      </c>
-      <c r="H18" s="3">
+      <c r="H18" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I18" s="3">
         <v>-5300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-40700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-4300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-4000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-8300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-98200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-11300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-8400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-63000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>11800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>26100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>23300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>26100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>32800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>26700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>21000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>15700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>10000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>10300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>4300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>2700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-2500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>4000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-5100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-2500</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-6100</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>-20100</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>-24800</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1917,151 +1950,155 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E20" s="3">
         <v>200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I20" s="3">
+        <v>300</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="K20" s="3">
+        <v>200</v>
+      </c>
+      <c r="L20" s="3">
+        <v>400</v>
+      </c>
+      <c r="M20" s="3">
         <v>-100</v>
       </c>
-      <c r="H20" s="3">
-        <v>300</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-300</v>
-      </c>
-      <c r="J20" s="3">
-        <v>200</v>
-      </c>
-      <c r="K20" s="3">
-        <v>400</v>
-      </c>
-      <c r="L20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>14900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>9500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>8700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>9300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>8500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>14700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>8900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>9000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>10300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>11900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>11300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>12100</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>13600</v>
       </c>
       <c r="Z20" s="3">
         <v>13600</v>
       </c>
       <c r="AA20" s="3">
+        <v>13600</v>
+      </c>
+      <c r="AB20" s="3">
         <v>11600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>8300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>7700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>7100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-320100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-200</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>1000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>700</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>300</v>
-      </c>
-      <c r="AJ20" s="3">
-        <v>100</v>
       </c>
       <c r="AK20" s="3">
         <v>100</v>
       </c>
       <c r="AL20" s="3">
+        <v>100</v>
+      </c>
+      <c r="AM20" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3">
         <v>-5700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-6600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-1200</v>
       </c>
-      <c r="G21" s="3">
-        <v>-100</v>
-      </c>
       <c r="H21" s="3">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3">
         <v>-2200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-36800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-1100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-1500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-4500</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>16</v>
       </c>
@@ -2137,8 +2174,11 @@
       <c r="AL21" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AM21" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2169,8 +2209,8 @@
       <c r="L22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -2247,123 +2287,129 @@
       <c r="AL22" s="3">
         <v>0</v>
       </c>
+      <c r="AM22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E23" s="3">
         <v>600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-23200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>3800</v>
       </c>
-      <c r="G23" s="3">
-        <v>4400</v>
-      </c>
-      <c r="H23" s="3">
+      <c r="H23" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I23" s="3">
         <v>10500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-38100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>4000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>5800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-83300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>11000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-54500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>26500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>35000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>32300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>36300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>44700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>38000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>33100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>29300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>23600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>21900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>12600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>10300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>6700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-322600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>3900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-4300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-2200</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-6100</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-20000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>-24800</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>400</v>
+      <c r="D24" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="E24" s="3">
         <v>400</v>
@@ -2372,86 +2418,86 @@
         <v>400</v>
       </c>
       <c r="G24" s="3">
-        <v>300</v>
-      </c>
-      <c r="H24" s="3">
+        <v>400</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I24" s="3">
         <v>700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>800</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>-800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-11400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>5800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>8400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>5700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>5200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>7500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>7600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>5900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>4200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>4300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>3300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>2900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-4600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-1200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-600</v>
       </c>
-      <c r="AG24" s="3">
-        <v>0</v>
-      </c>
       <c r="AH24" s="3">
         <v>0</v>
       </c>
@@ -2467,8 +2513,11 @@
       <c r="AL24" s="3">
         <v>0</v>
       </c>
+      <c r="AM24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2577,228 +2626,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E26" s="3">
         <v>100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-23600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>3400</v>
       </c>
-      <c r="G26" s="3">
-        <v>4100</v>
-      </c>
-      <c r="H26" s="3">
+      <c r="H26" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I26" s="3">
         <v>9800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-38800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>5800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-82500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>8300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-2700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-43100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>20700</v>
-      </c>
-      <c r="S26" s="3">
-        <v>26700</v>
       </c>
       <c r="T26" s="3">
         <v>26700</v>
       </c>
       <c r="U26" s="3">
+        <v>26700</v>
+      </c>
+      <c r="V26" s="3">
         <v>31200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>37300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>30500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>27200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>25000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>19200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>18600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>9700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>15000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>7900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-321700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>4500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-4300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-2200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-6100</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-20000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>-24800</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E27" s="3">
         <v>100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-23600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>3400</v>
       </c>
-      <c r="G27" s="3">
-        <v>4100</v>
-      </c>
-      <c r="H27" s="3">
+      <c r="H27" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I27" s="3">
         <v>9800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-38800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>5800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-82500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>8300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-2700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-43100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>74500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>26700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>26600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>35200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>37300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>30500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>27000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>24600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>19200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>18600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>9700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>14500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>7900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-310800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-71200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-5800</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-2200</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-6100</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-20000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>-24800</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2907,8 +2965,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3017,8 +3078,11 @@
       <c r="AL29" s="3">
         <v>0</v>
       </c>
+      <c r="AM29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3127,8 +3191,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3237,228 +3304,237 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E32" s="3">
         <v>-200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="J32" s="3">
+        <v>300</v>
+      </c>
+      <c r="K32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="L32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="M32" s="3">
         <v>100</v>
       </c>
-      <c r="H32" s="3">
-        <v>-300</v>
-      </c>
-      <c r="I32" s="3">
-        <v>300</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-200</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-400</v>
-      </c>
-      <c r="L32" s="3">
-        <v>100</v>
-      </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-14900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-9500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-8700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-9300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-8500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-14700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-8900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-9000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-10300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-11900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-11300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-12100</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>-13600</v>
       </c>
       <c r="Z32" s="3">
         <v>-13600</v>
       </c>
       <c r="AA32" s="3">
+        <v>-13600</v>
+      </c>
+      <c r="AB32" s="3">
         <v>-11600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-8300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-7700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-7100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>320100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>200</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-700</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-300</v>
-      </c>
-      <c r="AJ32" s="3">
-        <v>-100</v>
       </c>
       <c r="AK32" s="3">
         <v>-100</v>
       </c>
       <c r="AL32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AM32" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E33" s="3">
         <v>100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-23600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>3400</v>
       </c>
-      <c r="G33" s="3">
-        <v>4100</v>
-      </c>
-      <c r="H33" s="3">
+      <c r="H33" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I33" s="3">
         <v>9800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-38800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>3200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>5800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-82500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>8300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-2700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-43100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>74500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>26700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>26600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>35200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>37300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>30500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>27000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>24600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>19200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>18600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>9700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>14500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>7900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-310800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-71200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-700</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-5800</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-2200</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-6100</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-20000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>-24800</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3567,233 +3643,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E35" s="3">
         <v>100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-23600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>3400</v>
       </c>
-      <c r="G35" s="3">
-        <v>4100</v>
-      </c>
-      <c r="H35" s="3">
+      <c r="H35" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I35" s="3">
         <v>9800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-38800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>3200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>5800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-82500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>8300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-2700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-43100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>74500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>26700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>26600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>35200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>37300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>30500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>27000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>24600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>19200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>18600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>9700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>14500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>7900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-310800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-71200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-700</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-5800</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-2200</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-6100</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-20000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>-24800</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3832,8 +3917,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3872,101 +3958,102 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3">
+      <c r="D41" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E41" s="3">
         <v>40900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>162900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>156200</v>
       </c>
-      <c r="G41" s="3">
-        <v>138400</v>
-      </c>
-      <c r="H41" s="3">
+      <c r="H41" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I41" s="3">
         <v>75100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>72200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>113100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>95400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>282600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>97900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>149600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>287500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>205800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1397500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1437100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1383600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1370200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1290200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1341400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1230000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1243000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1209800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1322900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1254600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>869400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>826800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>805000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>770000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>584200</v>
       </c>
-      <c r="AG41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AH41" s="3" t="s">
         <v>16</v>
       </c>
@@ -3982,98 +4069,101 @@
       <c r="AL41" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AM41" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>684600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>558300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>780200</v>
       </c>
-      <c r="G42" s="3">
-        <v>767600</v>
-      </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>918900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>966200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1049400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1148700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1139800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1271800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1322300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1202300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1250300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>112500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>143500</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>158700</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>159500</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>168000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>249800</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>353400</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>384600</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>341800</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>165000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>137700</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>97600</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>43600</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>17000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>21300</v>
       </c>
-      <c r="AF42" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AG42" s="3" t="s">
         <v>16</v>
       </c>
@@ -4092,101 +4182,104 @@
       <c r="AL42" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AM42" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E43" s="3">
         <v>15400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>60000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>12800</v>
       </c>
-      <c r="G43" s="3">
-        <v>9700</v>
-      </c>
-      <c r="H43" s="3">
+      <c r="H43" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I43" s="3">
         <v>10300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>58000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>23800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>17100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>21600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>20300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>21600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>30400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>30500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>32600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>40700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>41000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>33800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>18900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>19000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>17100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>17600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>17500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>25700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>14600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>33500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>41100</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>18500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>19900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>19800</v>
       </c>
-      <c r="AG43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AH43" s="3" t="s">
         <v>16</v>
       </c>
@@ -4202,8 +4295,11 @@
       <c r="AL43" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AM43" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4234,8 +4330,8 @@
       <c r="L44" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -4312,101 +4408,104 @@
       <c r="AL44" s="3">
         <v>0</v>
       </c>
+      <c r="AM44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E45" s="3">
         <v>113000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>50600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>146300</v>
       </c>
-      <c r="G45" s="3">
-        <v>127500</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I45" s="3">
         <v>111300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>50500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>91000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>81800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>83000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>90400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>140500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>111200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>129200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>99300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>133300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>107700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>94800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>91900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>71800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>61100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>63100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>61900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>68100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>46800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>35500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>46400</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>32700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>24700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>12200</v>
       </c>
-      <c r="AG45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AH45" s="3" t="s">
         <v>16</v>
       </c>
@@ -4422,101 +4521,104 @@
       <c r="AL45" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AM45" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3">
+      <c r="D46" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E46" s="3">
         <v>856300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>834100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1098100</v>
       </c>
-      <c r="G46" s="3">
-        <v>1045400</v>
-      </c>
-      <c r="H46" s="3">
+      <c r="H46" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I46" s="3">
         <v>1118300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1149400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1280000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1345900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1529300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1480400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1633900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1631500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1615700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1641800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1754600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1690900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1658300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1568900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1682100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1661600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1708300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1630900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1581700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1453600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1035900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>957800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>873300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>835800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>616200</v>
       </c>
-      <c r="AG46" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AH46" s="3" t="s">
         <v>16</v>
       </c>
@@ -4532,101 +4634,104 @@
       <c r="AL46" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AM46" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>64000</v>
+      <c r="D47" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="E47" s="3">
+        <v>200400</v>
+      </c>
+      <c r="F47" s="3">
         <v>261800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>301700</v>
       </c>
-      <c r="G47" s="3">
-        <v>310100</v>
-      </c>
-      <c r="H47" s="3">
+      <c r="H47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I47" s="3">
         <v>414800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>466100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>407500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>380700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>227700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>279000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>176400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>125000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>120300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>83900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>82800</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>72500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>73200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>65000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>66400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>63400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>63500</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>58400</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>57400</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>56200</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>50200</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>31900</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>29800</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>30400</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>100</v>
       </c>
-      <c r="AG47" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AH47" s="3" t="s">
         <v>16</v>
       </c>
@@ -4642,101 +4747,104 @@
       <c r="AL47" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AM47" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E48" s="3">
         <v>114500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>112800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>113400</v>
       </c>
-      <c r="G48" s="3">
-        <v>106000</v>
-      </c>
-      <c r="H48" s="3">
+      <c r="H48" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I48" s="3">
         <v>103500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>99500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>80000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>79200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>81100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>77000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>71700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>70800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>64600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>65400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>69300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>26100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>23300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>25300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>30000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>30900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>29100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>30700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>33500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>33600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>28900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>12700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>11700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>10000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>5500</v>
       </c>
-      <c r="AG48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AH48" s="3" t="s">
         <v>16</v>
       </c>
@@ -4752,101 +4860,104 @@
       <c r="AL48" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AM48" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3">
+      <c r="D49" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E49" s="3">
         <v>83700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>84500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>83600</v>
       </c>
-      <c r="G49" s="3">
-        <v>83000</v>
-      </c>
-      <c r="H49" s="3">
+      <c r="H49" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I49" s="3">
         <v>84400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>87300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>5500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>6500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>7600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>92500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>8700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>10000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>11000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>11600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>12900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>13600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>7300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>8700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>10700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>9700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>7000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>6900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>7400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>6900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>7400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>7500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>7000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>5200</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>800</v>
       </c>
-      <c r="AG49" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AH49" s="3" t="s">
         <v>16</v>
       </c>
@@ -4862,8 +4973,11 @@
       <c r="AL49" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AM49" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4972,8 +5086,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5082,101 +5199,104 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>151700</v>
+      <c r="D52" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="E52" s="3">
-        <v>17600</v>
+        <v>15200</v>
       </c>
       <c r="F52" s="3">
         <v>17600</v>
       </c>
       <c r="G52" s="3">
-        <v>16700</v>
-      </c>
-      <c r="H52" s="3">
+        <v>17600</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I52" s="3">
         <v>20000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>20300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>16800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>14600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>13700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>15600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>19100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>25900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>29600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>23600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>25200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>64800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>63900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>59500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>21700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>28900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>27700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>23200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>25400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>23300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>20600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>22000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>10500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>2200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>5400</v>
       </c>
-      <c r="AG52" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AH52" s="3" t="s">
         <v>16</v>
       </c>
@@ -5192,8 +5312,11 @@
       <c r="AL52" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AM52" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5302,101 +5425,104 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3">
+      <c r="D54" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E54" s="3">
         <v>1270000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1310800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1614400</v>
       </c>
-      <c r="G54" s="3">
-        <v>1561100</v>
-      </c>
-      <c r="H54" s="3">
+      <c r="H54" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I54" s="3">
         <v>1741000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1822700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1789900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1826800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1859400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1944500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1909800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1863200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1841100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1826300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1944700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1868000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1826100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1727600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1810900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1794500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1835600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1750200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1705400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1573700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1143100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1032000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>932300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>883600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>627900</v>
       </c>
-      <c r="AG54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AH54" s="3" t="s">
         <v>16</v>
       </c>
@@ -5412,8 +5538,11 @@
       <c r="AL54" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AM54" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5452,8 +5581,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5492,100 +5622,101 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D57" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E57" s="3">
         <v>3300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>9100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>9700</v>
       </c>
-      <c r="G57" s="3">
-        <v>2500</v>
-      </c>
-      <c r="H57" s="3">
+      <c r="H57" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I57" s="3">
         <v>4900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>7600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5200</v>
-      </c>
-      <c r="P57" s="3">
-        <v>1700</v>
       </c>
       <c r="Q57" s="3">
         <v>1700</v>
       </c>
       <c r="R57" s="3">
+        <v>1700</v>
+      </c>
+      <c r="S57" s="3">
         <v>2700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>8100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>5100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>3000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1000</v>
       </c>
-      <c r="AF57" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG57" s="3" t="s">
-        <v>16</v>
+      <c r="AG57" s="3">
+        <v>0</v>
       </c>
       <c r="AH57" s="3" t="s">
         <v>16</v>
@@ -5602,41 +5733,44 @@
       <c r="AL57" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AM57" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
+      <c r="D58" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E58" s="3">
         <v>3800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>4200</v>
       </c>
-      <c r="G58" s="3">
-        <v>4500</v>
-      </c>
-      <c r="H58" s="3">
-        <v>4500</v>
+      <c r="H58" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="I58" s="3">
         <v>4500</v>
       </c>
       <c r="J58" s="3">
+        <v>4500</v>
+      </c>
+      <c r="K58" s="3">
         <v>1400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3300</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
@@ -5712,101 +5846,104 @@
       <c r="AL58" s="3">
         <v>0</v>
       </c>
+      <c r="AM58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E59" s="3">
         <v>392100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>83700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>315800</v>
       </c>
-      <c r="G59" s="3">
-        <v>65600</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="H59" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I59" s="3">
         <v>220700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>106600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>72200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>72900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>74000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>314800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>304700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>310800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>339000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>353200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>370200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>355100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>339900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>330600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>340500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>362100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>368100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>376200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>337600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>298300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>242600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>199100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>151400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>128700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>244600</v>
       </c>
-      <c r="AG59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AH59" s="3" t="s">
         <v>16</v>
       </c>
@@ -5822,101 +5959,104 @@
       <c r="AL59" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AM59" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
+      <c r="D60" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E60" s="3">
         <v>548900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>265500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>514300</v>
       </c>
-      <c r="G60" s="3">
-        <v>244900</v>
-      </c>
-      <c r="H60" s="3">
+      <c r="H60" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I60" s="3">
         <v>405600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>304800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>248200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>262400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>267800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>318000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>307600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>316000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>340700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>354900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>372900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>363200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>341000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>332000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>343400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>367200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>368500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>376700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>339300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>301100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>245600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>200500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>154000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>129600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>244600</v>
       </c>
-      <c r="AG60" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AH60" s="3" t="s">
         <v>16</v>
       </c>
@@ -5932,41 +6072,44 @@
       <c r="AL60" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AM60" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3">
         <v>1900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3500</v>
       </c>
-      <c r="G61" s="3">
-        <v>4600</v>
-      </c>
       <c r="H61" s="3">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
         <v>5700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>6800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1000</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -6042,8 +6185,11 @@
       <c r="AL61" s="3">
         <v>0</v>
       </c>
+      <c r="AM61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -6074,69 +6220,69 @@
       <c r="L62" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N62" s="3">
         <v>18000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>16900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>19900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>23700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>23200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>28600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>34800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>35700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>34700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>35000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>37800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>38500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>36200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>35300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>33300</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>27800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>11700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>9600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>10700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>7000</v>
       </c>
-      <c r="AG62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AH62" s="3" t="s">
         <v>16</v>
       </c>
@@ -6152,8 +6298,11 @@
       <c r="AL62" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AM62" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6262,8 +6411,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6372,8 +6524,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6482,101 +6637,104 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3">
+      <c r="D66" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E66" s="3">
         <v>558800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>276400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>527400</v>
       </c>
-      <c r="G66" s="3">
-        <v>258600</v>
-      </c>
-      <c r="H66" s="3">
+      <c r="H66" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I66" s="3">
         <v>422800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>324300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>259200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>274400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>281900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>336000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>324500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>335900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>364300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>378200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>401500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>398000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>376600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>366600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>378400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>405000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>407000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>412900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>374500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>334300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>273300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>212200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>163700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>140300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>251600</v>
       </c>
-      <c r="AG66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AH66" s="3" t="s">
         <v>16</v>
       </c>
@@ -6592,8 +6750,11 @@
       <c r="AL66" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AM66" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6632,8 +6793,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6742,8 +6904,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6852,8 +7017,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6942,11 +7110,11 @@
         <v>0</v>
       </c>
       <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG70" s="3">
         <v>434700</v>
       </c>
-      <c r="AG70" s="3">
-        <v>0</v>
-      </c>
       <c r="AH70" s="3">
         <v>0</v>
       </c>
@@ -6962,8 +7130,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7072,101 +7243,104 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E72" s="3">
         <v>-272400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-271000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-257400</v>
       </c>
-      <c r="G72" s="3">
-        <v>-251700</v>
-      </c>
-      <c r="H72" s="3">
+      <c r="H72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I72" s="3">
         <v>-257400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-272200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-217100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-220100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-235800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-243200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-157500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-166900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-164200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-162300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-123000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-199500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-226300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-245200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-296800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-224900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-276600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-295900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-324700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-336800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-355400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-347000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-348400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-365300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-59100</v>
       </c>
-      <c r="AG72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AH72" s="3" t="s">
         <v>16</v>
       </c>
@@ -7182,8 +7356,11 @@
       <c r="AL72" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AM72" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7292,8 +7469,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7402,8 +7582,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7512,101 +7695,104 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3">
+      <c r="D76" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E76" s="3">
         <v>711200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1034500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1087100</v>
       </c>
-      <c r="G76" s="3">
-        <v>1302500</v>
-      </c>
-      <c r="H76" s="3">
+      <c r="H76" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I76" s="3">
         <v>1318100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1498300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1530700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1552400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1577600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1608500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1585200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1527300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1476700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1448100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1543200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1470100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1449400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1360900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1432500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1389500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1428600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1337300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1330900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1239400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>869700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>819800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>768600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>743300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>-58300</v>
       </c>
-      <c r="AG76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AH76" s="3" t="s">
         <v>16</v>
       </c>
@@ -7622,8 +7808,11 @@
       <c r="AL76" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AM76" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7732,233 +7921,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E81" s="3">
         <v>100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-23600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>3400</v>
       </c>
-      <c r="G81" s="3">
-        <v>4100</v>
-      </c>
-      <c r="H81" s="3">
+      <c r="H81" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I81" s="3">
         <v>9800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-38800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>3200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>5800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-82500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>8300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-2700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-43100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>74500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>26700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>26600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>35200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>37300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>30500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>27000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>24600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>19200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>18600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>9700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>14500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>7900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-310800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-71200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-700</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-5800</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-2200</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-6100</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-20000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>-24800</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7997,8 +8195,9 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8029,8 +8228,8 @@
       <c r="L83" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
+      <c r="M83" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="N83" s="3">
         <v>0</v>
@@ -8107,8 +8306,11 @@
       <c r="AL83" s="3">
         <v>0</v>
       </c>
+      <c r="AM83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8217,8 +8419,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8327,8 +8532,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8437,8 +8645,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8547,8 +8758,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8657,8 +8871,11 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -8689,8 +8906,8 @@
       <c r="L89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M89" s="3">
-        <v>0</v>
+      <c r="M89" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="N89" s="3">
         <v>0</v>
@@ -8767,8 +8984,11 @@
       <c r="AL89" s="3">
         <v>0</v>
       </c>
+      <c r="AM89" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8807,8 +9027,9 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8839,8 +9060,8 @@
       <c r="L91" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
+      <c r="M91" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
@@ -8917,8 +9138,11 @@
       <c r="AL91" s="3">
         <v>0</v>
       </c>
+      <c r="AM91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9027,8 +9251,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9137,8 +9364,11 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -9169,8 +9399,8 @@
       <c r="L94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
+      <c r="M94" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="N94" s="3">
         <v>0</v>
@@ -9247,8 +9477,11 @@
       <c r="AL94" s="3">
         <v>0</v>
       </c>
+      <c r="AM94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9287,8 +9520,9 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9319,8 +9553,8 @@
       <c r="L96" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -9397,8 +9631,11 @@
       <c r="AL96" s="3">
         <v>0</v>
       </c>
+      <c r="AM96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9507,8 +9744,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9617,8 +9857,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9727,8 +9970,11 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -9759,8 +10005,8 @@
       <c r="L100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
+      <c r="M100" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="N100" s="3">
         <v>0</v>
@@ -9837,8 +10083,11 @@
       <c r="AL100" s="3">
         <v>0</v>
       </c>
+      <c r="AM100" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9869,8 +10118,8 @@
       <c r="L101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -9947,8 +10196,11 @@
       <c r="AL101" s="3">
         <v>0</v>
       </c>
+      <c r="AM101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -9979,8 +10231,8 @@
       <c r="L102" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M102" s="3">
-        <v>0</v>
+      <c r="M102" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="N102" s="3">
         <v>0</v>
@@ -10055,6 +10307,9 @@
         <v>0</v>
       </c>
       <c r="AL102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM102" s="3">
         <v>0</v>
       </c>
     </row>
